--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -15,16 +15,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_終了コード" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_環境変数" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_実行例" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_JVM_OTel設定" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_概要'!$A$2:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_概要'!$A$2:$D$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_build_and_push'!$A$2:$H$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_buildx_build_and_push'!$A$2:$H$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_build_and_verify'!$A$2:$H$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_処理フロー'!$A$2:$E$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_build_and_verify'!$A$2:$H$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_処理フロー'!$A$2:$E$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_終了コード'!$A$2:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_環境変数'!$A$2:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_環境変数'!$A$2:$E$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_実行例'!$A$2:$D$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_JVM_OTel設定'!$A$2:$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -101,7 +103,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -123,11 +125,113 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -158,6 +262,31 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -525,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -535,480 +664,511 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>3 スクリプトの比較と使い分け</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>観点</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>目的</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>compose でビルドし ECR へプッシュ</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>buildx でビルドし ECR へプッシュ</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>ビルドと動作確認 (ECR 操作なし)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>ビルド方法</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>docker compose build</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>docker buildx build --load</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>docker compose build</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>ビルド定義</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>compose.yml</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Dockerfile + ビルドコンテキスト</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>compose.yml</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>ECR ログイン / タグ付け / プッシュ</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>imagedefinition.json 出力</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>起動確認 / URL 応答確認</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>--build-only 経由で可</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>あり (中核機能)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>コンテナ内調査 (bash/HTTP/ログ)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>--build-only 経由で可</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>JVM パラメータ / OpenTelemetry 表示</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>--build-only 経由で可</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>あり (起動確認時に自動)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>シークレット注入</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>compose.yml の secrets</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>--secret id=...,env=...</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>compose.yml の secrets</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>プラットフォーム指定</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>--platform (単一のみ)</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>必須コマンド</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>docker / aws / compose</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>docker / aws / buildx</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>docker / compose (+curl, +aws)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>AWS 認証 (aws login --remote)</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>--jboss-password-param 時のみ</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>ECR 権限</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>必須 (無い場合はスイッチバック)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>必須 (無い場合はスイッチバック)</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>--dry-run</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>--log-dir</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>なし (委譲元で対応)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>--copy-file</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>終了コード</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>0 / 1 / 2</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>0 / 1 / 2</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>0 / 1 / 2</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>行数の目安</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>約 1,000 行</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>約 1,000 行</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>約 5,400 行</t>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>約 6,000 行</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>【共通の前提】想定実行環境は RHEL 9.6 の EC2 インスタンス (bash 5.x / GNU coreutils / Docker CE)。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>【共通の前提】ログ・イメージタグ・ログファイル名の時刻はすべて JST に固定される (Asia/Tokyo → JST-9 の順にフォールバック)。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>【イメージタグ】&lt;TAG_PREFIX&gt;-&lt;YYYYMMDDHHMMSS&gt; 形式。リポジトリ名 (--repository) とは独立に指定できる。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>【命名規則】リポジトリ名は小文字英数字と . _ - / のみ (大文字不可)。タグは英数字と . _ - (大文字可、128 文字以内)。ビルド開始前に検証される。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>【委譲】build_and_push.sh --build-only は build_and_verify.sh へ委譲される。ECR 関連オプションは警告のうえ無視される。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>【中断時】SIGINT (Ctrl-C) / SIGTERM で中断しても EXIT トラップが動作し、一時コピーしたファイルと一時ファイルは削除される。</t>
         </is>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>【自動表示】build_and_verify.sh は起動確認を伴う実行で、Java の JVM パラメータと OpenTelemetry 環境変数・JVM パラメータを自動表示する (オプション指定は不要)。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D20"/>
-  <mergeCells count="7">
+  <autoFilter ref="A2:D21"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A24:D24"/>
   </mergeCells>
@@ -1090,13 +1250,13 @@
           <t>■ ECR 接続先</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="17" t="n"/>
+      <c r="H3" s="18" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1314,13 +1474,13 @@
           <t>■ ビルドと出力</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="18" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1572,13 +1732,13 @@
           <t>■ 実行制御・ログ</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="18" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1750,13 +1910,13 @@
           <t>■ 一時ファイル</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="18" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1806,13 +1966,13 @@
           <t>■ JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="17" t="n"/>
+      <c r="H23" s="18" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1946,13 +2106,13 @@
           <t>■ スイッチバック</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2169,13 +2329,13 @@
           <t>■ ECR 接続先 (compose 版と同一)</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="17" t="n"/>
+      <c r="H3" s="18" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2385,13 +2545,13 @@
           <t>■ buildx ビルド (このスクリプト固有)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="18" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2803,13 +2963,13 @@
           <t>■ 出力・実行制御</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="18" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -3023,13 +3183,13 @@
           <t>■ 一時ファイル</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="18" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -3079,13 +3239,13 @@
           <t>■ JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="18" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -3261,13 +3421,13 @@
           <t>■ スイッチバック (compose 版と同一)</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
+      <c r="G33" s="17" t="n"/>
+      <c r="H33" s="18" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3412,7 +3572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3426,1897 +3586,1996 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>build_and_verify.sh パラメータ一覧 (ビルド + 動作確認・ECR 操作なし)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>分類</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>値の形式</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>既定値</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>複数指定</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>備考・注意</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>■ ビルド関連</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="21" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>ビルド</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>--local-image NAME</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>イメージ名</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>j1/base.local</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>compose build で生成されるローカルイメージ名</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>compose.yml の image: と一致させること</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>ビルド</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>--compose-file FILE</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>ファイルパス</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>compose.yml</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>compose 定義ファイル</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="H5" s="14" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>ビルド</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>--compose-service NAME</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>サービス名</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>(全サービス)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>可 (繰り返し / カンマ区切り)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>ビルド・起動対象のサービス</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>複数指定時は base を単独で先行ビルド。base は起動対象にならない</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>ビルド</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>--no-cache</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>フラグ</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>キャッシュを破棄してビルドする</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="H7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>ビルド</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>--dry-run</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>フラグ</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>ビルド/起動/URL 呼び出し/ファイル操作を行わず内容のみ表示</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>レポート出力もスキップされる</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>一時ファイル</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>--copy-file SRC:DEST_DIR</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>コピー元:コピー先ディレクトリ</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>(なし)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>ビルド前にコピーし、処理終了後に自動削除する</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>コピー先は既存ディレクトリ。同名ファイルがあれば中止 (exit 1)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>■ JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="21" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>シークレット</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>--jboss-password-param NAME</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>SSM パラメータ名</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>(なし)</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>パラメータストアから取得する</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>このオプション使用時のみ aws コマンドと AWS 認証が必要</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>シークレット</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>--jboss-password VALUE</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>パスワード文字列</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>(なし)</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>マスターパスワードを直接指定する</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>ps / シェル履歴に平文が残るため非推奨。param とは排他</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>シークレット</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>--jboss-password-env NAME</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>環境変数名</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>シークレット受け渡しに使う環境変数名</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>単独指定時は事前 export 済みの値を使用</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>シークレット</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>--region REGION</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>AWS リージョン名</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>ap-northeast-1 (env: AWS_REGION)</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>パラメータストア参照時のリージョン</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr"/>
+      <c r="H14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>■ 起動確認 (JBoss EAP / WildFly)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="21" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>--verify-startup</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>フラグ</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>ビルド後にコンテナを起動し、起動完了をログから確認する</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>確認後はコンテナを停止・削除する</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>--startup-service NAME</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>サービス名</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>(対象全体)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>可 (繰り返し / カンマ区切り)</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>起動完了チェックを行うサービス</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>指定すると --verify-startup を暗黙に有効化。--compose-service の対象に含める必要がある</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>--startup-log-pattern P</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>拡張正規表現</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>WFLYSRV0025:</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>起動完了とみなすログのパターン</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>WFLYSRV0026 / WFLYSRV0056 は失敗扱い (固定)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>--startup-timeout SEC</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>1 以上の整数</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>起動完了を待つ最大秒数</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>0 や非数値は exit 2</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>--startup-interval SEC</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>1 以上の整数</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="15" t="inlineStr">
         <is>
           <t>ポーリング間隔 (秒)</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr"/>
+      <c r="H20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>--startup-log-lines N|all</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>1 以上の整数または all</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>logs モードで選択したログにも適用される</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>--wait-healthy</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>フラグ</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="15" t="inlineStr">
         <is>
           <t>compose up に --wait を付け healthy になるまで待つ</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="15" t="inlineStr">
         <is>
           <t>compose.yml の healthcheck / depends_on 整備が前提</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>--wait-timeout SEC</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>1 以上の整数</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>--wait の最大待機秒数</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>--allow-service-exit NAME</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>サービス名</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>(なし)</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>可 (繰り返し / カンマ区切り)</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="15" t="inlineStr">
         <is>
           <t>停止していても失敗扱いにしないサービス</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="15" t="inlineStr">
         <is>
           <t>初期化専用の短命サービス等に使う</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>--suppress-startup-logs</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>フラグ</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>起動ログの表示を抑制する (判定は継続)</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>失敗時は原因を隠さないため表示される</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>--suppress-removed-logs</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>フラグ</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="15" t="inlineStr">
         <is>
           <t>compose down の Removed 等の出力を抑制する</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr"/>
+      <c r="H26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>--keep-container</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>フラグ</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>確認後もコンテナを停止・削除せずに残す</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>--cleanup-all-docker-data とは排他</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>■ URL 応答確認</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="21" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>URL 確認</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>--verify-url URL</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>(なし)</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>起動確認後にこの URL へリクエストして応答を確認する</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>単独指定でもコンテナを起動する</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>URL 確認</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>--expect-status CODE</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>HTTP ステータスコード</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="15" t="inlineStr">
         <is>
           <t>期待するステータスコード</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr"/>
+      <c r="H30" s="15" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>URL 確認</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>--url-method METHOD</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>HTTP メソッド</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>リクエストメソッド</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
+      <c r="H31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>URL 確認</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>--url-content-type TYPE</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>MIME タイプ</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>(ボディに応じ自動)</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="15" t="inlineStr">
         <is>
           <t>Content-Type ヘッダ値</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H32" s="15" t="inlineStr">
         <is>
           <t>--verify-url と併用必須</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>URL 確認</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>--url-body-json JSON</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>JSON 文字列</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>(なし)</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>リクエストボディに JSON を設定する</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>Content-Type 未指定時は application/json。form とは排他</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>URL 確認</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>--url-body-form DATA</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>key=value&amp;...</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>(なし)</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="15" t="inlineStr">
         <is>
           <t>リクエストボディに form データを設定する</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="15" t="inlineStr">
         <is>
           <t>Content-Type 未指定時は application/x-www-form-urlencoded。json とは排他</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>URL 確認</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>--url-timeout SEC</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>1 以上の整数</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>期待応答を得るまでの最大秒数</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>HTTP / healthcheck 診断の 1 回あたりの最大秒数にも使う</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>URL 確認</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>--url-interval SEC</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>1 以上の整数</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G36" s="15" t="inlineStr">
         <is>
           <t>リトライ間隔 (秒)</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr"/>
+      <c r="H36" s="15" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>URL 確認</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>--url-insecure</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>フラグ</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>TLS 証明書検証を無効化する (curl -k)</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
+      <c r="H37" s="14" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>■ 起動維持後の対話操作</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20" t="n"/>
+      <c r="F38" s="20" t="n"/>
+      <c r="G38" s="20" t="n"/>
+      <c r="H38" s="21" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>対話操作</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>--keep-container-mode MODE</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>bash / http / logs</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>(なし)</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>起動後に残したコンテナで対話操作を行う</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>--verify-startup と --keep-container を暗黙に有効化。対象複数時は番号選択</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>対話操作</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>--jboss-context-root ROOT</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>コンテキストルートのパス</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>(WFLYUT0021 ログから検出)</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="15" t="inlineStr">
         <is>
           <t>http モードで使うコンテキストルート</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H40" s="15" t="inlineStr">
         <is>
           <t>--keep-container-mode http と併用必須。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>対話操作</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>--jboss-http-port PORT</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>1〜65535</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>(WFLYUT0006 ログから検出。既定 8080)</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>http モードで使うコンテナ側 HTTP ポート</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>--keep-container-mode http と併用必須。公開ポートがあれば自動変換</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>■ 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n"/>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
-      <c r="H42" s="7" t="n"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="21" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>情報表示</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>--env-list-limit N|all</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>1 以上の整数または all</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>環境変数一覧の表示件数 (コンテナごと)</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" s="14" t="inlineStr">
         <is>
           <t>コンテナ起動を伴う場合のみ有効</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>情報表示</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>--env-list-file FILE</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>ファイルパス</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>(なし)</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F44" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="15" t="inlineStr">
         <is>
           <t>環境変数一覧をファイルにも出力する</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H44" s="15" t="inlineStr">
         <is>
           <t>画面表示は継続</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>情報表示</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>--directory-tree-depth N|all</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>1 以上の整数または all</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
         <is>
           <t>コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H45" s="14" t="inlineStr">
         <is>
           <t>JBoss デプロイ構造にも同じ深さを適用</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>情報表示</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>--directory-file-limit N|all</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>1 以上の整数または all</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>(ファイル非表示)</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="15" t="inlineStr">
         <is>
           <t>通常ファイルの表示を有効化する</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="H46" s="15" t="inlineStr">
         <is>
           <t>N 件超過時は拡張子別件数を表示。all は常に全ファイル名</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>情報表示</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>--deployment-dir-env NAME</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>環境変数名</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>(なし)</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>可 (繰り返し / カンマ区切り)</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>ディレクトリパスを値に持つ環境変数</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" s="14" t="inlineStr">
         <is>
           <t>その配下を JBoss デプロイ構造と併せて階層表示</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>レポート</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>--report-dir DIR</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>ディレクトリパス</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>(なし)</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G48" s="15" t="inlineStr">
         <is>
           <t>全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存する</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>画面の制限にかかわらず全深度・全ファイル名。失敗時は全サービスのログも全行保存</t>
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>[1] ビルド結果 / [2] 環境変数 / [3] ツリー / [4] JBoss デプロイ構造 / [5] JVM パラメータ / [6] OpenTelemetry / [7] サービス別ログ (失敗時) を保存。画面の制限にかかわらず全量</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>■ オプション指定不要の自動表示 (起動確認を伴う実行のみ)</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="20" t="n"/>
+      <c r="H49" s="21" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>情報表示</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>常に表示</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>コンテナ内の Java プロセスを /proc から検出し、JVM パラメータを分類表示する</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>ヒープ・メモリ / GC / Java エージェント / OpenTelemetry / JBoss / システムプロパティ / クラスパス・モジュール / その他 / 起動対象への引数。JAVA_OPTS・JAVA_TOOL_OPTIONS 等の環境変数経由の指定も別枠で表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>情報表示</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>常に表示</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>OpenTelemetry の環境変数と JVM パラメータを 1 つの一覧にまとめて表示する</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>OTEL_ 接頭辞の標準環境変数 / AWS_XRAY_* 等の関連環境変数 / -Dotel.* と OpenTelemetry の -javaagent / 主要設定の未設定検出。Java 非実行のコンテナでも環境変数側を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>■ 終了時のクリーンアップ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="B52" s="20" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="20" t="n"/>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="20" t="n"/>
+      <c r="H52" s="21" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
         <is>
           <t>クリーンアップ</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B53" s="22" t="inlineStr">
         <is>
           <t>--cleanup-all-docker-data</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>フラグ</t>
         </is>
       </c>
-      <c r="D50" s="10" t="inlineStr">
+      <c r="D53" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="E53" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F53" s="22" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G50" s="10" t="inlineStr">
+      <c r="G53" s="22" t="inlineStr">
         <is>
           <t>終了時に Docker context の全データを削除する</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H53" s="22" t="inlineStr">
         <is>
           <t>確認フレーズ『DELETE ALL DOCKER DATA』の入力が必須。--keep-container とは排他。取り扱い注意</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>■ その他</t>
         </is>
       </c>
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="B54" s="20" t="n"/>
+      <c r="C54" s="20" t="n"/>
+      <c r="D54" s="20" t="n"/>
+      <c r="E54" s="20" t="n"/>
+      <c r="F54" s="20" t="n"/>
+      <c r="G54" s="20" t="n"/>
+      <c r="H54" s="21" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>ヘルプ</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>-h, --help</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>フラグ</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E55" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G55" s="14" t="inlineStr">
         <is>
           <t>ヘルプを表示して exit 0</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr"/>
+      <c r="H55" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H52"/>
-  <mergeCells count="9">
+  <autoFilter ref="A2:H55"/>
+  <mergeCells count="10">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A42:H42"/>
@@ -5333,7 +5592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5344,1699 +5603,1749 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>処理の流れ (フェーズ別)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>スクリプト</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>処理内容</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>失敗時の動作</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>■ build_and_push.sh (compose 版)</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="21" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>初期化</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>表示タイムゾーンを JST に固定 (Asia/Tokyo → JST-9 の順)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>警告のみで継続</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>引数の事前走査</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>--log-dir の値取得と --build-only の検出 (値を取るオプションの値は読み飛ばす)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>ログ複製開始</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>--log-dir 指定時、tee で DIR/build_and_push_&lt;日時&gt;.log へ全出力を複製</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>ディレクトリ作成失敗で exit 1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>--build-only 委譲</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>ECR 専用オプションを警告して除去し build_and_verify.sh を実行</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>委譲先が無ければ exit 1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>引数パース</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>全オプションを解釈 (値の欠落を検出)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>exit 2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>オプション検証</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>JBoss パスワードの取得元排他、環境変数名の形式</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>exit 2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>依存確認</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>docker / aws の存在確認</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Docker 確認</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>docker info でデーモン接続を確認</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>exit 1 (--dry-run 時は警告のみ)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>AWS 認証確認</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>aws sts get-caller-identity</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>exit 1 (--dry-run 時は警告のみ)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>compose 判定</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>docker compose (v2) → docker-compose (v1) の順に検出</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>レジストリ決定</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>--registry か &lt;account&gt;.dkr.ecr.&lt;region&gt;.amazonaws.com を組み立て</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>exit 2</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>イメージ参照検証</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>リポジトリ名 (小文字のみ) とタグ接頭辞の形式を検証</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>exit 2 (ビルド前に検出)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>ECR 権限チェック</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>aws ecr get-login-password の成否で判定。成功時のトークンを保持</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>auto-switchback / dry-run 継続 / exit 1</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>シークレット準備</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>パラメータストア・直接指定・既存環境変数から取得し export</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>事前コピー</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>--copy-file を検証してコピー (終了時に自動削除)</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>exit 1 / exit 2</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>ビルド</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>docker compose -f &lt;file&gt; build [--no-cache] [service]</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>イメージ確認</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>docker image inspect &lt;local-image&gt;</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>exit 1 (--dry-run 時はスキップ)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>タグ生成</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>&lt;TAG_PREFIX&gt;-&lt;YYYYMMDDHHMMSS&gt; (JST)</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>ECR ログイン</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>docker login --username AWS --password-stdin</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>タグ付け・プッシュ</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>docker image tag → docker push (出力を tee で保存)</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>原因診断ガイドを表示して exit 1</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>出力</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>imagedefinition.json を書き込み</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>build_and_push.sh</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>後始末 (EXIT)</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>コピーファイル削除 → 一時ファイル削除 → 処理実行時間 → ログ書き込み完了</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>■ buildx_build_and_push.sh (buildx 版)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="21" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>初期化</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>表示タイムゾーンを JST に固定</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>警告のみで継続</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>ログ複製開始</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>--log-dir を事前走査し、パース前に tee でログ複製を開始</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>ディレクトリ作成失敗で exit 1</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>引数パース</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>全オプションを解釈 (値の欠落を検出)</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>exit 2 (エラーもログに残る)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>オプション検証</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>JBoss パスワードの排他、環境変数名、--jboss-secret-id の空文字禁止</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>exit 2</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>依存確認</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>aws / docker の存在確認</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>buildx 確認</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>docker buildx version</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>exit 1 (導入方法を案内)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>Docker 確認</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>docker info でデーモン接続を確認</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>exit 1 (--dry-run 時は警告のみ)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>AWS 認証確認</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>aws sts get-caller-identity</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>exit 1 (--dry-run 時は警告のみ)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>platform 検証</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>--load のため複数プラットフォーム指定を禁止</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>exit 2</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>progress 検証</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>auto / plain / tty / rawjson / quiet のみ許可</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>exit 2</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>レジストリ決定</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>--registry か &lt;account&gt;.dkr.ecr.&lt;region&gt;.amazonaws.com を組み立て</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>exit 2</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>イメージ参照検証</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>リポジトリ名 (小文字のみ) とタグ接頭辞の形式を検証</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>exit 2 (ビルド前に検出)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>ECR 権限チェック</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>aws ecr get-login-password の成否で判定</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>auto-switchback / dry-run 継続 / exit 1</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>シークレット準備</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>マスターパスワードを取得し export</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>事前コピー</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>--copy-file を検証してコピー (終了時に自動削除)</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>exit 1 / exit 2</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>入力確認</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>--dockerfile のファイルと --context のディレクトリの存在確認</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B43" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>ビルド</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>docker buildx build --load -t &lt;image&gt; -f &lt;dockerfile&gt; [各オプション] &lt;context&gt;</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>イメージ確認</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>docker image inspect &lt;local-image&gt;</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>exit 1 (--dry-run 時はスキップ)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B45" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>タグ生成</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>&lt;TAG_PREFIX&gt;-&lt;YYYYMMDDHHMMSS&gt; (JST)</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>ECR ログイン</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>docker login --username AWS --password-stdin</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>タグ付け・プッシュ</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>docker image tag → docker image push (出力を tee で保存)</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>原因診断ガイドを表示して exit 1</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>出力</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>imagedefinition.json を書き込み</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
+      <c r="B49" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>後始末 (EXIT)</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>コピーファイル削除 → 一時ファイル削除 → 処理実行時間 → ログ書き込み完了</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>■ build_and_verify.sh (ビルド + 動作確認)</t>
         </is>
       </c>
-      <c r="B50" s="7" t="n"/>
-      <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
-      <c r="E50" s="7" t="n"/>
+      <c r="B50" s="20" t="n"/>
+      <c r="C50" s="20" t="n"/>
+      <c r="D50" s="20" t="n"/>
+      <c r="E50" s="21" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B51" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>初期化</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>表示タイムゾーンを JST に固定</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="14" t="inlineStr">
         <is>
           <t>警告のみで継続</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" s="15" t="inlineStr">
         <is>
           <t>引数パース</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>カンマ区切りを分割しつつ全オプションを解釈 (値の欠落を検出)</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>exit 2</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n">
+      <c r="B53" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>入力値の検証</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>数値 (1 以上)、モード、ポート範囲、排他関係、サービス指定の整合性</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="14" t="inlineStr">
         <is>
           <t>exit 2</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="15" t="inlineStr">
         <is>
           <t>起動対象の決定</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>COMPOSE_TARGET_SERVICES = 指定サービス - base</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>起動対象が無ければ exit 2</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n">
+      <c r="B55" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>依存確認</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>docker (+ --verify-url/http モード時は curl、--jboss-password-param 時は aws)</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="14" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="15" t="inlineStr">
         <is>
           <t>AWS 認証確認</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="15" t="inlineStr">
         <is>
           <t>--jboss-password-param 指定時のみ aws sts get-caller-identity</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr">
         <is>
           <t>exit 1 (--dry-run 時は警告のみ)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n">
+      <c r="B57" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>compose 判定</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>docker compose (v2) → docker-compose (v1)。並列オプションも準備</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="14" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B58" s="4" t="n">
+      <c r="B58" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="15" t="inlineStr">
         <is>
           <t>EXIT トラップ設定</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="15" t="inlineStr">
         <is>
           <t>cleanup_all (レポート → Docker 削除 → down → 一時ファイル削除)</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E58" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
+      <c r="B59" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="14" t="inlineStr">
         <is>
           <t>シークレット準備</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>マスターパスワードを取得し export</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="14" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="15" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="15" t="inlineStr">
         <is>
           <t>事前コピー</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="15" t="inlineStr">
         <is>
           <t>--copy-file を検証してコピー (終了時に自動削除)</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr">
         <is>
           <t>exit 1 / exit 2</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n">
+      <c r="B61" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="14" t="inlineStr">
         <is>
           <t>ビルド (第 1 フェーズ)</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>サービス 2 個以上指定時、base を単独で先行ビルドし、イメージを確認</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="14" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="15" t="inlineStr">
         <is>
           <t>ビルド (第 2 フェーズ)</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="15" t="inlineStr">
         <is>
           <t>base 以外をまとめて並列ビルド (単一・未指定時は 1 回のビルド)</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" s="15" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n">
+      <c r="B63" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="14" t="inlineStr">
         <is>
           <t>イメージ確認</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>docker image inspect で id / 作成日時 (JST) / サイズを記録</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E63" s="14" t="inlineStr">
         <is>
           <t>exit 1 (--dry-run 時はスキップ)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="15" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="15" t="inlineStr">
         <is>
           <t>分岐</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>--verify-startup / --verify-url いずれも無ければビルドのみで終了</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr">
         <is>
           <t>exit 0</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n">
+      <c r="B65" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="14" t="inlineStr">
         <is>
           <t>コンテナ起動</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="14" t="inlineStr">
         <is>
           <t>compose up -d --no-build (--wait-healthy 時は --wait --wait-timeout)</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E65" s="14" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="15" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="15" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="15" t="inlineStr">
         <is>
           <t>起動完了パターンを検出するまでポーリング。失敗パターン・途中停止・タイムアウトを監視</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E66" s="15" t="inlineStr">
         <is>
           <t>ログを表示して exit 1</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n">
+      <c r="B67" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="14" t="inlineStr">
         <is>
           <t>URL 応答確認</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="14" t="inlineStr">
         <is>
           <t>curl でリトライしながら期待ステータスを待つ。応答本文の先頭 20 行を表示</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E67" s="14" t="inlineStr">
         <is>
           <t>exit 1</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="15" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="15" t="inlineStr">
         <is>
           <t>対話操作</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="15" t="inlineStr">
         <is>
           <t>--keep-container-mode に応じて bash / http / logs を実行</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E68" s="15" t="inlineStr">
         <is>
           <t>exit 1 (コンテナは残す)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n">
+      <c r="B69" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="14" t="inlineStr">
         <is>
           <t>情報表示</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="14" t="inlineStr">
         <is>
           <t>環境変数一覧 → コンテナ内ツリー → JBoss デプロイ構造</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E69" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="15" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B70" s="4" t="n">
+      <c r="B70" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>JVM パラメータ表示</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>/proc/&lt;pid&gt;/cmdline から Java プロセスを検出し、JVM パラメータを分類表示</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>検出できない場合はその旨を表示して継続</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>OpenTelemetry 表示</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>OTEL_* とその関連環境変数、-Dotel.* / OpenTelemetry の -javaagent を一覧表示</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>未検出の場合はその旨を表示して継続</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
         <is>
           <t>後始末 (EXIT)</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D72" s="15" t="inlineStr">
         <is>
           <t>全量レポート保存 → Docker 全体クリーンアップ (任意) → compose down → 一時ファイル削除</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E72" s="15" t="inlineStr">
         <is>
           <t>元の終了コードを優先。後始末失敗時は exit 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E70"/>
+  <autoFilter ref="A2:E72"/>
   <mergeCells count="4">
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A1:E1"/>
@@ -7326,7 +7635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7337,394 +7646,484 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>環境変数一覧</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>スクリプト</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>環境変数</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>対応オプション</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>共通 (push 系 2 本)</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>AWS_ACCOUNT_ID</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>入力</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>--account-id</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>レジストリ URL の組み立てに使用。オプション指定が優先される</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>共通 (push 系 2 本)</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>AWS_REGION</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>入力</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>--region</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>未設定時は AWS_DEFAULT_REGION → ap-northeast-1 の順にフォールバック</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>共通 (push 系 2 本)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>AWS_DEFAULT_REGION</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>入力</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>--region</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>AWS_REGION が未設定の場合に参照される</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>共通 (push 系 2 本)</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>ECR_REGISTRY</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>入力</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>--registry</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>レジストリ URL を直接指定する</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>共通 (push 系 2 本)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>SWITCHBACK_SHELL</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>入力</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>--switchback-shell</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>スイッチバック用シェルのパス</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>全 3 本</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>入力 / 設定</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>--jboss-password-env</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>既定のシークレット受け渡し変数。事前 export した値も利用できる。未使用時は空文字で定義される</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>全 3 本</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>TZ</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>設定</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Asia/Tokyo または JST-9 を設定し、表示時刻を JST に統一する</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>--secret env=NAME で参照する変数</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>入力</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>--secret</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>利用者が事前に export しておく (例: GITHUB_TOKEN)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>BUILDKIT_PROGRESS</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>入力 / 設定</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>ビルドログの表示形式。未指定時は plain を使用し、ビルドステップの出力欠落を防ぐ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>NO_COLOR</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>入力</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>定義されていれば起動ログの色分けを無効化する</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>CLICOLOR_FORCE</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>入力</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>0 以外なら非 tty でも色分けを強制する</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>TERM</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>入力</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>dumb の場合は色分けしない</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>全 3 本</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>TMPDIR</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>入力</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>一時ファイルの作成先 (mktemp が参照)</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>build_and_verify.sh (コンテナ側)</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>検出・表示</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>コンテナ内で JVM オプションを渡す環境変数。起動コマンドラインに現れないため、JVM パラメータ一覧へ別枠で表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>build_and_verify.sh (コンテナ側)</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>OTEL_* (接頭辞一致)</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>検出・表示</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>OpenTelemetry 標準環境変数。OTEL_SERVICE_NAME / OTEL_RESOURCE_ATTRIBUTES / OTEL_TRACES_EXPORTER / OTEL_METRICS_EXPORTER / OTEL_LOGS_EXPORTER / OTEL_EXPORTER_OTLP_* / OTEL_PROPAGATORS / OTEL_TRACES_SAMPLER / OTEL_INSTRUMENTATION_* / OTEL_JAVAAGENT_* / OTEL_SDK_DISABLED などを接頭辞で検出</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>build_and_verify.sh (コンテナ側)</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>AWS_XRAY_DAEMON_ADDRESS / AWS_XRAY_CONTEXT_MISSING / AWS_XRAY_TRACING_NAME / AWS_LAMBDA_EXEC_WRAPPER / AOT_CONFIG_CONTENT</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>検出・表示</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>OTEL_ 接頭辞を持たない OpenTelemetry 関連環境変数 (ADOT / X-Ray 連携、Collector 設定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>【区分の見方】「入力」「設定」は実行ホスト側の環境変数。「検出・表示」は起動したコンテナ内の環境変数を読み取って一覧表示するもので、スクリプトの動作は変わらない。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:E15"/>
-  <mergeCells count="1">
+  <autoFilter ref="A2:E18"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A20:E20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8298,7 +8697,11 @@
           <t>./build_and_verify.sh --verify-startup --report-dir ./reports --directory-tree-depth 3 --directory-file-limit 20</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr"/>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>JVM パラメータと OpenTelemetry 設定も同じレポートへ保存される</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -8329,4 +8732,692 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>JVM パラメータの分類と OpenTelemetry 設定の検出条件 (build_and_verify.sh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>対象 (名前・パターン)</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>表示先</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>説明・備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>■ JVM パラメータの分類 (上から順に判定し、最初に一致した分類へ入る)</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="21" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>JVM パラメータ</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>-javaagent: / -agentlib: / -agentpath:</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>パターン一致</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>[Java エージェント]</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>OpenTelemetry の -javaagent もここに入り、OpenTelemetry 一覧へも再掲される</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>JVM パラメータ</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>-Dotel.* / -Dio.opentelemetry.*</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>パターン一致</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>[OpenTelemetry]</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Java エージェントの設定をシステムプロパティで渡す形式</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>JVM パラメータ</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>-cp / -classpath / --class-path / -p / --module-path / --add-opens / --add-exports / --add-modules / --add-reads / --patch-module / --upgrade-module-path / --limit-modules / -Djava.class.path / -Djava.library.path / -Xbootclasspath*</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>パターン一致</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>[クラスパス・モジュール]</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>値を次の引数として取る書式は、次の引数を値として取り込む</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>JVM パラメータ</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>-Xms / -Xmx / -Xss / -Xmn / -XX:*Metaspace* / -XX:*Heap* / -XX:*RAM* / -XX:MaxDirectMemorySize / -XX:*CodeCache* / -XX:*ThreadStackSize* / -XX:*CompressedOops* / -XX:*CompressedClassSpaceSize*</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>パターン一致</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>[ヒープ・メモリ]</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>ヒープ・メタスペース・スタックの各サイズ指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>JVM パラメータ</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>-Xlog:gc* / -Xloggc: / -XX:*GC* / -XX:*SurvivorRatio* / -XX:*NewRatio* / -XX:*Tenuring*</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>パターン一致</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>[GC (ガベージコレクション)]</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>GC アルゴリズムと世代・ログの設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>JVM パラメータ</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>-Djboss.* / -Dorg.jboss.* / -Dwildfly.* / -Dorg.wildfly.* / -Dlogging.configuration / -Dmodule.path</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>パターン一致</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>[JBoss / WildFly]</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>JBoss EAP / WildFly 固有のシステムプロパティ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>JVM パラメータ</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>上記以外の -D 指定</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>パターン一致</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>[システムプロパティ (-D)]</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>-D[Standalone] のように値を持たない指定は名前だけを表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>JVM パラメータ</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>上記以外の - で始まるオプション</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>パターン一致</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>[その他 JVM オプション]</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>-server などの汎用オプション</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>JVM パラメータ</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>-jar / 主クラス / --module より後ろの引数</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>位置で判定</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>[起動対象へ渡される引数]</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>JBoss の -mp や org.jboss.as.standalone など。JVM ではなく起動対象が解釈する</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>■ JVM オプションを渡す環境変数 (起動コマンドラインに現れないため別枠で表示)</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="21" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>環境変数 (コンテナ側)</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>JAVA_OPTS / JAVA_OPTS_APPEND / JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JBOSS_JAVA_OPTS / JBOSS_JAVA_SIZING / JAVA_ARGS</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>名前が完全一致</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>[JVM オプションを渡す環境変数]</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>値をそのまま表示する。分類別の件数には含めない</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>■ OpenTelemetry 環境変数の特定条件</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="21" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>OpenTelemetry 環境変数</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>OTEL_ で始まる名前すべて</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>接頭辞一致</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>[OpenTelemetry 標準環境変数 (OTEL_*)]</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>OpenTelemetry 仕様が定める設定名の接頭辞。列挙を更新しなくても仕様追加に追随する</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>OpenTelemetry 環境変数 (代表例)</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>OTEL_SERVICE_NAME / OTEL_RESOURCE_ATTRIBUTES / OTEL_TRACES_EXPORTER / OTEL_METRICS_EXPORTER / OTEL_LOGS_EXPORTER / OTEL_EXPORTER_OTLP_ENDPOINT / OTEL_EXPORTER_OTLP_PROTOCOL / OTEL_EXPORTER_OTLP_HEADERS / OTEL_PROPAGATORS / OTEL_TRACES_SAMPLER / OTEL_BSP_* / OTEL_INSTRUMENTATION_* / OTEL_JAVAAGENT_* / OTEL_SDK_DISABLED / OTEL_LOG_LEVEL</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>接頭辞一致に含まれる</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>[OpenTelemetry 標準環境変数 (OTEL_*)]</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>上の接頭辞判定で自動的に対象となる代表的な設定名</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>OpenTelemetry 関連環境変数</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>AWS_XRAY_DAEMON_ADDRESS / AWS_XRAY_CONTEXT_MISSING / AWS_XRAY_TRACING_NAME / AWS_LAMBDA_EXEC_WRAPPER / AOT_CONFIG_CONTENT</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>名前が完全一致</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>[OpenTelemetry 関連環境変数]</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>OTEL_ 接頭辞を持たない ADOT / X-Ray 連携と Collector 設定用の変数</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>OpenTelemetry 関連環境変数 (条件付き)</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>JAVA_TOOL_OPTIONS / JDK_JAVA_OPTIONS / _JAVA_OPTIONS / JAVA_OPTS / JAVA_OPTS_APPEND / JBOSS_JAVA_OPTS</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>値が OpenTelemetry を参照する場合のみ</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>[OpenTelemetry 関連環境変数]</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>javaagent の注入に使われるため、値に opentelemetry / otel を含む場合だけ対象にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>■ OpenTelemetry 関連 JVM パラメータの特定条件</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="21" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>JVM パラメータ</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>-Dotel.* / -Dio.opentelemetry.*</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>パターン一致</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>[OpenTelemetry 関連 JVM パラメータ (コマンドライン)]</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>起動対象へ渡される引数側にあっても検出する</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>JVM パラメータ</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>値に opentelemetry を含むもの</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>部分一致</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>[OpenTelemetry 関連 JVM パラメータ (コマンドライン)]</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>-javaagent:/opt/otel/opentelemetry-javaagent.jar などのエージェント指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>JVM パラメータ</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>-javaagent:*otel* / -agentpath:*otel* / -agentlib:*otel*</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>パターン一致</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>[OpenTelemetry 関連 JVM パラメータ (コマンドライン)]</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>パス名に opentelemetry を含まないエージェント配置の救済</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>JVM パラメータ (環境変数由来)</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>上記と同じパターン</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>環境変数の値を空白で分割</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>[OpenTelemetry 関連 JVM パラメータ (環境変数由来)]</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>&lt;環境変数名&gt;: &lt;パラメータ名&gt; の形式で、由来が分かるように表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>■ 未設定と判定する主要設定 (環境変数とシステムプロパティの両方が無い場合)</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="21" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>未設定判定</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>OTEL_SERVICE_NAME / OTEL_RESOURCE_ATTRIBUTES / OTEL_TRACES_EXPORTER / OTEL_METRICS_EXPORTER / OTEL_LOGS_EXPORTER / OTEL_EXPORTER_OTLP_ENDPOINT / OTEL_EXPORTER_OTLP_PROTOCOL / OTEL_PROPAGATORS / OTEL_TRACES_SAMPLER / OTEL_SDK_DISABLED</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>環境変数とシステムプロパティの双方が未設定</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>[未設定の主要 OpenTelemetry 設定]</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>対応するプロパティ名は「小文字化して _ を . へ置換」で求める (OTEL_SERVICE_NAME ⇔ -Dotel.service.name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>■ 値のマスキング</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="21" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>マスキング</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>PASSWORD / PASSWD / TOKEN / SECRET / PRIVATE_KEY / ACCESS_KEY / API_KEY / CREDENTIAL / HEADERS を名前に含むもの</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>名前の部分一致 (大文字小文字を無視)</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>全一覧に共通</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>値を [REDACTED] へ置き換える。名前は分類・設定漏れの確認のため残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>【取得方法】コンテナ内の /proc/&lt;pid&gt;/cmdline を読み、実行ファイル名が java のプロセスを検出する。ps / jcmd / jinfo をコンテナへ要求しないため、JDK ツールを含まないランタイム専用イメージでも取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>【表示条件】起動確認を伴う実行 (--verify-startup / --verify-url) のときに自動表示され、--report-dir 指定時は [5] / [6] としてレポートにも保存される。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E28"/>
+  <mergeCells count="9">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_概要'!$A$2:$D$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_build_and_push'!$A$2:$H$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_buildx_build_and_push'!$A$2:$H$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_build_and_verify'!$A$2:$H$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_build_and_verify'!$A$2:$H$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_処理フロー'!$A$2:$E$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_終了コード'!$A$2:$D$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_環境変数'!$A$2:$E$18</definedName>
@@ -1152,7 +1152,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
@@ -3572,7 +3571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4501,42 +4500,46 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>起動確認</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>--suppress-removed-logs</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>フラグ</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>--shutdown-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G26" s="15" t="inlineStr">
-        <is>
-          <t>compose down の Removed 等の出力を抑制する</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>エラー終了時に SIGTERM で終了させる際、SIGKILL までの猶予秒数</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>ECS の StopTimeout 既定と同じ。停止後に増えたログを終了ログとして表示・保存する</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
@@ -4546,7 +4549,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>--keep-container</t>
+          <t>--no-shutdown-logs</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
@@ -4571,53 +4574,77 @@
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>確認後もコンテナを停止・削除せずに残す</t>
+          <t>エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>--cleanup-all-docker-data とは排他</t>
+          <t>従来どおり compose down でまとめて削除する。--keep-container 指定時は元から実行されない</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>■ URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="20" t="n"/>
-      <c r="H28" s="21" t="n"/>
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>起動確認</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>フラグ</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>compose down の Removed 等の出力を抑制する</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>URL 確認</t>
+          <t>起動確認</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>--verify-url URL</t>
+          <t>--keep-container</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>フラグ</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>(なし)</t>
+          <t>false</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
@@ -4627,52 +4654,28 @@
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>起動確認後にこの URL へリクエストして応答を確認する</t>
+          <t>確認後もコンテナを停止・削除せずに残す</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>単独指定でもコンテナを起動する</t>
+          <t>--cleanup-all-docker-data とは排他</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>URL 確認</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="inlineStr">
-        <is>
-          <t>期待するステータスコード</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="n"/>
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>■ URL 応答確認</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="20" t="n"/>
+      <c r="G30" s="20" t="n"/>
+      <c r="H30" s="21" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -4682,17 +4685,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>--url-method METHOD</t>
+          <t>--verify-url URL</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>HTTP メソッド</t>
+          <t>URL</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>(なし)</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
@@ -4707,10 +4710,14 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>リクエストメソッド</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="n"/>
+          <t>起動確認後にこの URL へリクエストして応答を確認する</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>単独指定でもコンテナを起動する</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
@@ -4720,17 +4727,17 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>--url-content-type TYPE</t>
+          <t>--expect-status CODE</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>MIME タイプ</t>
+          <t>HTTP ステータスコード</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>(ボディに応じ自動)</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
@@ -4745,14 +4752,10 @@
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
-          <t>Content-Type ヘッダ値</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="inlineStr">
-        <is>
-          <t>--verify-url と併用必須</t>
-        </is>
-      </c>
+          <t>期待するステータスコード</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -4762,17 +4765,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>--url-body-json JSON</t>
+          <t>--url-method METHOD</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>JSON 文字列</t>
+          <t>HTTP メソッド</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>(なし)</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
@@ -4787,14 +4790,10 @@
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>リクエストボディに JSON を設定する</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>Content-Type 未指定時は application/json。form とは排他</t>
-        </is>
-      </c>
+          <t>リクエストメソッド</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
@@ -4804,17 +4803,17 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>--url-body-form DATA</t>
+          <t>--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>key=value&amp;...</t>
+          <t>MIME タイプ</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>(なし)</t>
+          <t>(ボディに応じ自動)</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
@@ -4829,12 +4828,12 @@
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>
-          <t>リクエストボディに form データを設定する</t>
+          <t>Content-Type ヘッダ値</t>
         </is>
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Content-Type 未指定時は application/x-www-form-urlencoded。json とは排他</t>
+          <t>--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -4846,17 +4845,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>--url-timeout SEC</t>
+          <t>--url-body-json JSON</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>1 以上の整数</t>
+          <t>JSON 文字列</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>(なし)</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
@@ -4871,12 +4870,12 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>期待応答を得るまでの最大秒数</t>
+          <t>リクエストボディに JSON を設定する</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>HTTP / healthcheck 診断の 1 回あたりの最大秒数にも使う</t>
+          <t>Content-Type 未指定時は application/json。form とは排他</t>
         </is>
       </c>
     </row>
@@ -4888,17 +4887,17 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>--url-interval SEC</t>
+          <t>--url-body-form DATA</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>1 以上の整数</t>
+          <t>key=value&amp;...</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>(なし)</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
@@ -4913,10 +4912,14 @@
       </c>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>リトライ間隔 (秒)</t>
-        </is>
-      </c>
-      <c r="H36" s="15" t="n"/>
+          <t>リクエストボディに form データを設定する</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t>Content-Type 未指定時は application/x-www-form-urlencoded。json とは排他</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -4926,22 +4929,22 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>--url-insecure</t>
+          <t>--url-timeout SEC</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>フラグ</t>
+          <t>1 以上の整数</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="F37" s="14" t="inlineStr">
@@ -4951,49 +4954,77 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>TLS 証明書検証を無効化する (curl -k)</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="n"/>
+          <t>期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>HTTP / healthcheck 診断の 1 回あたりの最大秒数にも使う</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>■ 起動維持後の対話操作</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="n"/>
-      <c r="C38" s="20" t="n"/>
-      <c r="D38" s="20" t="n"/>
-      <c r="E38" s="20" t="n"/>
-      <c r="F38" s="20" t="n"/>
-      <c r="G38" s="20" t="n"/>
-      <c r="H38" s="21" t="n"/>
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>URL 確認</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>--url-interval SEC</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>リトライ間隔 (秒)</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>対話操作</t>
+          <t>URL 確認</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>--keep-container-mode MODE</t>
+          <t>--url-insecure</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>bash / http / logs</t>
+          <t>フラグ</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>(なし)</t>
+          <t>false</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
@@ -5003,56 +5034,24 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>起動後に残したコンテナで対話操作を行う</t>
-        </is>
-      </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>--verify-startup と --keep-container を暗黙に有効化。対象複数時は番号選択</t>
-        </is>
-      </c>
+          <t>TLS 証明書検証を無効化する (curl -k)</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>対話操作</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>--jboss-context-root ROOT</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>コンテキストルートのパス</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>(WFLYUT0021 ログから検出)</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>http モードで使うコンテキストルート</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="inlineStr">
-        <is>
-          <t>--keep-container-mode http と併用必須。URL 全体は指定不可</t>
-        </is>
-      </c>
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>■ 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="21" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -5062,17 +5061,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>--jboss-http-port PORT</t>
+          <t>--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>1〜65535</t>
+          <t>bash / http / logs</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>(WFLYUT0006 ログから検出。既定 8080)</t>
+          <t>(なし)</t>
         </is>
       </c>
       <c r="E41" s="14" t="inlineStr">
@@ -5087,48 +5086,76 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>http モードで使うコンテナ側 HTTP ポート</t>
+          <t>起動後に残したコンテナで対話操作を行う</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>--keep-container-mode http と併用必須。公開ポートがあれば自動変換</t>
+          <t>--verify-startup と --keep-container を暗黙に有効化。対象複数時は番号選択</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>■ 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n"/>
-      <c r="C42" s="20" t="n"/>
-      <c r="D42" s="20" t="n"/>
-      <c r="E42" s="20" t="n"/>
-      <c r="F42" s="20" t="n"/>
-      <c r="G42" s="20" t="n"/>
-      <c r="H42" s="21" t="n"/>
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>対話操作</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>--jboss-context-root ROOT</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>コンテキストルートのパス</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>(WFLYUT0021 ログから検出)</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>http モードで使うコンテキストルート</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>--keep-container-mode http と併用必須。URL 全体は指定不可</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>情報表示</t>
+          <t>対話操作</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>--env-list-limit N|all</t>
+          <t>--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>1 以上の整数または all</t>
+          <t>1〜65535</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>(WFLYUT0006 ログから検出。既定 8080)</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
@@ -5143,56 +5170,28 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>環境変数一覧の表示件数 (コンテナごと)</t>
+          <t>http モードで使うコンテナ側 HTTP ポート</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>コンテナ起動を伴う場合のみ有効</t>
+          <t>--keep-container-mode http と併用必須。公開ポートがあれば自動変換</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>情報表示</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>--env-list-file FILE</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>ファイルパス</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
-        <is>
-          <t>(なし)</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="G44" s="15" t="inlineStr">
-        <is>
-          <t>環境変数一覧をファイルにも出力する</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="inlineStr">
-        <is>
-          <t>画面表示は継続</t>
-        </is>
-      </c>
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>■ 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="20" t="n"/>
+      <c r="F44" s="20" t="n"/>
+      <c r="G44" s="20" t="n"/>
+      <c r="H44" s="21" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
@@ -5202,7 +5201,7 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>--directory-tree-depth N|all</t>
+          <t>--env-list-limit N|all</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
@@ -5227,12 +5226,12 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
+          <t>環境変数一覧の表示件数 (コンテナごと)</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>JBoss デプロイ構造にも同じ深さを適用</t>
+          <t>コンテナ起動を伴う場合のみ有効</t>
         </is>
       </c>
     </row>
@@ -5244,17 +5243,17 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>--directory-file-limit N|all</t>
+          <t>--env-list-file FILE</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>1 以上の整数または all</t>
+          <t>ファイルパス</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>(ファイル非表示)</t>
+          <t>(なし)</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
@@ -5269,12 +5268,12 @@
       </c>
       <c r="G46" s="15" t="inlineStr">
         <is>
-          <t>通常ファイルの表示を有効化する</t>
+          <t>環境変数一覧をファイルにも出力する</t>
         </is>
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>N 件超過時は拡張子別件数を表示。all は常に全ファイル名</t>
+          <t>画面表示は継続</t>
         </is>
       </c>
     </row>
@@ -5286,22 +5285,22 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>--deployment-dir-env NAME</t>
+          <t>--directory-tree-depth N|all</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>環境変数名</t>
+          <t>1 以上の整数または all</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>(なし)</t>
+          <t>all</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>可 (繰り返し / カンマ区切り)</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
@@ -5311,215 +5310,243 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>ディレクトリパスを値に持つ環境変数</t>
+          <t>コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>その配下を JBoss デプロイ構造と併せて階層表示</t>
+          <t>JBoss デプロイ構造にも同じ深さを適用</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>レポート</t>
+          <t>情報表示</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>--report-dir DIR</t>
+          <t>--directory-file-limit N|all</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>ディレクトリパス</t>
+          <t>1 以上の整数または all</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
+          <t>(ファイル非表示)</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>通常ファイルの表示を有効化する</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>N 件超過時は拡張子別件数を表示。all は常に全ファイル名</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>情報表示</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>環境変数名</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
           <t>(なし)</t>
         </is>
       </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>可 (繰り返し / カンマ区切り)</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G48" s="15" t="inlineStr">
-        <is>
-          <t>全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存する</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="inlineStr">
-        <is>
-          <t>[1] ビルド結果 / [2] 環境変数 / [3] ツリー / [4] JBoss デプロイ構造 / [5] JVM パラメータ / [6] OpenTelemetry / [7] サービス別ログ (失敗時) を保存。画面の制限にかかわらず全量</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>■ オプション指定不要の自動表示 (起動確認を伴う実行のみ)</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n"/>
-      <c r="C49" s="20" t="n"/>
-      <c r="D49" s="20" t="n"/>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="20" t="n"/>
-      <c r="G49" s="20" t="n"/>
-      <c r="H49" s="21" t="n"/>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>ディレクトリパスを値に持つ環境変数</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>その配下を JBoss デプロイ構造と併せて階層表示</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
         <is>
+          <t>レポート</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>(なし)</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存する</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>[1] ビルド結果 / [2] 環境変数 / [3] ツリー / [4] JBoss デプロイ構造 / [5] JVM パラメータ / [6] OpenTelemetry / [7] サービス別ログ (失敗時) を保存。画面の制限にかかわらず全量</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>■ オプション指定不要の自動表示 (起動確認を伴う実行のみ)</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
+      <c r="H51" s="21" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
           <t>情報表示</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>(オプション不要)</t>
         </is>
       </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="C52" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>常に表示</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="F52" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G50" s="15" t="inlineStr">
+      <c r="G52" s="15" t="inlineStr">
         <is>
           <t>コンテナ内の Java プロセスを /proc から検出し、JVM パラメータを分類表示する</t>
         </is>
       </c>
-      <c r="H50" s="15" t="inlineStr">
+      <c r="H52" s="15" t="inlineStr">
         <is>
           <t>ヒープ・メモリ / GC / Java エージェント / OpenTelemetry / JBoss / システムプロパティ / クラスパス・モジュール / その他 / 起動対象への引数。JAVA_OPTS・JAVA_TOOL_OPTIONS 等の環境変数経由の指定も別枠で表示</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>情報表示</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>(オプション不要)</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>常に表示</t>
         </is>
       </c>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="E53" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="14" t="inlineStr">
+      <c r="F53" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>OpenTelemetry の環境変数と JVM パラメータを 1 つの一覧にまとめて表示する</t>
         </is>
       </c>
-      <c r="H51" s="14" t="inlineStr">
+      <c r="H53" s="14" t="inlineStr">
         <is>
           <t>OTEL_ 接頭辞の標準環境変数 / AWS_XRAY_* 等の関連環境変数 / -Dotel.* と OpenTelemetry の -javaagent / 主要設定の未設定検出。Java 非実行のコンテナでも環境変数側を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
-        <is>
-          <t>■ 終了時のクリーンアップ</t>
-        </is>
-      </c>
-      <c r="B52" s="20" t="n"/>
-      <c r="C52" s="20" t="n"/>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="20" t="n"/>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="20" t="n"/>
-      <c r="H52" s="21" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="22" t="inlineStr">
-        <is>
-          <t>クリーンアップ</t>
-        </is>
-      </c>
-      <c r="B53" s="22" t="inlineStr">
-        <is>
-          <t>--cleanup-all-docker-data</t>
-        </is>
-      </c>
-      <c r="C53" s="22" t="inlineStr">
-        <is>
-          <t>フラグ</t>
-        </is>
-      </c>
-      <c r="D53" s="22" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E53" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="22" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="G53" s="22" t="inlineStr">
-        <is>
-          <t>終了時に Docker context の全データを削除する</t>
-        </is>
-      </c>
-      <c r="H53" s="22" t="inlineStr">
-        <is>
-          <t>確認フレーズ『DELETE ALL DOCKER DATA』の入力が必須。--keep-container とは排他。取り扱い注意</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>■ その他</t>
+          <t>■ 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B54" s="20" t="n"/>
@@ -5531,55 +5558,111 @@
       <c r="H54" s="21" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="inlineStr">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>クリーンアップ</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>フラグ</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="22" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr">
+        <is>
+          <t>終了時に Docker context の全データを削除する</t>
+        </is>
+      </c>
+      <c r="H55" s="22" t="inlineStr">
+        <is>
+          <t>確認フレーズ『DELETE ALL DOCKER DATA』の入力が必須。--keep-container とは排他。取り扱い注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>■ その他</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="n"/>
+      <c r="C56" s="20" t="n"/>
+      <c r="D56" s="20" t="n"/>
+      <c r="E56" s="20" t="n"/>
+      <c r="F56" s="20" t="n"/>
+      <c r="G56" s="20" t="n"/>
+      <c r="H56" s="21" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>ヘルプ</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>-h, --help</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>フラグ</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E55" s="14" t="inlineStr">
+      <c r="E57" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="F57" s="14" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
+      <c r="G57" s="14" t="inlineStr">
         <is>
           <t>ヘルプを表示して exit 0</t>
         </is>
       </c>
-      <c r="H55" s="14" t="n"/>
+      <c r="H57" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H55"/>
+  <autoFilter ref="A2:H57"/>
   <mergeCells count="10">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A51:H51"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7335,7 +7418,7 @@
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>全量レポート保存 → Docker 全体クリーンアップ (任意) → compose down → 一時ファイル削除</t>
+          <t>全量レポート保存 (失敗時はログ本文の直前に compose stop で SIGTERM 送出 → 終了ログを取得) → Docker 全体クリーンアップ (任意) → compose down → 一時ファイル削除</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
@@ -8111,7 +8194,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
@@ -9390,7 +9472,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">75 件</t>
+          <t xml:space="preserve">80 件</t>
         </is>
       </c>
     </row>
@@ -4474,108 +4474,248 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="19.5" customHeight="1">
+    <row r="75" ht="33.0" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E75" s="7"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="76" ht="33.0" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E76" s="7"/>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="77" ht="33.0" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E77" s="7"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="78" ht="33.0" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
-        </is>
-      </c>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E78" s="7"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="79" ht="33.0" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E79" s="7"/>
       <c r="F79" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="19.5" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.9 その他</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-h, --help</t>
+        </is>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="33.0" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="33.0" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="33.0" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="33.0" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F79"/>
+  <autoFilter ref="A4:F84"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -6015,71 +6155,119 @@
       </c>
     </row>
     <row r="79" ht="19.5" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">タイミング</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="148.5" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-usage-report 指定時に使用量を測定 (増減の基準にする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="132.0" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="148.5" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ローカルイメージ確認の直後</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID が変わっていれば、タグを失った旧世代イメージを削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-    </row>
-    <row r="80" ht="33.0" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+    </row>
+    <row r="84" ht="33.0" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">状況</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの扱い</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="66.0" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
+    <row r="85" ht="66.0" customHeight="1">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">通常</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down で停止・削除</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="82.5" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
+    <row r="86" ht="82.5" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--keep-container / --keep-container-mode 指定</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="99.0" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="87" ht="99.0" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="99.0" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
+    <row r="88" ht="99.0" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--suppress-removed-logs 指定</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down / compose stop の出力を抑制</t>
         </is>
@@ -6097,7 +6285,7 @@
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A83:E83"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8068,7 +8256,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="33.0" customHeight="1">
+    <row r="47" ht="82.5" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -8076,32 +8264,101 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">15-2</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディスクを増やさずに --no-cache の検証を回す
+旧世代イメージの回収は既定で有効。ビルドキャッシュは 10GB まで残して削除し、
+実行前からの増減を表示する</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --no-cache --verify-startup \
+    --disk-usage-report --prune-build-cache-keep 10GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="33.0" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15-3</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">使用量の増減だけを先に測る (削除は行わない)</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --no-cache --disk-usage-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="33.0" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15-4</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世代を比較したいので旧イメージを残す (調査用)</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --no-cache --no-reclaim-old-image</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="33.0" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_push.sh 経由での呼び出し (同じ処理)</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_push.sh --build-only --verify-startup --log-dir ./logs</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="115.5" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="51" ht="115.5" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">デプロイ結果ファイルと Java 例外解析 (Excel + テキスト) をまとめて保存
 (reports/build_and_verify_&lt;日時&gt;.txt、
@@ -8109,7 +8366,7 @@
 reports/build_and_verify_&lt;日時&gt;_java_exceptions.txt が出力される)</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -8117,23 +8374,23 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="66.0" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="52" ht="66.0" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-2</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析の Excel / テキストを任意のパスへ出力する</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -8142,30 +8399,30 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="33.0" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
+    <row r="53" ht="33.0" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-3</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析を行わない (ログ量を抑えたい場合)</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-deploy-exception-analysis</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D50"/>
+  <autoFilter ref="A4:D53"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -345,17 +345,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">22 件</t>
+          <t xml:space="preserve">26 件</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 件</t>
+          <t xml:space="preserve">32 件</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">80 件</t>
+          <t xml:space="preserve">84 件</t>
         </is>
       </c>
     </row>
@@ -389,7 +389,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 件</t>
+          <t xml:space="preserve">10 件</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" ht="33.0" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 ビルドと出力</t>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--container-name NAME</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">任意の文字列</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">--repository の値</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -1032,11 +1032,11 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json の name</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない (5.7 参照)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="33.0" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 ビルドと出力</t>
@@ -1044,17 +1044,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--output FILE</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1064,196 +1064,208 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition の出力先</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19.5" customHeight="1">
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="33.0" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 実行制御・ログ</t>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--dry-run</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (無制限)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="33.0" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-build-watchdog</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド/ログイン/タグ付け/プッシュ/ファイル出力を行わず、実行内容のみ表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.3 実行制御・ログ</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--build-only</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルドのみ実行 (build_and_verify.sh へ委譲)。ECR 関連処理は行わない</t>
+          <t xml:space="preserve">上記の監視をすべて行わない。監視が有効な間は BUILDKIT_PROGRESS=tty を plain へ切り替えるため、tty 形式を使いたい場合に指定する</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 実行制御・ログ</t>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--log-dir DIR</t>
+          <t xml:space="preserve">--container-name NAME</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E18" s="7"/>
+          <t xml:space="preserve">任意の文字列</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--repository の値</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力を DIR/build_and_push_&lt;日時&gt;.log にも保存。ディレクトリは自動作成</t>
+          <t xml:space="preserve">imagedefinition.json の name</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--output FILE</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition.json</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition の出力先</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.3 実行制御・ログ</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--dry-run</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="33.0" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.4 ビルド前後の一時ファイル</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
-        </is>
-      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E20" s="7"/>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前にコピーし、終了後 (成功・失敗を問わず) 自動削除</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="49.5" customHeight="1">
+          <t xml:space="preserve">ビルド/ログイン/タグ付け/プッシュ/ファイル出力を行わず、実行内容のみ表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.3 実行制御・ログ</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-param NAME</t>
+          <t xml:space="preserve">--build-only</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SSM パラメータ名</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストアから取得 (--with-decryption)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="49.5" customHeight="1">
+          <t xml:space="preserve">ビルドのみ実行 (build_and_verify.sh へ委譲)。ECR 関連処理は行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.3 実行制御・ログ</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password VALUE</t>
+          <t xml:space="preserve">--log-dir DIR</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パスワード文字列</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1264,124 +1276,240 @@
       <c r="E22" s="7"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="49.5" customHeight="1">
+          <t xml:space="preserve">画面出力を DIR/build_and_push_&lt;日時&gt;.log にも保存。ディレクトリは自動作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19.5" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.3 実行制御・ログ</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
     <row r="24" ht="33.0" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 スイッチバック</t>
+          <t xml:space="preserve">4.4 ビルド前後の一時ファイル</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--switchback-shell PATH</t>
+          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シェルスクリプトのパス</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
-        </is>
-      </c>
-      <c r="E24" s="7"/>
+          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">別チーム提供のスイッチバック用シェル (source で読み込む)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="19.5" customHeight="1">
+          <t xml:space="preserve">ビルド前にコピーし、終了後 (成功・失敗を問わず) 自動削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="49.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 スイッチバック</t>
+          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--auto-switchback</t>
+          <t xml:space="preserve">--jboss-password-param NAME</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">SSM パラメータ名</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR 権限が無い場合に自動でスイッチバックして継続</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="19.5" customHeight="1">
+          <t xml:space="preserve">パラメータストアから取得 (--with-decryption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="49.5" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 スイッチバック</t>
+          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--warn-only</t>
+          <t xml:space="preserve">--jboss-password VALUE</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">既定</t>
+          <t xml:space="preserve">パスワード文字列</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="49.5" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+        </is>
+      </c>
+      <c r="E27" s="7"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="33.0" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--switchback-shell PATH</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">シェルスクリプトのパス</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
+        </is>
+      </c>
+      <c r="E28" s="7"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">別チーム提供のスイッチバック用シェル (source で読み込む)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--auto-switchback</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E29" s="7"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECR 権限が無い場合に自動でスイッチバックして継続</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--warn-only</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定</t>
+        </is>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ECR 権限が無い場合に警告して終了</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F26"/>
+  <autoFilter ref="A4:F30"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -1905,7 +2033,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CI ログには plain が読みやすい</t>
+          <t xml:space="preserve">CI ログには plain が読みやすい。ビルド監視が有効な間は tty を plain へ切り替える</t>
         </is>
       </c>
     </row>
@@ -1941,99 +2069,111 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="19.5" customHeight="1">
+    <row r="20" ht="33.0" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 出力・実行制御</t>
+          <t xml:space="preserve">5.2 buildx ビルド関連 (このスクリプト固有)</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--container-name NAME</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">任意の文字列</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">--repository の値</t>
-        </is>
-      </c>
-      <c r="E20" s="7"/>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json の name</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33.0" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 出力・実行制御</t>
+          <t xml:space="preserve">5.2 buildx ビルド関連 (このスクリプト固有)</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--output FILE</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json</t>
-        </is>
-      </c>
-      <c r="E21" s="7"/>
+          <t xml:space="preserve">300</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition の出力先</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="19.5" customHeight="1">
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="33.0" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 出力・実行制御</t>
+          <t xml:space="preserve">5.2 buildx ビルド関連 (このスクリプト固有)</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--log-dir DIR</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E22" s="7"/>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (無制限)</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力を DIR/buildx_build_and_push_&lt;日時&gt;.log にも保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19.5" customHeight="1">
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="33.0" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 出力・実行制御</t>
+          <t xml:space="preserve">5.2 buildx ビルド関連 (このスクリプト固有)</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--dry-run</t>
+          <t xml:space="preserve">--no-build-watchdog</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2046,10 +2186,14 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E23" s="7"/>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド/ログイン/タグ付け/プッシュ/ファイル出力を行わずプレビュー</t>
+          <t xml:space="preserve">上記の監視をすべて行わない</t>
         </is>
       </c>
     </row>
@@ -2061,72 +2205,68 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
+          <t xml:space="preserve">--container-name NAME</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">任意の文字列</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--repository の値</t>
         </is>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="33.0" customHeight="1">
+          <t xml:space="preserve">imagedefinition.json の name</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4 ビルド前後の一時ファイル</t>
+          <t xml:space="preserve">5.3 出力・実行制御</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
+          <t xml:space="preserve">--output FILE</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition.json</t>
+        </is>
+      </c>
+      <c r="E25" s="7"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前にコピーし、終了後に自動削除</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="49.5" customHeight="1">
+          <t xml:space="preserve">imagedefinition の出力先</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">5.3 出力・実行制御</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-param NAME</t>
+          <t xml:space="preserve">--log-dir DIR</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SSM パラメータ名</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2137,180 +2277,296 @@
       <c r="E26" s="7"/>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストアから取得 (--with-decryption)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="49.5" customHeight="1">
+          <t xml:space="preserve">画面出力を DIR/buildx_build_and_push_&lt;日時&gt;.log にも保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19.5" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">5.3 出力・実行制御</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password VALUE</t>
+          <t xml:space="preserve">--dry-run</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パスワード文字列</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="49.5" customHeight="1">
+          <t xml:space="preserve">ビルド/ログイン/タグ付け/プッシュ/ファイル出力を行わずプレビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">5.3 出力・実行制御</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="49.5" customHeight="1">
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="33.0" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.4 ビルド前後の一時ファイル</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前にコピーし、終了後に自動削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="49.5" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">シークレット id</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jboss_master_password</t>
-        </is>
-      </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--secret id=... の id。Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="33.0" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.6 スイッチバック</t>
-        </is>
-      </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--switchback-shell PATH</t>
+          <t xml:space="preserve">--jboss-password-param NAME</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シェルスクリプトのパス</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
+          <t xml:space="preserve">SSM パラメータ名</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">スイッチバック用シェル (source で読み込む)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="19.5" customHeight="1">
+          <t xml:space="preserve">パラメータストアから取得 (--with-decryption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="49.5" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 スイッチバック</t>
+          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--auto-switchback</t>
+          <t xml:space="preserve">--jboss-password VALUE</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">パスワード文字列</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR 権限が無い場合に自動でスイッチバックして継続</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="19.5" customHeight="1">
+          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="49.5" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 スイッチバック</t>
+          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--warn-only</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">受け渡しに使う環境変数名</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="49.5" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">シークレット id</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jboss_master_password</t>
+        </is>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--secret id=... の id。Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="33.0" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--switchback-shell PATH</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">シェルスクリプトのパス</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
+        </is>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スイッチバック用シェル (source で読み込む)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--auto-switchback</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECR 権限が無い場合に自動でスイッチバックして継続</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--warn-only</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定</t>
+        </is>
+      </c>
+      <c r="E36" s="7"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ECR 権限が無い場合に警告して終了</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F32"/>
+  <autoFilter ref="A4:F36"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -2518,7 +2774,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19.5" customHeight="1">
+    <row r="9" ht="33.0" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
@@ -2526,27 +2782,27 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--dry-run</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド/起動/URL 呼び出し/ファイル操作を行わずプレビュー</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
@@ -2558,171 +2814,187 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="33.0" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--build-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (無制限)</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="33.0" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-build-watchdog</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の監視をすべて行わない。監視が有効な間は BUILDKIT_PROGRESS=tty を plain へ切り替えるため、tty 形式を使いたい場合に指定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--dry-run</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド/起動/URL 呼び出し/ファイル操作を行わずプレビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="33.0" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">可</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド前にコピーし、終了後に自動削除。コピー先に同名ファイルがあれば強制上書きし、終了時に上書き前のファイルへ復元</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--copy-file-no-overwrite</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--copy-file のコピー先に同名ファイルがあれば上書きせず中止 (exit 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="49.5" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-param NAME</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SSM パラメータ名</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">パラメータストアから取得。このとき AWS 認証が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="49.5" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password VALUE</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">パスワード文字列</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="49.5" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
-        </is>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="49.5" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">シークレット id</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jboss_master_password</t>
-        </is>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
@@ -2734,135 +3006,135 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--region REGION</t>
+          <t xml:space="preserve">--jboss-password-param NAME</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS リージョン名</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
+          <t xml:space="preserve">SSM パラメータ名</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="33.0" customHeight="1">
+          <t xml:space="preserve">パラメータストアから取得。このとき AWS 認証が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="49.5" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-jboss-password</t>
+          <t xml:space="preserve">--jboss-password VALUE</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
+          <t xml:space="preserve">パスワード文字列</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="33.0" customHeight="1">
+          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="49.5" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-mask</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="33.0" customHeight="1">
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="49.5" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">シークレット id</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="33.0" customHeight="1">
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="49.5" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">AWS リージョン名</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
         </is>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
@@ -2874,23 +3146,23 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--verify-jboss-password</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
         </is>
       </c>
     </row>
@@ -2902,119 +3174,119 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--jboss-password-mask</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="33.0" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
     <row r="24" ht="33.0" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-verify-cwagent</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証を行わない</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="25" ht="33.0" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="26" ht="33.0" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3024,13 +3296,13 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -3042,12 +3314,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">列挙</t>
+          <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -3058,7 +3330,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3342,7 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-report</t>
+          <t xml:space="preserve">--no-verify-cwagent</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3080,13 +3352,13 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
+          <t xml:space="preserve">検証を行わない</t>
         </is>
       </c>
     </row>
@@ -3098,23 +3370,23 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-delivery-report</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達レポートを行わない (既定)</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -3126,23 +3398,23 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -3154,23 +3426,23 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">列挙</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
@@ -3182,23 +3454,23 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
         </is>
       </c>
     </row>
@@ -3210,23 +3482,23 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--no-cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">送達レポートを行わない (既定)</t>
         </is>
       </c>
     </row>
@@ -3238,23 +3510,23 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-required</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -3266,23 +3538,23 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -3294,151 +3566,135 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="37" ht="33.0" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-startup</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1〜65535</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+        </is>
+      </c>
+      <c r="E37" s="7"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
     <row r="38" ht="33.0" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-required</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(対象全体)</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E38" s="7"/>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
         </is>
       </c>
     </row>
     <row r="39" ht="33.0" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">拡張正規表現</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E39" s="7"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="33.0" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--no-cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E40" s="7"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
         </is>
       </c>
     </row>
@@ -3450,27 +3706,27 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--verify-startup</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
         </is>
       </c>
     </row>
@@ -3482,27 +3738,27 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -3514,27 +3770,27 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-healthy</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">拡張正規表現</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3802,7 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -3556,7 +3812,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -3566,7 +3822,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -3578,27 +3834,27 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--allow-service-exit NAME</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -3610,27 +3866,27 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -3642,27 +3898,27 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--wait-healthy</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
         </is>
       </c>
     </row>
@@ -3674,27 +3930,27 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -3706,27 +3962,27 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--allow-service-exit NAME</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
         </is>
       </c>
     </row>
@@ -3738,139 +3994,155 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--suppress-startup-logs</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="33.0" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="33.0" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="33.0" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="33.0" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E51" s="7"/>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E52" s="7"/>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="E53" s="7"/>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIME タイプ</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="E54" s="7"/>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -3882,12 +4154,12 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSON 文字列</t>
+          <t xml:space="preserve">URL</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -3898,7 +4170,7 @@
       <c r="E55" s="7"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -3910,23 +4182,23 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">key=value&amp;...</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -3938,23 +4210,23 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP メソッド</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -3966,23 +4238,23 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">MIME タイプ</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E58" s="7"/>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -3994,40 +4266,40 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">JSON 文字列</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E59" s="7"/>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
         </is>
       </c>
     </row>
     <row r="60" ht="19.5" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
+          <t xml:space="preserve">key=value&amp;...</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -4038,75 +4310,75 @@
       <c r="E60" s="7"/>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="19.5" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E61" s="7"/>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="33.0" customHeight="1">
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -4122,191 +4394,175 @@
       <c r="E63" s="7"/>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="33.0" customHeight="1">
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="19.5" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E64" s="7"/>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="19.5" customHeight="1">
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="33.0" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">コンテキストルートのパス</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出)</t>
+        </is>
+      </c>
+      <c r="E65" s="7"/>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="66" ht="33.0" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E66" s="7"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
         </is>
       </c>
     </row>
     <row r="67" ht="33.0" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E67" s="7"/>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="33.0" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-file FILE</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="33.0" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir DIR</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
@@ -4314,7 +4570,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel とテキストも同じディレクトリへ追加出力</t>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
         </is>
       </c>
     </row>
@@ -4326,17 +4582,17 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -4346,7 +4602,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
@@ -4358,17 +4614,17 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -4378,7 +4634,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
         </is>
       </c>
     </row>
@@ -4390,27 +4646,27 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
         </is>
       </c>
     </row>
@@ -4422,17 +4678,17 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--report-dir DIR</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -4442,103 +4698,115 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel とテキストも同じディレクトリへ追加出力</t>
         </is>
       </c>
     </row>
     <row r="74" ht="33.0" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E74" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="75" ht="33.0" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E75" s="7"/>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="19.5" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E76" s="7"/>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
     <row r="77" ht="33.0" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -4551,38 +4819,42 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E77" s="7"/>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
         </is>
       </c>
     </row>
     <row r="78" ht="33.0" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -4594,115 +4866,147 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="19.5" customHeight="1">
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="33.0" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E80" s="7"/>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="81" ht="33.0" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E81" s="7"/>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="82" ht="33.0" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E82" s="7"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="83" ht="33.0" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
-        </is>
-      </c>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E83" s="7"/>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C84" s="3"/>
@@ -4710,12 +5014,92 @@
       <c r="E84" s="7"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="33.0" customHeight="1">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="33.0" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="33.0" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="33.0" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F84"/>
+  <autoFilter ref="A4:F88"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -5134,7 +5518,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="33.0" customHeight="1">
+    <row r="22" ht="99.0" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -5147,7 +5531,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">docker compose -f &lt;file&gt; build [--no-cache] [service]</t>
+          <t xml:space="preserve">docker compose -f &lt;file&gt; build [--no-cache] [service] を監視プロセス付きで実行 (進捗表示・停滞検知・上限時間での中断。5.7 参照)。開始前に data root の空き容量を確認</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -5800,7 +6184,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="49.5" customHeight="1">
+    <row r="56" ht="115.5" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
@@ -5813,7 +6197,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">docker buildx build --load -t &lt;local-image&gt; -f &lt;dockerfile&gt; [オプション] &lt;context&gt;</t>
+          <t xml:space="preserve">docker buildx build --load -t &lt;local-image&gt; -f &lt;dockerfile&gt; [オプション] &lt;context&gt; を監視プロセス付きで実行 (進捗表示・停滞検知・上限時間での中断。6.8 参照)。開始前に data root の空き容量を確認</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -6178,7 +6562,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="132.0" customHeight="1">
+    <row r="81" ht="165.0" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド前</t>
@@ -6186,88 +6570,100 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">data root の空き容量を確認し、5 GiB 未満なら警告する (5.2-2 参照)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="132.0" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">世代交代の判定に使う現在のローカルイメージ ID を控える</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="148.5" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
+    <row r="83" ht="148.5" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">ローカルイメージ確認の直後</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ID が変わっていれば、タグを失った旧世代イメージを削除する</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="19.5" customHeight="1">
-      <c r="A83" s="8" t="inlineStr">
+    <row r="84" ht="19.5" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.5 後始末フェーズの詳細》</t>
         </is>
       </c>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-    </row>
-    <row r="84" ht="33.0" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+    </row>
+    <row r="85" ht="33.0" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">状況</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナの扱い</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="66.0" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
+    <row r="86" ht="66.0" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">通常</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down で停止・削除</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="82.5" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
+    <row r="87" ht="82.5" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--keep-container / --keep-container-mode 指定</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="99.0" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
         </is>
       </c>
     </row>
     <row r="88" ht="99.0" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="99.0" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--suppress-removed-logs 指定</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down / compose stop の出力を抑制</t>
         </is>
@@ -6285,7 +6681,7 @@
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A84:E84"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6368,7 +6764,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="49.5" customHeight="1">
+    <row r="6" ht="66.0" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_push.sh</t>
@@ -6386,7 +6782,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS 未認証、Docker デーモン未接続、ECR 権限なし、スイッチバック失敗、SSM 取得失敗、コピー失敗、ビルド失敗、ローカルイメージ未検出、ログイン失敗、タグ付け失敗、push 失敗、出力書き込み失敗、ログディレクトリ作成失敗、必須コマンド不足</t>
+          <t xml:space="preserve">AWS 未認証、Docker デーモン未接続、ECR 権限なし、スイッチバック失敗、SSM 取得失敗、コピー失敗、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、ログイン失敗、タグ付け失敗、push 失敗、出力書き込み失敗、ログディレクトリ作成失敗、必須コマンド不足</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6804,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、--account-id/--registry 未指定、リポジトリ名・タグ接頭辞の形式違反、JBoss オプションの排他違反、--copy-file の書式不正</t>
+          <t xml:space="preserve">不明なオプション、値の欠落、ビルド監視の各値が 0 未満か非数値、--account-id/--registry 未指定、リポジトリ名・タグ接頭辞の形式違反、JBoss オプションの排他違反、--copy-file の書式不正</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6830,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="49.5" customHeight="1">
+    <row r="9" ht="66.0" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
@@ -6452,7 +6848,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS 未認証、buildx 不在、Docker デーモン未接続、ECR 権限なし、スイッチバック失敗、SSM 取得失敗、コピー失敗、Dockerfile / コンテキスト不在、ビルド失敗、ローカルイメージ未検出、ログイン失敗、タグ付け失敗、push 失敗、出力書き込み失敗、ログディレクトリ作成失敗</t>
+          <t xml:space="preserve">AWS 未認証、buildx 不在、Docker デーモン未接続、ECR 権限なし、スイッチバック失敗、SSM 取得失敗、コピー失敗、Dockerfile / コンテキスト不在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、ログイン失敗、タグ付け失敗、push 失敗、出力書き込み失敗、ログディレクトリ作成失敗</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6870,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、--account-id/--registry 未指定、複数 platform 指定、--progress の不正値、リポジトリ名・タグ接頭辞の形式違反、JBoss オプションの排他違反、--jboss-secret-id が空、--copy-file の書式不正</t>
+          <t xml:space="preserve">不明なオプション、値の欠落、ビルド監視の各値が 0 未満か非数値、--account-id/--registry 未指定、複数 platform 指定、--progress の不正値、リポジトリ名・タグ接頭辞の形式違反、JBoss オプションの排他違反、--jboss-secret-id が空、--copy-file の書式不正</t>
         </is>
       </c>
     </row>
@@ -6518,11 +6914,11 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="82.5" customHeight="1">
+          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="99.0" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -6540,7 +6936,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満、--keep-container-mode の不正値、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
+          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
         </is>
       </c>
     </row>
@@ -6752,7 +7148,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="19.5" customHeight="1">
+    <row r="10" ht="33.0" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_push.sh</t>
@@ -6760,16 +7156,24 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TZ</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力</t>
-        </is>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+          <t xml:space="preserve">入力</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用。ビルド監視が有効な間は tty を plain へ切り替える</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -6779,7 +7183,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+          <t xml:space="preserve">TZ</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -6798,7 +7202,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -6812,56 +7216,40 @@
     <row r="13" ht="19.5" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">buildx_build_and_push.sh</t>
+          <t xml:space="preserve">build_and_push.sh</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_ACCOUNT_ID</t>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--account-id</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">レジストリ URL の組み立て</t>
-        </is>
-      </c>
+          <t xml:space="preserve">出力</t>
+        </is>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">buildx_build_and_push.sh</t>
+          <t xml:space="preserve">build_and_push.sh</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">未指定時は ap-northeast-1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">出力</t>
+        </is>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
@@ -6871,7 +7259,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR_REGISTRY</t>
+          <t xml:space="preserve">AWS_ACCOUNT_ID</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -6881,12 +7269,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--registry</t>
+          <t xml:space="preserve">--account-id</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">レジストリ URL の直接指定</t>
+          <t xml:space="preserve">レジストリ URL の組み立て</t>
         </is>
       </c>
     </row>
@@ -6898,7 +7286,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWITCHBACK_SHELL</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -6908,12 +7296,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--switchback-shell</t>
+          <t xml:space="preserve">--region</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">スイッチバック用シェルのパス</t>
+          <t xml:space="preserve">未指定時は ap-northeast-1</t>
         </is>
       </c>
     </row>
@@ -6925,7 +7313,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
+          <t xml:space="preserve">ECR_REGISTRY</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -6935,16 +7323,16 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env</t>
+          <t xml:space="preserve">--registry</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前 export した値をそのまま使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="33.0" customHeight="1">
+          <t xml:space="preserve">レジストリ URL の直接指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
@@ -6952,7 +7340,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--secret ...,env=NAME で参照する変数</t>
+          <t xml:space="preserve">SWITCHBACK_SHELL</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -6962,12 +7350,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">--switchback-shell</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用者が事前に export しておく</t>
+          <t xml:space="preserve">スイッチバック用シェルのパス</t>
         </is>
       </c>
     </row>
@@ -6979,18 +7367,26 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TZ</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力</t>
-        </is>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" ht="19.5" customHeight="1">
+          <t xml:space="preserve">入力</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-password-env</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事前 export した値をそのまま使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="33.0" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
@@ -6998,62 +7394,62 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+          <t xml:space="preserve">--secret ...,env=NAME で参照する変数</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力</t>
-        </is>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+          <t xml:space="preserve">入力</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">利用者が事前に export しておく</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">build_and_verify.sh</t>
+          <t xml:space="preserve">buildx_build_and_push.sh</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
+          <t xml:space="preserve">TZ</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力</t>
+          <t xml:space="preserve">出力</t>
         </is>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">build_and_verify.sh</t>
+          <t xml:space="preserve">buildx_build_and_push.sh</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力</t>
+          <t xml:space="preserve">出力</t>
         </is>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
-        </is>
-      </c>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
@@ -7063,7 +7459,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -7074,7 +7470,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
+          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7482,7 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_COLOR</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -7097,7 +7493,7 @@
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">定義されていれば色分けを無効化</t>
+          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7505,7 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLICOLOR_FORCE</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -7120,7 +7516,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7528,7 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERM</t>
+          <t xml:space="preserve">NO_COLOR</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -7143,7 +7539,7 @@
       <c r="D26" s="3"/>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dumb の場合は色分けしない</t>
+          <t xml:space="preserve">定義されていれば色分けを無効化</t>
         </is>
       </c>
     </row>
@@ -7155,16 +7551,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TZ</t>
+          <t xml:space="preserve">CLICOLOR_FORCE</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力</t>
+          <t xml:space="preserve">入力</t>
         </is>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
@@ -7174,16 +7574,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">TERM</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力</t>
+          <t xml:space="preserve">入力</t>
         </is>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dumb の場合は色分けしない</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
@@ -7193,7 +7597,7 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+          <t xml:space="preserve">TZ</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -7212,7 +7616,7 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -7223,8 +7627,46 @@
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出力</t>
+        </is>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出力</t>
+        </is>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E30"/>
+  <autoFilter ref="A4:E32"/>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
@@ -7493,7 +7935,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="33.0" customHeight="1">
+    <row r="14" ht="99.0" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_push.sh</t>
@@ -7506,12 +7948,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">レジストリを直接指定 (アカウント ID 不要)</t>
+          <t xml:space="preserve">レジストリを直接指定 (アカウント ID 不要)
+ビルドが exporting layers から進まないときの調査 (進捗 10 秒 / 停滞判定 60 秒)
+30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">./build_and_push.sh --registry 123456789012.dkr.ecr.ap-northeast-1.amazonaws.com</t>
+          <t xml:space="preserve">./build_and_push.sh --registry 123456789012.dkr.ecr.ap-northeast-1.amazonaws.com
+./build_and_push.sh --account-id 123456789012 \
+    --build-progress-interval 10 --build-stall-timeout 60
+./build_and_push.sh --account-id 123456789012 --build-timeout 1800</t>
         </is>
       </c>
     </row>
@@ -7678,7 +8125,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="49.5" customHeight="1">
+    <row r="22" ht="99.0" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
@@ -7691,14 +8138,19 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR 権限が無い場合に自動スイッチバック + ログ保存</t>
+          <t xml:space="preserve">ECR 権限が無い場合に自動スイッチバック + ログ保存
+ビルドが exporting layers から進まないときの調査 (進捗 10 秒 / 停滞判定 60 秒)
+30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./buildx_build_and_push.sh --account-id 123456789012 \
     --auto-switchback --switchback-shell /opt/team/switchback.sh \
-    --log-dir ./logs</t>
+    --log-dir ./logs
+./buildx_build_and_push.sh --account-id 123456789012 \
+    --build-progress-interval 10 --build-stall-timeout 60
+./buildx_build_and_push.sh --account-id 123456789012 --build-timeout 1800</t>
         </is>
       </c>
     </row>
@@ -8421,8 +8873,53 @@
         </is>
       </c>
     </row>
+    <row r="54" ht="66.0" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
+進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="33.0" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D53"/>
+  <autoFilter ref="A4:D55"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">84 件</t>
+          <t xml:space="preserve">87 件</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="33.0" customHeight="1">
+    <row r="73" ht="49.5" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel とテキストも同じディレクトリへ追加出力</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
         </is>
       </c>
     </row>
@@ -4833,68 +4833,76 @@
     <row r="78" ht="33.0" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E78" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="79" ht="33.0" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E79" s="7"/>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="19.5" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -4907,22 +4915,26 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E80" s="7"/>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
     <row r="81" ht="33.0" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -4938,7 +4950,7 @@
       <c r="E81" s="7"/>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -4950,23 +4962,23 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4990,7 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -4994,79 +5006,103 @@
       <c r="E83" s="7"/>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="19.5" customHeight="1">
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="33.0" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E84" s="7"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="85" ht="33.0" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E85" s="7"/>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="86" ht="33.0" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E86" s="7"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C87" s="3"/>
@@ -5074,7 +5110,7 @@
       <c r="E87" s="7"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5122,7 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">--directory-tree-depth N</t>
         </is>
       </c>
       <c r="C88" s="3"/>
@@ -5094,12 +5130,72 @@
       <c r="E88" s="7"/>
       <c r="F88" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="33.0" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="33.0" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="33.0" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F88"/>
+  <autoFilter ref="A4:F91"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -6918,7 +7014,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="99.0" customHeight="1">
+    <row r="13" ht="115.5" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -6936,7 +7032,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
+          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
         </is>
       </c>
     </row>
@@ -8873,7 +8969,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="66.0" customHeight="1">
+    <row r="54" ht="99.0" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -8881,45 +8977,118 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">17-4</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
+既定で毎回実行される。--report-dir があれば
+reports/build_and_verify_&lt;日時&gt;_readonly_filesystem.xlsx / .txt も出力される</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --compose-service app --startup-service app \
+    --report-dir ./reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="66.0" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-5</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel / テキストを任意のパスへ出力する</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --compose-service app --startup-service app \
+    --readonly-analysis-excel ./reports/readonly.xlsx \
+    --readonly-analysis-text ./reports/readonly.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="33.0" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-6</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステムの分析を行わない</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-readonly-analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="66.0" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
 進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="33.0" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="58" ht="33.0" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D55"/>
+  <autoFilter ref="A4:D58"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">87 件</t>
+          <t xml:space="preserve">93 件</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--no-pull-images</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
         </is>
       </c>
     </row>
@@ -4026,17 +4026,17 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">0 以上の整数</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4058,27 +4058,27 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -4090,27 +4090,27 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--up-retry N</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4122,195 +4122,219 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-up-retry</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="33.0" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="33.0" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-startup-logs</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="33.0" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="33.0" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="33.0" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="33.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E55" s="7"/>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E56" s="7"/>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="E57" s="7"/>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B58" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIME タイプ</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="E58" s="7"/>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E59" s="7"/>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key=value&amp;...</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E60" s="7"/>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
         </is>
       </c>
     </row>
@@ -4322,23 +4346,23 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">URL</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E61" s="7"/>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -4350,23 +4374,23 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -4378,327 +4402,303 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">HTTP メソッド</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E63" s="7"/>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
     <row r="64" ht="19.5" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">MIME タイプ</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="33.0" customHeight="1">
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="19.5" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">JSON 文字列</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E65" s="7"/>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="19.5" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">key=value&amp;...</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="19.5" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="33.0" customHeight="1">
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E68" s="7"/>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">リトライ間隔</t>
         </is>
       </c>
     </row>
     <row r="69" ht="19.5" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E69" s="7"/>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="19.5" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="33.0" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="E70" s="7"/>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="71" ht="33.0" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出)</t>
+        </is>
+      </c>
+      <c r="E71" s="7"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="19.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="33.0" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1〜65535</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E72" s="7"/>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="49.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="33.0" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E73" s="7"/>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
         </is>
       </c>
     </row>
@@ -4710,91 +4710,91 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="19.5" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-file FILE</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="33.0" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="33.0" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
@@ -4806,17 +4806,17 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -4826,11 +4826,11 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="33.0" customHeight="1">
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="19.5" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -4838,159 +4838,167 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="49.5" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="33.0" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="33.0" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="19.5" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="81" ht="33.0" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E81" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="19.5" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E82" s="7"/>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
     <row r="83" ht="33.0" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -5003,55 +5011,63 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E83" s="7"/>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
         </is>
       </c>
     </row>
     <row r="84" ht="33.0" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E84" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="85" ht="33.0" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -5059,22 +5075,26 @@
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E85" s="7"/>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -5087,115 +5107,287 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E86" s="7"/>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="19.5" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="33.0" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E87" s="7"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
     <row r="88" ht="33.0" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E88" s="7"/>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="89" ht="33.0" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E89" s="7"/>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="90" ht="33.0" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
-        </is>
-      </c>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E90" s="7"/>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="91" ht="33.0" customHeight="1">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E91" s="7"/>
       <c r="F91" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="33.0" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E92" s="7"/>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.9 その他</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-h, --help</t>
+        </is>
+      </c>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="33.0" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="33.0" customHeight="1">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="33.0" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="33.0" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F91"/>
+  <autoFilter ref="A4:F97"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -8969,7 +9161,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="99.0" customHeight="1">
+    <row r="54" ht="165.0" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -8984,7 +9176,9 @@
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
 既定で毎回実行される。--report-dir があれば
-reports/build_and_verify_&lt;日時&gt;_readonly_filesystem.xlsx / .txt も出力される</t>
+reports/build_and_verify_&lt;日時&gt;_readonly_filesystem.xlsx / .txt も出力される
+Dockerfile のビルド時に書くだけのディレクトリは「ビルド時のみ」として
+対象から外し、entrypoint.sh などが起動のたびに書く場所を「要対応」に挙げる</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -345,17 +345,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">26 件</t>
+          <t xml:space="preserve">31 件</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">32 件</t>
+          <t xml:space="preserve">36 件</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">93 件</t>
+          <t xml:space="preserve">98 件</t>
         </is>
       </c>
     </row>
@@ -389,7 +389,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 件</t>
+          <t xml:space="preserve">12 件</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 件</t>
+          <t xml:space="preserve">12 件</t>
         </is>
       </c>
     </row>
@@ -1508,8 +1508,156 @@
         </is>
       </c>
     </row>
+    <row r="31" ht="33.0" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-dir DIR</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリのパス</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="33.0" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英数字と . _ -</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacerts</t>
+        </is>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名、Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="33.0" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tar のパス</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一時ファイル</t>
+        </is>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="33.0" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+        </is>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="33.0" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">glob パターン</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*.crt と *.pem</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F30"/>
+  <autoFilter ref="A4:F35"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -2565,8 +2713,128 @@
         </is>
       </c>
     </row>
+    <row r="37" ht="33.0" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-dir DIR</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリのパス</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめて --secret で渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="33.0" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英数字と . _ -</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacerts</t>
+        </is>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">シークレット id。Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="33.0" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tar のパス</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一時ファイル</t>
+        </is>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="33.0" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">glob パターン</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*.crt と *.pem</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F36"/>
+  <autoFilter ref="A4:F40"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -3141,140 +3409,148 @@
     <row r="21" ht="33.0" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-jboss-password</t>
+          <t xml:space="preserve">--cacert-dir DIR</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
+          <t xml:space="preserve">ディレクトリのパス</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E21" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
+          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
         </is>
       </c>
     </row>
     <row r="22" ht="33.0" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-mask</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">英数字と . _ -</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="23" ht="33.0" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">tar のパス</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">一時ファイル</t>
         </is>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
         </is>
       </c>
     </row>
     <row r="24" ht="33.0" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
         </is>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
         </is>
       </c>
     </row>
     <row r="25" ht="33.0" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">glob パターン</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
-        </is>
-      </c>
-      <c r="E25" s="7"/>
+          <t xml:space="preserve">*.crt と *.pem</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
@@ -3286,35 +3562,35 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--verify-jboss-password</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="33.0" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-password-mask</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -3322,83 +3598,83 @@
           <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto</t>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="33.0" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-verify-cwagent</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証を行わない</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
     <row r="29" ht="33.0" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="30" ht="33.0" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3408,41 +3684,41 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="31" ht="33.0" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">列挙</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3730,7 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-report</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3462,15 +3738,15 @@
           <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3758,7 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-delivery-report</t>
+          <t xml:space="preserve">--no-verify-cwagent</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -3498,7 +3774,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達レポートを行わない (既定)</t>
+          <t xml:space="preserve">検証を行わない</t>
         </is>
       </c>
     </row>
@@ -3510,23 +3786,23 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -3538,23 +3814,23 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -3566,23 +3842,23 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">列挙</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
@@ -3594,23 +3870,23 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3898,7 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-required</t>
+          <t xml:space="preserve">--no-cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3632,13 +3908,13 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
+          <t xml:space="preserve">送達レポートを行わない (既定)</t>
         </is>
       </c>
     </row>
@@ -3650,23 +3926,23 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -3678,183 +3954,163 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="33.0" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-startup</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
+        </is>
+      </c>
+      <c r="E41" s="7"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="42" ht="33.0" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+        </is>
+      </c>
+      <c r="E42" s="7"/>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
     <row r="43" ht="33.0" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-required</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">拡張正規表現</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E43" s="7"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
         </is>
       </c>
     </row>
     <row r="44" ht="33.0" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E44" s="7"/>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="33.0" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--no-cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E45" s="7"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
         </is>
       </c>
     </row>
@@ -3866,27 +4122,27 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--verify-startup</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
         </is>
       </c>
     </row>
@@ -3898,27 +4154,27 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-healthy</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -3930,17 +4186,17 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">拡張正規表現</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -3950,7 +4206,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -3962,27 +4218,27 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--allow-service-exit NAME</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -3994,27 +4250,27 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-pull-images</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -4026,17 +4282,17 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -4046,7 +4302,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -4058,27 +4314,27 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--wait-healthy</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
         </is>
       </c>
     </row>
@@ -4090,17 +4346,17 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -4110,7 +4366,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4122,27 +4378,27 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-up-retry</t>
+          <t xml:space="preserve">--allow-service-exit NAME</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
+          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
         </is>
       </c>
     </row>
@@ -4154,27 +4410,27 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--no-pull-images</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
         </is>
       </c>
     </row>
@@ -4186,27 +4442,27 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4218,17 +4474,17 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">0 以上の整数</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
@@ -4238,7 +4494,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -4250,27 +4506,27 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--up-retry N</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4538,7 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--no-up-retry</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4302,7 +4558,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
         </is>
       </c>
     </row>
@@ -4314,167 +4570,187 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="33.0" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-startup-logs</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="33.0" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="33.0" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="33.0" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="33.0" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E61" s="7"/>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E62" s="7"/>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="E63" s="7"/>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="19.5" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIME タイプ</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="E64" s="7"/>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="19.5" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E65" s="7"/>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4762,12 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">key=value&amp;...</t>
+          <t xml:space="preserve">URL</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -4502,7 +4778,7 @@
       <c r="E66" s="7"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -4514,23 +4790,23 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -4542,23 +4818,23 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP メソッド</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -4570,40 +4846,40 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">MIME タイプ</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E69" s="7"/>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
     <row r="70" ht="19.5" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
+          <t xml:space="preserve">JSON 文字列</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -4614,140 +4890,136 @@
       <c r="E70" s="7"/>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="19.5" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">key=value&amp;...</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="19.5" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="33.0" customHeight="1">
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="19.5" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E73" s="7"/>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E74" s="7"/>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
         </is>
       </c>
     </row>
     <row r="75" ht="19.5" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">bash / http / logs</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -4755,174 +5027,158 @@
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="E75" s="7"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="76" ht="33.0" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出)</t>
+        </is>
+      </c>
+      <c r="E76" s="7"/>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="77" ht="33.0" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1〜65535</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E77" s="7"/>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="33.0" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E78" s="7"/>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="33.0" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="19.5" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="19.5" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-file FILE</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="49.5" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir DIR</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="33.0" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
         </is>
       </c>
     </row>
@@ -4934,123 +5190,123 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="33.0" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="49.5" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="19.5" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B82" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="33.0" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="33.0" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B84" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
         </is>
       </c>
     </row>
@@ -5062,211 +5318,231 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="33.0" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="19.5" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="33.0" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E87" s="7"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
     <row r="88" ht="33.0" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E88" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
         </is>
       </c>
     </row>
     <row r="89" ht="33.0" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E89" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="90" ht="33.0" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="19.5" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-readonly-analysis</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E90" s="7"/>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="33.0" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E91" s="7"/>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
     <row r="92" ht="33.0" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -5282,112 +5558,252 @@
       <c r="E92" s="7"/>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="19.5" customHeight="1">
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="33.0" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E93" s="7"/>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="94" ht="33.0" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E94" s="7"/>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="95" ht="33.0" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E95" s="7"/>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="96" ht="33.0" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
-        </is>
-      </c>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E96" s="7"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="97" ht="33.0" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E97" s="7"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.9 その他</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-h, --help</t>
+        </is>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="33.0" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="33.0" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="33.0" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="33.0" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F97"/>
+  <autoFilter ref="A4:F102"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -7444,43 +7860,51 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle-env</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事前 export 済みなら、その tar のパスをそのまま使用 (--cacert-dir 未指定時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="33.0" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_push.sh</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">入力</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用。ビルド監視が有効な間は tty を plain へ切り替える</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">build_and_push.sh</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TZ</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">出力</t>
-        </is>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -7490,7 +7914,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">TZ</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -7509,7 +7933,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -7528,7 +7952,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -7542,56 +7966,40 @@
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">buildx_build_and_push.sh</t>
+          <t xml:space="preserve">build_and_push.sh</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_ACCOUNT_ID</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--account-id</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">レジストリ URL の組み立て</t>
-        </is>
-      </c>
+          <t xml:space="preserve">出力</t>
+        </is>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">buildx_build_and_push.sh</t>
+          <t xml:space="preserve">build_and_push.sh</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
+          <t xml:space="preserve">&lt;--cacert-bundle-env の値&gt;</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">未指定時は ap-northeast-1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">出力</t>
+        </is>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -7601,7 +8009,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR_REGISTRY</t>
+          <t xml:space="preserve">AWS_ACCOUNT_ID</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -7611,12 +8019,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--registry</t>
+          <t xml:space="preserve">--account-id</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">レジストリ URL の直接指定</t>
+          <t xml:space="preserve">レジストリ URL の組み立て</t>
         </is>
       </c>
     </row>
@@ -7628,7 +8036,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWITCHBACK_SHELL</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -7638,12 +8046,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--switchback-shell</t>
+          <t xml:space="preserve">--region</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">スイッチバック用シェルのパス</t>
+          <t xml:space="preserve">未指定時は ap-northeast-1</t>
         </is>
       </c>
     </row>
@@ -7655,7 +8063,7 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
+          <t xml:space="preserve">ECR_REGISTRY</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -7665,16 +8073,16 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env</t>
+          <t xml:space="preserve">--registry</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前 export した値をそのまま使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="33.0" customHeight="1">
+          <t xml:space="preserve">レジストリ URL の直接指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
@@ -7682,7 +8090,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--secret ...,env=NAME で参照する変数</t>
+          <t xml:space="preserve">SWITCHBACK_SHELL</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -7692,12 +8100,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">--switchback-shell</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用者が事前に export しておく</t>
+          <t xml:space="preserve">スイッチバック用シェルのパス</t>
         </is>
       </c>
     </row>
@@ -7709,18 +8117,26 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TZ</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力</t>
-        </is>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" ht="19.5" customHeight="1">
+          <t xml:space="preserve">入力</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-password-env</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事前 export した値をそのまま使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="33.0" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
@@ -7728,62 +8144,62 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+          <t xml:space="preserve">--secret ...,env=NAME で参照する変数</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力</t>
-        </is>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+          <t xml:space="preserve">入力</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">利用者が事前に export しておく</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">build_and_verify.sh</t>
+          <t xml:space="preserve">buildx_build_and_push.sh</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
+          <t xml:space="preserve">TZ</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力</t>
+          <t xml:space="preserve">出力</t>
         </is>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
-        </is>
-      </c>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">build_and_verify.sh</t>
+          <t xml:space="preserve">buildx_build_and_push.sh</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力</t>
+          <t xml:space="preserve">出力</t>
         </is>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
-        </is>
-      </c>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
@@ -7793,7 +8209,7 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -7804,7 +8220,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
+          <t xml:space="preserve">--region の既定値 (パラメータストア参照時)</t>
         </is>
       </c>
     </row>
@@ -7816,7 +8232,7 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_COLOR</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -7827,7 +8243,7 @@
       <c r="D26" s="3"/>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">定義されていれば色分けを無効化</t>
+          <t xml:space="preserve">--jboss-password-env 単独指定時に使用</t>
         </is>
       </c>
     </row>
@@ -7839,7 +8255,7 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLICOLOR_FORCE</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -7850,7 +8266,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+          <t xml:space="preserve">--cacert-dir 未指定時、事前 export 済みならその tar のパスをそのまま使用</t>
         </is>
       </c>
     </row>
@@ -7862,7 +8278,7 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERM</t>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -7873,7 +8289,7 @@
       <c r="D28" s="3"/>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dumb の場合は色分けしない</t>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用</t>
         </is>
       </c>
     </row>
@@ -7885,16 +8301,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TZ</t>
+          <t xml:space="preserve">NO_COLOR</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力</t>
+          <t xml:space="preserve">入力</t>
         </is>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定義されていれば色分けを無効化</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
@@ -7904,16 +8324,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+          <t xml:space="preserve">CLICOLOR_FORCE</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力</t>
+          <t xml:space="preserve">入力</t>
         </is>
       </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以外なら、非 tty でも色分けを強制</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -7923,16 +8347,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+          <t xml:space="preserve">TERM</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">出力</t>
+          <t xml:space="preserve">入力</t>
         </is>
       </c>
       <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dumb の場合は色分けしない</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
@@ -7942,7 +8370,7 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">TZ</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -7953,8 +8381,84 @@
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出力</t>
+        </is>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出力</t>
+        </is>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出力</t>
+        </is>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;--cacert-bundle-env の値&gt;</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出力</t>
+        </is>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E32"/>
+  <autoFilter ref="A4:E36"/>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">98 件</t>
+          <t xml:space="preserve">105 件</t>
         </is>
       </c>
     </row>
@@ -5534,71 +5534,79 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="33.0" customHeight="1">
+    <row r="92" ht="49.5" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E92" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="93" ht="33.0" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">/ で始まるパス</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E93" s="7"/>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="33.0" customHeight="1">
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="19.5" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-undertow-probe</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5611,78 +5619,90 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E94" s="7"/>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
     <row r="95" ht="33.0" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E95" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="96" ht="33.0" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E96" s="7"/>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
         </is>
       </c>
     </row>
     <row r="97" ht="33.0" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -5695,115 +5715,319 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E97" s="7"/>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
         </is>
       </c>
     </row>
     <row r="98" ht="19.5" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="7"/>
+          <t xml:space="preserve">--no-undertow-analysis</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="99" ht="33.0" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E99" s="7"/>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
     <row r="100" ht="33.0" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E100" s="7"/>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="101" ht="33.0" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
-        </is>
-      </c>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E101" s="7"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="102" ht="33.0" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E102" s="7"/>
       <c r="F102" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="33.0" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E103" s="7"/>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="33.0" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E104" s="7"/>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.9 その他</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-h, --help</t>
+        </is>
+      </c>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="33.0" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="33.0" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="33.0" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="33.0" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F102"/>
+  <autoFilter ref="A4:F109"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">105 件</t>
+          <t xml:space="preserve">107 件</t>
         </is>
       </c>
     </row>
@@ -5761,68 +5761,76 @@
     <row r="99" ht="33.0" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="19.5" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E99" s="7"/>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="33.0" customHeight="1">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(オプション不要)</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E100" s="7"/>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="101" ht="33.0" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -5838,7 +5846,7 @@
       <c r="E101" s="7"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -5850,23 +5858,23 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E102" s="7"/>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -5878,23 +5886,23 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5914,7 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--prune-build-cache</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -5922,59 +5930,75 @@
       <c r="E104" s="7"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="19.5" customHeight="1">
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="33.0" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E105" s="7"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="106" ht="33.0" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E106" s="7"/>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="19.5" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C107" s="3"/>
@@ -5982,7 +6006,7 @@
       <c r="E107" s="7"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
@@ -5994,7 +6018,7 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--directory-tree-depth N</t>
         </is>
       </c>
       <c r="C108" s="3"/>
@@ -6002,7 +6026,7 @@
       <c r="E108" s="7"/>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6038,7 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">--directory-file-limit N</t>
         </is>
       </c>
       <c r="C109" s="3"/>
@@ -6022,12 +6046,52 @@
       <c r="E109" s="7"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="33.0" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="33.0" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F109"/>
+  <autoFilter ref="A4:F111"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">107 件</t>
+          <t xml:space="preserve">109 件</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--recreate-containers</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
         </is>
       </c>
     </row>
@@ -4634,27 +4634,27 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--no-recreate-containers</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--suppress-startup-logs</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
         </is>
       </c>
     </row>
@@ -4698,27 +4698,27 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
         </is>
       </c>
     </row>
@@ -4730,83 +4730,91 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="33.0" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="33.0" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E66" s="7"/>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E67" s="7"/>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -4818,23 +4826,23 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-method METHOD</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
+          <t xml:space="preserve">URL</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストメソッド</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -4846,23 +4854,23 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIME タイプ</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動)</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E69" s="7"/>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -4874,23 +4882,23 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">HTTP メソッド</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -4902,23 +4910,23 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">key=value&amp;...</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">MIME タイプ</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -4930,23 +4938,23 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">JSON 文字列</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
         </is>
       </c>
     </row>
@@ -4958,23 +4966,23 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">key=value&amp;...</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E73" s="7"/>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
         </is>
       </c>
     </row>
@@ -4986,83 +4994,83 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="75" ht="19.5" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="19.5" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="33.0" customHeight="1">
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="19.5" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -5070,23 +5078,23 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E77" s="7"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -5098,87 +5106,79 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="79" ht="33.0" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E79" s="7"/>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="19.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="33.0" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E80" s="7"/>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
         </is>
       </c>
     </row>
@@ -5190,219 +5190,219 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-file FILE</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="33.0" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">all</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="33.0" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
+    <row r="84" ht="33.0" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="19.5" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="85" ht="19.5" customHeight="1">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">可</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="49.5" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
+    <row r="86" ht="49.5" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--report-dir DIR</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="33.0" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
+    <row r="87" ht="33.0" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="33.0" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B86" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="19.5" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -5414,17 +5414,17 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
@@ -5434,11 +5434,11 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5446,17 +5446,17 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -5478,155 +5478,155 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="33.0" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="33.0" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="19.5" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="49.5" customHeight="1">
-      <c r="A92" s="11" t="inlineStr">
+    <row r="94" ht="49.5" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">可</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
+      <c r="F94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="33.0" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="19.5" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
@@ -5638,17 +5638,17 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -5658,11 +5658,11 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="33.0" customHeight="1">
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
+          <t xml:space="preserve">--no-undertow-probe</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
@@ -5702,59 +5702,59 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="33.0" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
+          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
         </is>
       </c>
     </row>
@@ -5766,17 +5766,17 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
+          <t xml:space="preserve">--no-undertow-analysis</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -5818,75 +5818,83 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="101" ht="33.0" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E101" s="7"/>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="33.0" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(オプション不要)</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E102" s="7"/>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="103" ht="33.0" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -5902,7 +5910,7 @@
       <c r="E103" s="7"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -5914,23 +5922,23 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E104" s="7"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -5942,23 +5950,23 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5978,7 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--prune-build-cache</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -5986,59 +5994,75 @@
       <c r="E106" s="7"/>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="19.5" customHeight="1">
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="33.0" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E107" s="7"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="108" ht="33.0" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E108" s="7"/>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="19.5" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C109" s="3"/>
@@ -6046,7 +6070,7 @@
       <c r="E109" s="7"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6082,7 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--directory-tree-depth N</t>
         </is>
       </c>
       <c r="C110" s="3"/>
@@ -6066,7 +6090,7 @@
       <c r="E110" s="7"/>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6102,7 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">--directory-file-limit N</t>
         </is>
       </c>
       <c r="C111" s="3"/>
@@ -6086,12 +6110,52 @@
       <c r="E111" s="7"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="33.0" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="33.0" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ディレクトリのみ表示</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F111"/>
+  <autoFilter ref="A4:F113"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">109 件</t>
+          <t xml:space="preserve">119 件</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="33.0" customHeight="1">
+    <row r="83" ht="19.5" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5254,17 +5254,17 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -5274,11 +5274,11 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5286,17 +5286,17 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -5306,11 +5306,11 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="19.5" customHeight="1">
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="33.0" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5318,31 +5318,31 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="49.5" customHeight="1">
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5350,17 +5350,17 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力</t>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -5414,91 +5414,91 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="33.0" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="49.5" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="33.0" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B90" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -5574,59 +5574,59 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="33.0" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="49.5" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
         </is>
       </c>
     </row>
@@ -5638,17 +5638,17 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -5658,11 +5658,11 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="19.5" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="33.0" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5670,91 +5670,91 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="19.5" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-readonly-analysis</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="33.0" customHeight="1">
-      <c r="A97" s="11" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="49.5" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="33.0" customHeight="1">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5766,17 +5766,17 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
+          <t xml:space="preserve">--no-undertow-probe</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="19.5" customHeight="1">
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="33.0" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -5882,19 +5882,19 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
         </is>
       </c>
     </row>
     <row r="103" ht="33.0" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -5907,122 +5907,138 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E103" s="7"/>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="33.0" customHeight="1">
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="19.5" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-undertow-analysis</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E104" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="105" ht="33.0" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="19.5" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E105" s="7"/>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="33.0" customHeight="1">
-      <c r="A106" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B106" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--prune-build-cache</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E106" s="7"/>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="107" ht="33.0" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -6034,115 +6050,147 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E108" s="7"/>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="19.5" customHeight="1">
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="33.0" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E109" s="7"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="110" ht="33.0" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E110" s="7"/>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="111" ht="33.0" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
-        </is>
-      </c>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E111" s="7"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="112" ht="33.0" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
-        </is>
-      </c>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E112" s="7"/>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="19.5" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C113" s="3"/>
@@ -6150,12 +6198,212 @@
       <c r="E113" s="7"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリのみ表示</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="33.0" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="33.0" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="7"/>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="33.0" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree</t>
+        </is>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="7"/>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="33.0" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="33.0" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="7"/>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="33.0" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="33.0" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="33.0" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="33.0" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="33.0" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F113"/>
+  <autoFilter ref="A4:F123"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -9569,7 +9817,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="49.5" customHeight="1">
+    <row r="35" ht="66.0" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -9582,148 +9830,195 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートとコンテナ内ツリーを保存
-(JVM パラメータと OpenTelemetry 設定も同じレポートへ保存される)</t>
+          <t xml:space="preserve">全量レポートを保存 (ツリーは画面・レポートとも既定では出さない)
+(JVM パラメータと OpenTelemetry 設定は指定不要で同じレポートへ保存される)</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup --report-dir ./reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="82.5" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11-2</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面にもレポートにもコンテナ内ツリーを出す
+--directory-tree-depth / --directory-file-limit を付けると画面表示は自動で有効になる</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
-    --report-dir ./reports --directory-tree-depth 3 --directory-file-limit 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="33.0" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+    --report-dir ./reports --directory-tree-report \
+    --directory-tree-depth 3 --directory-file-limit 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="33.0" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11-3</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面には出さず、全量レポートにだけツリーを残す</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --report-dir ./reports --directory-tree-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="33.0" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">デプロイ構造を環境変数から特定して表示</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">デプロイ構造を環境変数から特定して表示 (指定すると画面表示が有効になる)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --deployment-dir-env JBOSS_HOME,APP_DEPLOY_DIR</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="49.5" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="39" ht="49.5" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">認証情報を一時配置してビルド
 (コピー先に .npmrc があっても強制上書きし、終了時に元のファイルへ戻す)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --copy-file .npmrc:./app</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="33.0" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="40" ht="33.0" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">13-2</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コピー先の既存ファイルには一切触れず、あれば中止する</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --copy-file-no-overwrite --copy-file .npmrc:./app</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="33.0" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="41" ht="33.0" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストアのマスターパスワードを使ってビルド</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --jboss-password-param /j1/jboss/master-password</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="66.0" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="42" ht="66.0" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-2</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">マスターパスワードが実行時の値まで一致しているかを検証
 (standalone.xml と CredentialStore まで見るので起動確認と併用する)</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">export JBOSS_MASTER_PASSWORD='pa$w#o"r`d&amp;x'
 ./build_and_verify.sh --verify-startup --verify-jboss-password</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="49.5" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="43" ht="49.5" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-3</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストアから取得した値で検証し、平文は伏せる</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --jboss-password-param /j1/jboss/master-password \
@@ -9731,23 +10026,23 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="49.5" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="44" ht="49.5" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-4</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">既定以外のパスに設定ファイル・CredentialStore がある場合</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --verify-jboss-password \
     --jboss-config-file /opt/eap/standalone/configuration/standalone-full.xml \
@@ -9755,47 +10050,47 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="66.0" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="45" ht="66.0" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-5</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">cwagent の設定ファイルチェックとコンテナ内設定の照合を行う
 (compose.yml に cwagent があれば自動。送達レポートは既定では行わない)</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent,cloudwatch-logs-mock --startup-service app</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="66.0" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="46" ht="66.0" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-6</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">送達レポートまで行い、送達待ちを 3 分へ延ばして届かなければビルド失敗とする</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent,cloudwatch-logs-mock --startup-service app \
@@ -9804,24 +10099,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="66.0" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="47" ht="66.0" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-7</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実 CloudWatch Logs のロググループへ届いたかを aws logs で確認する
 (ロググループが無ければ設定ファイルの名前で作成してから確認する)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent --startup-service app \
@@ -9830,97 +10125,53 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="33.0" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="48" ht="33.0" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">検証後に Docker を完全クリーンアップ (確認フレーズ入力が必要)</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --cleanup-all-docker-data</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="82.5" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="49" ht="82.5" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15-2</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ディスクを増やさずに --no-cache の検証を回す
 旧世代イメージの回収は既定で有効。ビルドキャッシュは 10GB まで残して削除し、
 実行前からの増減を表示する</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --no-cache --verify-startup \
     --disk-usage-report --prune-build-cache-keep 10GB</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="33.0" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">build_and_verify.sh</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15-3</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">使用量の増減だけを先に測る (削除は行わない)</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">./build_and_verify.sh --no-cache --disk-usage-report</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="33.0" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">build_and_verify.sh</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15-4</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">世代を比較したいので旧イメージを残す (調査用)</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">./build_and_verify.sh --no-cache --no-reclaim-old-image</t>
-        </is>
-      </c>
-    </row>
     <row r="50" ht="33.0" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
@@ -9929,32 +10180,76 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">15-3</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">使用量の増減だけを先に測る (削除は行わない)</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --no-cache --disk-usage-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="33.0" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15-4</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世代を比較したいので旧イメージを残す (調査用)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --no-cache --no-reclaim-old-image</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="33.0" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_push.sh 経由での呼び出し (同じ処理)</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_push.sh --build-only --verify-startup --log-dir ./logs</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="115.5" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="53" ht="115.5" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">デプロイ結果ファイルと Java 例外解析 (Excel + テキスト) をまとめて保存
 (reports/build_and_verify_&lt;日時&gt;.txt、
@@ -9962,7 +10257,7 @@
 reports/build_and_verify_&lt;日時&gt;_java_exceptions.txt が出力される)</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -9970,23 +10265,23 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="66.0" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="54" ht="66.0" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-2</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析の Excel / テキストを任意のパスへ出力する</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -9995,40 +10290,40 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="33.0" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="55" ht="33.0" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-3</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析を行わない (ログ量を抑えたい場合)</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-deploy-exception-analysis</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="165.0" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
+    <row r="56" ht="165.0" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-4</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
 既定で毎回実行される。--report-dir があれば
@@ -10037,7 +10332,7 @@
 対象から外し、entrypoint.sh などが起動のたびに書く場所を「要対応」に挙げる</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -10045,23 +10340,23 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="66.0" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="57" ht="66.0" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-5</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel / テキストを任意のパスへ出力する</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -10070,75 +10365,75 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="33.0" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="58" ht="33.0" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-6</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの分析を行わない</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-readonly-analysis</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="66.0" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="59" ht="66.0" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
 進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="33.0" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="60" ht="33.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D58"/>
+  <autoFilter ref="A4:D60"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">119 件</t>
+          <t xml:space="preserve">124 件</t>
         </is>
       </c>
     </row>
@@ -5185,44 +5185,40 @@
     <row r="81" ht="33.0" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--keep-container-after-interaction</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E81" s="7"/>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
         </is>
       </c>
     </row>
     <row r="82" ht="19.5" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--usage-check-script PATH</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -5230,115 +5226,107 @@
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動解決)</t>
+        </is>
+      </c>
+      <c r="E82" s="7"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
         </is>
       </c>
     </row>
     <row r="83" ht="19.5" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-free-path DIR</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリ</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定の 7 か所)</t>
+        </is>
+      </c>
+      <c r="E83" s="7"/>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="33.0" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="19.5" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="19.5" customHeight="1">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-directory-tree</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-file FILE</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="33.0" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B85" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5338,7 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -5360,7 +5348,7 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -5370,11 +5358,11 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5382,17 +5370,17 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -5402,7 +5390,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -5414,91 +5402,91 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="33.0" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="33.0" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="49.5" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B90" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir DIR</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -5510,17 +5498,17 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -5530,7 +5518,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5530,12 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -5557,108 +5545,108 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="66.0" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="19.5" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析のテキストは --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="49.5" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="33.0" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] と Excel に残る)。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="A95" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="33.0" customHeight="1">
-      <c r="A95" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B95" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
         </is>
       </c>
     </row>
@@ -5670,91 +5658,91 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--report-dir 指定時は未指定でも自動出力。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="33.0" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="19.5" customHeight="1">
-      <c r="A97" s="11" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="49.5" customHeight="1">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -5766,17 +5754,17 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
@@ -5786,11 +5774,11 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="19.5" customHeight="1">
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="33.0" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5798,17 +5786,17 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
@@ -5818,7 +5806,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5830,199 +5818,199 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-readonly-analysis</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="49.5" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="33.0" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="33.0" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="E106" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="33.0" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="33.0" customHeight="1">
-      <c r="A103" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B103" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="19.5" customHeight="1">
-      <c r="A104" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B104" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="33.0" customHeight="1">
-      <c r="A105" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B105" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="19.5" customHeight="1">
-      <c r="A106" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B106" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="107" ht="33.0" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -6035,50 +6023,58 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E107" s="7"/>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
         </is>
       </c>
     </row>
     <row r="108" ht="33.0" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E108" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="33.0" customHeight="1">
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="19.5" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-undertow-analysis</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -6091,78 +6087,90 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E109" s="7"/>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="110" ht="33.0" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="19.5" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E110" s="7"/>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="33.0" customHeight="1">
-      <c r="A111" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E111" s="7"/>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="112" ht="33.0" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -6178,119 +6186,159 @@
       <c r="E112" s="7"/>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="19.5" customHeight="1">
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="33.0" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E113" s="7"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="114" ht="33.0" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E114" s="7"/>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="115" ht="33.0" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E115" s="7"/>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="116" ht="33.0" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
-        </is>
-      </c>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E116" s="7"/>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="117" ht="33.0" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E117" s="7"/>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="19.5" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C118" s="3"/>
@@ -6298,7 +6346,7 @@
       <c r="E118" s="7"/>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6358,7 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C119" s="3"/>
@@ -6318,7 +6366,7 @@
       <c r="E119" s="7"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6378,7 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C120" s="3"/>
@@ -6338,7 +6386,7 @@
       <c r="E120" s="7"/>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6398,7 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C121" s="3"/>
@@ -6358,7 +6406,7 @@
       <c r="E121" s="7"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6418,7 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C122" s="3"/>
@@ -6378,7 +6426,7 @@
       <c r="E122" s="7"/>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6438,7 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C123" s="3"/>
@@ -6398,12 +6446,112 @@
       <c r="E123" s="7"/>
       <c r="F123" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="33.0" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="33.0" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="33.0" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="33.0" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="7"/>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="33.0" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="7"/>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F123"/>
+  <autoFilter ref="A4:F128"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -7937,37 +8085,61 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="82.5" customHeight="1">
+    <row r="87" ht="165.0" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container / --keep-container-mode 指定</t>
+          <t xml:space="preserve">--keep-container-mode logs の対話操作をすべて終了し、終了コードが 0</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">compose down で削除したうえで、未使用リソースまで完全クリア (→ 5.4-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="82.5" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-container / --keep-container-mode 指定 (上記以外)</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="99.0" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
+    <row r="89" ht="82.5" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-container-after-interaction 指定</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">対話操作を終えても残す (従来の動作)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="99.0" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="99.0" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
+    <row r="91" ht="99.0" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--suppress-removed-logs 指定</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down / compose stop の出力を抑制</t>
         </is>
@@ -8200,7 +8372,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="82.5" customHeight="1">
+    <row r="12" ht="99.0" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -8218,7 +8390,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
+          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、対話操作の終了後の完全クリーンアップ失敗 (docker-usage-check.sh が見つからない・失敗した)、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8412,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
+          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--usage-check-script のパスを読み取れない、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
         </is>
       </c>
     </row>
@@ -10251,10 +10423,10 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイ結果ファイルと Java 例外解析 (Excel + テキスト) をまとめて保存
-(reports/build_and_verify_&lt;日時&gt;.txt、
-reports/build_and_verify_&lt;日時&gt;_java_exceptions.xlsx、
-reports/build_and_verify_&lt;日時&gt;_java_exceptions.txt が出力される)</t>
+          <t xml:space="preserve">デプロイ結果ファイルと Java 例外解析の Excel をまとめて保存
+(reports/build_and_verify_&lt;日時&gt;.txt … [10] に例外解析の全文、
+reports/build_and_verify_&lt;日時&gt;_java_exceptions.xlsx が出力される。
+画面には解析結果を出さない ← 既定)</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -10278,10 +10450,36 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外解析の Excel / テキストを任意のパスへ出力する</t>
+          <t xml:space="preserve">解析結果を画面でも読む (既定は非表示)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --compose-service app --startup-service app \
+    --report-dir ./reports \
+    --deploy-exception-display</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="66.0" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-3</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Java 例外解析の Excel / テキストを任意のパスへ出力する
+(テキストは --deploy-exception-text を指定したときだけ出力される)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -10290,40 +10488,40 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="33.0" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="56" ht="33.0" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-3</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Java 例外解析を行わない (ログ量を抑えたい場合)</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-4</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Java 例外解析を行わない (解析処理ごと省く)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-deploy-exception-analysis</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="165.0" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="57" ht="165.0" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-4</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-5</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
 既定で毎回実行される。--report-dir があれば
@@ -10332,7 +10530,7 @@
 対象から外し、entrypoint.sh などが起動のたびに書く場所を「要対応」に挙げる</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -10340,23 +10538,23 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="66.0" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="58" ht="66.0" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-5</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-6</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel / テキストを任意のパスへ出力する</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -10365,75 +10563,75 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="33.0" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="59" ht="33.0" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-6</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-7</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの分析を行わない</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-readonly-analysis</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="66.0" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
+    <row r="60" ht="66.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
 進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="33.0" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="61" ht="33.0" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D60"/>
+  <autoFilter ref="A4:D61"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">124 件</t>
+          <t xml:space="preserve">131 件</t>
         </is>
       </c>
     </row>
@@ -3266,431 +3266,451 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="49.5" customHeight="1">
+    <row r="16" ht="33.0" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--verify-copy-artifact</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">auto (--copy-file 指定時のみ有効)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-file を指定していない実行でも取り込み検証を行う (→ 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="33.0" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-verify-copy-artifact</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">取り込み検証を行わない。--copy-artifact-path / --copy-artifact-search-dir / --copy-artifact-required とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="33.0" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-artifact-path PATH</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動探索)</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33.0" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-artifact-search-dir DIR</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="33.0" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-artifact-required</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コピーしたファイルがコンテナ内に見つからない場合もエラーとする (既定は警告のみ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="49.5" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--jboss-password-param NAME</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">SSM パラメータ名</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E21" s="7"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストアから取得。このとき AWS 認証が必要</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="49.5" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="22" ht="49.5" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--jboss-password VALUE</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パスワード文字列</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="49.5" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
-        </is>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="49.5" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">シークレット id</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jboss_master_password</t>
-        </is>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="49.5" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region REGION</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS リージョン名</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
-        </is>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="33.0" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cacert-dir DIR</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリのパス</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="33.0" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cacert-secret-id ID</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">英数字と . _ -</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="33.0" customHeight="1">
+          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="49.5" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle PATH</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパス</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">一時ファイル</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="33.0" customHeight="1">
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="49.5" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">シークレット id</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="33.0" customHeight="1">
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="49.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-glob PATTERN</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">glob パターン</t>
+          <t xml:space="preserve">AWS リージョン名</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">*.crt と *.pem</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
+        </is>
+      </c>
+      <c r="E25" s="7"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
     <row r="26" ht="33.0" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-jboss-password</t>
+          <t xml:space="preserve">--cacert-dir DIR</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
+          <t xml:space="preserve">ディレクトリのパス</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E26" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
+          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
         </is>
       </c>
     </row>
     <row r="27" ht="33.0" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-mask</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">英数字と . _ -</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="28" ht="33.0" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">tar のパス</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">一時ファイル</t>
         </is>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
         </is>
       </c>
     </row>
     <row r="29" ht="33.0" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
         </is>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
         </is>
       </c>
     </row>
     <row r="30" ht="33.0" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">glob パターン</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
-        </is>
-      </c>
-      <c r="E30" s="7"/>
+          <t xml:space="preserve">*.crt と *.pem</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
@@ -3702,35 +3722,35 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--verify-jboss-password</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="33.0" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--jboss-password-mask</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3738,83 +3758,83 @@
           <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto</t>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="33.0" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-verify-cwagent</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証を行わない</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
     <row r="34" ht="33.0" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="35" ht="33.0" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -3824,41 +3844,41 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="36" ht="33.0" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">列挙</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3890,7 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-report</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3878,15 +3898,15 @@
           <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3918,7 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-delivery-report</t>
+          <t xml:space="preserve">--no-verify-cwagent</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3914,7 +3934,7 @@
       <c r="E38" s="7"/>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達レポートを行わない (既定)</t>
+          <t xml:space="preserve">検証を行わない</t>
         </is>
       </c>
     </row>
@@ -3926,23 +3946,23 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -3954,23 +3974,23 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -3982,23 +4002,23 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">列挙</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
@@ -4010,23 +4030,23 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4058,7 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-required</t>
+          <t xml:space="preserve">--no-cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -4048,13 +4068,13 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
+          <t xml:space="preserve">送達レポートを行わない (既定)</t>
         </is>
       </c>
     </row>
@@ -4066,23 +4086,23 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -4094,183 +4114,163 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E45" s="7"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="33.0" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-startup</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
+        </is>
+      </c>
+      <c r="E46" s="7"/>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="47" ht="33.0" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+        </is>
+      </c>
+      <c r="E47" s="7"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
     <row r="48" ht="33.0" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-required</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">拡張正規表現</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E48" s="7"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
         </is>
       </c>
     </row>
     <row r="49" ht="33.0" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E49" s="7"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="33.0" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--no-cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E50" s="7"/>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
         </is>
       </c>
     </row>
@@ -4282,27 +4282,27 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--verify-startup</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
         </is>
       </c>
     </row>
@@ -4314,27 +4314,27 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-healthy</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4346,17 +4346,17 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">拡張正規表現</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -4378,27 +4378,27 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--allow-service-exit NAME</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -4410,27 +4410,27 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-pull-images</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -4442,17 +4442,17 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -4474,27 +4474,27 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--wait-healthy</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
         </is>
       </c>
     </row>
@@ -4506,17 +4506,17 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4538,27 +4538,27 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-up-retry</t>
+          <t xml:space="preserve">--allow-service-exit NAME</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
+          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
         </is>
       </c>
     </row>
@@ -4570,27 +4570,27 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--no-pull-images</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
         </is>
       </c>
     </row>
@@ -4602,27 +4602,27 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--recreate-containers</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4634,27 +4634,27 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-recreate-containers</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -4666,27 +4666,27 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--up-retry N</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4698,27 +4698,27 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--no-up-retry</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
         </is>
       </c>
     </row>
@@ -4730,27 +4730,27 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">compose up の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--recreate-containers</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
         </is>
       </c>
     </row>
@@ -4794,167 +4794,187 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-recreate-containers</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="33.0" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-startup-logs</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="33.0" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="33.0" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="33.0" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="33.0" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E68" s="7"/>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="19.5" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E69" s="7"/>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="19.5" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="E70" s="7"/>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="19.5" customHeight="1">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIME タイプ</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="E71" s="7"/>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="19.5" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E72" s="7"/>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
         </is>
       </c>
     </row>
@@ -4966,12 +4986,12 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">key=value&amp;...</t>
+          <t xml:space="preserve">URL</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -4982,7 +5002,7 @@
       <c r="E73" s="7"/>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -4994,23 +5014,23 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -5022,23 +5042,23 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP メソッド</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -5050,40 +5070,40 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">MIME タイプ</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
     <row r="77" ht="19.5" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
+          <t xml:space="preserve">JSON 文字列</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -5094,103 +5114,103 @@
       <c r="E77" s="7"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="19.5" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">key=value&amp;...</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="19.5" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="33.0" customHeight="1">
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="19.5" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="19.5" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-after-interaction</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -5206,7 +5226,7 @@
       <c r="E81" s="7"/>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
         </is>
       </c>
     </row>
@@ -5218,27 +5238,27 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--usage-check-script PATH</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動解決)</t>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="19.5" customHeight="1">
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="33.0" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -5246,99 +5266,91 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-free-path DIR</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定の 7 か所)</t>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="E83" s="7"/>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="84" ht="33.0" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E84" s="7"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="19.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="33.0" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E85" s="7"/>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="19.5" customHeight="1">
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="33.0" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--keep-container-after-interaction</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -5346,31 +5358,27 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E86" s="7"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
         </is>
       </c>
     </row>
     <row r="87" ht="19.5" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--remove-volumes</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -5383,26 +5391,22 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="E87" s="7"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
         </is>
       </c>
     </row>
     <row r="88" ht="33.0" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--keep-volumes</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -5410,83 +5414,71 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E88" s="7"/>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
         </is>
       </c>
     </row>
     <row r="89" ht="19.5" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--usage-check-script PATH</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(自動解決)</t>
+        </is>
+      </c>
+      <c r="E89" s="7"/>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="33.0" customHeight="1">
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="19.5" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--disk-free-path DIR</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">ディレクトリ</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(既定の 7 か所)</t>
+        </is>
+      </c>
+      <c r="E90" s="7"/>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5490,7 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -5508,7 +5500,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -5518,11 +5510,11 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="33.0" customHeight="1">
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5530,12 +5522,12 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--env-list-file FILE</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -5545,16 +5537,16 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="66.0" customHeight="1">
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="19.5" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5562,17 +5554,17 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -5582,11 +5574,11 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析のテキストは --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="49.5" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="19.5" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5594,7 +5586,7 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5602,9 +5594,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -5614,11 +5606,11 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] と Excel に残る)。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="19.5" customHeight="1">
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="33.0" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5626,7 +5618,7 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-display</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5634,9 +5626,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -5646,11 +5638,11 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="33.0" customHeight="1">
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5658,17 +5650,17 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -5678,7 +5670,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--report-dir 指定時は未指定でも自動出力。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
         </is>
       </c>
     </row>
@@ -5690,17 +5682,17 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -5710,11 +5702,11 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="33.0" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5722,17 +5714,17 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
@@ -5742,7 +5734,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -5754,91 +5746,91 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="66.0" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析のテキストは --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="49.5" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="33.0" customHeight="1">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="33.0" customHeight="1">
-      <c r="A101" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B101" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] と Excel に残る)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5842,7 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -5860,7 +5852,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -5870,11 +5862,11 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="49.5" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="33.0" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5882,12 +5874,12 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -5897,12 +5889,12 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--report-dir 指定時は未指定でも自動出力。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5914,17 +5906,17 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -5934,7 +5926,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -5946,17 +5938,17 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
@@ -5966,7 +5958,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -5978,17 +5970,17 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -5998,7 +5990,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6010,17 +6002,17 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
@@ -6030,7 +6022,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6042,17 +6034,17 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
@@ -6062,7 +6054,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6066,7 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
+          <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -6094,11 +6086,11 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="33.0" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="49.5" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6106,12 +6098,12 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -6121,112 +6113,120 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="33.0" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="19.5" customHeight="1">
-      <c r="A111" s="11" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="19.5" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E111" s="7" t="inlineStr">
+      <c r="E112" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="33.0" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
-        </is>
-      </c>
-      <c r="B112" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E112" s="7"/>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
     <row r="113" ht="33.0" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E113" s="7"/>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="114" ht="33.0" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -6239,22 +6239,26 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E114" s="7"/>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
         </is>
       </c>
     </row>
     <row r="115" ht="33.0" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -6267,218 +6271,290 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E115" s="7"/>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="33.0" customHeight="1">
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="19.5" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-undertow-analysis</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E116" s="7"/>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="117" ht="33.0" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E117" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="118" ht="19.5" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="7"/>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="119" ht="33.0" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E119" s="7"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
     <row r="120" ht="33.0" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E120" s="7"/>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="121" ht="33.0" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
-        </is>
-      </c>
-      <c r="C121" s="3"/>
-      <c r="D121" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E121" s="7"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="122" ht="33.0" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C122" s="3"/>
-      <c r="D122" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E122" s="7"/>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="123" ht="33.0" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C123" s="3"/>
-      <c r="D123" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E123" s="7"/>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="124" ht="33.0" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C124" s="3"/>
-      <c r="D124" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E124" s="7"/>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="19.5" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C125" s="3"/>
@@ -6486,7 +6562,7 @@
       <c r="E125" s="7"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6574,7 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C126" s="3"/>
@@ -6506,7 +6582,7 @@
       <c r="E126" s="7"/>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6594,7 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C127" s="3"/>
@@ -6526,7 +6602,7 @@
       <c r="E127" s="7"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6614,7 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C128" s="3"/>
@@ -6546,12 +6622,152 @@
       <c r="E128" s="7"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="33.0" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="33.0" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="7"/>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="33.0" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="33.0" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="7"/>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="33.0" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="33.0" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="33.0" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F128"/>
+  <autoFilter ref="A4:F135"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -8073,7 +8289,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="66.0" customHeight="1">
+    <row r="86" ht="115.5" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">通常</t>
@@ -8081,11 +8297,11 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down で停止・削除</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="165.0" customHeight="1">
+          <t xml:space="preserve">compose down で停止・削除 (ボリュームは残す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="231.0" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--keep-container-mode logs の対話操作をすべて終了し、終了コードが 0</t>
@@ -8093,53 +8309,89 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down で削除したうえで、未使用リソースまで完全クリア (→ 5.4-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="82.5" customHeight="1">
+          <t xml:space="preserve">compose down --volumes でボリュームごと削除したうえで、未使用リソースまで完全クリア (→ 5.4-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="198.0" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">取り込み検証で「古い成果物を抱えたボリューム」を検出</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down --volumes でボリュームごと削除し、次回の実行で作り直させる (→ 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="148.5" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--remove-volumes 指定</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">この実行が行うすべての compose down へ --volumes を付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="115.5" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-volumes 指定</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記いずれの場合もボリュームを残す (従来の動作)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="82.5" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container / --keep-container-mode 指定 (上記以外)</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">残す (手動停止コマンドを案内)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="82.5" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
+    <row r="92" ht="82.5" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--keep-container-after-interaction 指定</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">対話操作を終えても残す (従来の動作)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="99.0" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
+    <row r="93" ht="99.0" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--cleanup-all-docker-data 指定</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認フレーズ入力後、Docker 全体を削除</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="99.0" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
+    <row r="94" ht="99.0" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--suppress-removed-logs 指定</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose down / compose stop の出力を抑制</t>
         </is>
@@ -8372,7 +8624,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="99.0" customHeight="1">
+    <row r="12" ht="115.5" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -8390,11 +8642,11 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、対話操作の終了後の完全クリーンアップ失敗 (docker-usage-check.sh が見つからない・失敗した)、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="115.5" customHeight="1">
+          <t xml:space="preserve">必須コマンド不足、AWS 未認証、SSM 取得失敗、コピー失敗、コピー先が通常ファイルでない、--copy-file-no-overwrite 指定時にコピー先へ同名ファイルが存在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、コンテナ起動失敗、起動確認失敗 (タイムアウト・失敗パターン検出・途中停止)、URL 応答確認失敗、対話操作失敗、対話操作の終了後の完全クリーンアップ失敗 (docker-usage-check.sh が見つからない・失敗した)、レポート保存失敗、Docker クリーンアップ未承認、--cwagent-required 指定時の cwagent 検証 NG、コピーしたファイルの取り込み検証 NG (コンテナ内の中身がコピー元と一致しない / --copy-artifact-required 指定時に未検出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="132.0" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -8412,7 +8664,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--usage-check-script のパスを読み取れない、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正</t>
+          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--usage-check-script のパスを読み取れない、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正、--copy-artifact-path / --copy-artifact-search-dir が絶対パスでない、--remove-volumes と --keep-volumes の同時指定</t>
         </is>
       </c>
     </row>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">131 件</t>
+          <t xml:space="preserve">136 件</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto (--copy-file 指定時のみ有効)</t>
+          <t xml:space="preserve">false (既定では照合しない)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-file を指定していない実行でも取り込み検証を行う (→ 5.13)</t>
+          <t xml:space="preserve">取り込み検証を行う (→ 5.13)</t>
         </is>
       </c>
     </row>
@@ -3314,9 +3314,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定と同じ)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する</t>
+          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)</t>
+          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コピーしたファイルがコンテナ内に見つからない場合もエラーとする (既定は警告のみ)</t>
+          <t xml:space="preserve">コピーしたファイルがコンテナ内に見つからない場合もエラーとする (既定は警告のみ)。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="49.5" customHeight="1">
+    <row r="101" ht="33.0" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] と Excel に残る)。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] に残る)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。--report-dir 指定時は未指定でも自動出力。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析と Excel 出力を行わない</t>
+          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6569,102 +6569,82 @@
     <row r="126" ht="33.0" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="7"/>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
+      <c r="F126" s="3"/>
     </row>
     <row r="127" ht="33.0" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="7"/>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
-        </is>
-      </c>
+      <c r="F127" s="3"/>
     </row>
     <row r="128" ht="33.0" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="7"/>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
-        </is>
-      </c>
+      <c r="F128" s="3"/>
     </row>
     <row r="129" ht="33.0" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="7"/>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
-        </is>
-      </c>
+      <c r="F129" s="3"/>
     </row>
     <row r="130" ht="33.0" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="7"/>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
-        </is>
-      </c>
+      <c r="F130" s="3"/>
     </row>
     <row r="131" ht="33.0" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
@@ -6674,7 +6654,7 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C131" s="3"/>
@@ -6682,7 +6662,7 @@
       <c r="E131" s="7"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6674,7 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C132" s="3"/>
@@ -6702,7 +6682,7 @@
       <c r="E132" s="7"/>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6694,7 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C133" s="3"/>
@@ -6722,7 +6702,7 @@
       <c r="E133" s="7"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6714,7 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C134" s="3"/>
@@ -6742,7 +6722,7 @@
       <c r="E134" s="7"/>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6734,7 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C135" s="3"/>
@@ -6762,12 +6742,112 @@
       <c r="E135" s="7"/>
       <c r="F135" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="33.0" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="33.0" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="33.0" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="33.0" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="7"/>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="33.0" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="7"/>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F135"/>
+  <autoFilter ref="A4:F140"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -10662,7 +10742,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="115.5" customHeight="1">
+    <row r="53" ht="99.0" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -10675,10 +10755,9 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイ結果ファイルと Java 例外解析の Excel をまとめて保存
-(reports/build_and_verify_&lt;日時&gt;.txt … [10] に例外解析の全文、
-reports/build_and_verify_&lt;日時&gt;_java_exceptions.xlsx が出力される。
-画面には解析結果を出さない ← 既定)</t>
+          <t xml:space="preserve">デプロイ結果ファイルへ Java 例外解析を残す
+(reports/build_and_verify_&lt;日時&gt;.txt … [10] に例外解析の全文。
+画面表示も Excel / テキストの出力も行わない ← 既定)</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">136 件</t>
+          <t xml:space="preserve">143 件</t>
         </is>
       </c>
     </row>
@@ -3018,27 +3018,27 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cache</t>
+          <t xml:space="preserve">--base-context DIR</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">キャッシュを破棄してビルド</t>
+          <t xml:space="preserve">サービス名に base を含むサービスの build.context を上書き (→ 5.1-2)</t>
         </is>
       </c>
     </row>
@@ -3050,17 +3050,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-progress-interval SEC</t>
+          <t xml:space="preserve">--base-dockerfile FILE</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数 (秒)</t>
+          <t xml:space="preserve">Dockerfile 名 / 相対パス</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3070,11 +3070,11 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ対象サービスの build.dockerfile を上書き。build.context からの相対パスとして解釈される (→ 5.1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
@@ -3082,17 +3082,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-stall-timeout SEC</t>
+          <t xml:space="preserve">--frontend-context DIR</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数 (秒)</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">300</t>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
+          <t xml:space="preserve">サービス名に frontend を含むサービスの build.context を上書き (→ 5.1-2)</t>
         </is>
       </c>
     </row>
@@ -3114,17 +3114,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-timeout SEC</t>
+          <t xml:space="preserve">--frontend-dockerfile FILE</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数 (秒)</t>
+          <t xml:space="preserve">Dockerfile 名 / 相対パス</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (無制限)</t>
+          <t xml:space="preserve">(compose の値)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -3134,11 +3134,11 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ対象サービスの build.dockerfile を上書き (→ 5.1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
@@ -3146,123 +3146,123 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-build-watchdog</t>
+          <t xml:space="preserve">--backend-context DIR</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(compose の値)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サービス名に backend を含むサービスの build.context を上書き (→ 5.1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="33.0" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--backend-dockerfile FILE</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dockerfile 名 / 相対パス</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(compose の値)</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ対象サービスの build.dockerfile を上書き (→ 5.1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cache</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上記の監視をすべて行わない。監視が有効な間は BUILDKIT_PROGRESS=tty を plain へ切り替えるため、tty 形式を使いたい場合に指定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">キャッシュを破棄してビルド</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66.0" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--dry-run</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド/起動/URL 呼び出し/ファイル操作を行わずプレビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="33.0" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--keep-service NAME</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前にコピーし、終了後に自動削除。コピー先に同名ファイルがあれば強制上書きし、終了時に上書き前のファイルへ復元</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--copy-file-no-overwrite</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可 (繰り返し / カンマ区切り)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-file のコピー先に同名ファイルがあれば上書きせず中止 (exit 1)</t>
+          <t xml:space="preserve">指定したサービスを --no-cache の対象から外し、後始末でイメージと名前付きボリュームを残す (→ 5.1-3)</t>
         </is>
       </c>
     </row>
@@ -3274,27 +3274,27 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-copy-artifact</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (既定では照合しない)</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取り込み検証を行う (→ 5.13)</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
@@ -3306,27 +3306,27 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-verify-copy-artifact</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定と同じ)</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取り込み検証を行わない。--copy-artifact-path / --copy-artifact-search-dir / --copy-artifact-required とは排他</t>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
@@ -3338,27 +3338,27 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-artifact-path PATH</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">0 (無制限)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する。指定すると取り込み検証を有効にする</t>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
         </is>
       </c>
     </row>
@@ -3370,221 +3370,241 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-artifact-search-dir DIR</t>
+          <t xml:space="preserve">--no-build-watchdog</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の監視をすべて行わない。監視が有効な間は BUILDKIT_PROGRESS=tty を plain へ切り替えるため、tty 形式を使いたい場合に指定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--dry-run</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド/起動/URL 呼び出し/ファイル操作を行わずプレビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33.0" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前にコピーし、終了後に自動削除。コピー先に同名ファイルがあれば強制上書きし、終了時に上書き前のファイルへ復元</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-file-no-overwrite</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-file のコピー先に同名ファイルがあれば上書きせず中止 (exit 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="33.0" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--verify-copy-artifact</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (既定では照合しない)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">取り込み検証を行う (→ 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="33.0" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-verify-copy-artifact</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定と同じ)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">取り込み検証を行わない。--copy-artifact-path / --copy-artifact-search-dir / --copy-artifact-required とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="33.0" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 ビルド関連</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-artifact-path PATH</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動探索)</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">可</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)。指定すると取り込み検証を有効にする</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="33.0" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1 ビルド関連</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--copy-artifact-required</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コピーしたファイルがコンテナ内に見つからない場合もエラーとする (既定は警告のみ)。指定すると取り込み検証を有効にする</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="49.5" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-param NAME</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SSM パラメータ名</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">パラメータストアから取得。このとき AWS 認証が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="49.5" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password VALUE</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">パスワード文字列</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="49.5" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
-        </is>
-      </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="49.5" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">シークレット id</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jboss_master_password</t>
-        </is>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="49.5" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region REGION</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS リージョン名</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
-        </is>
-      </c>
-      <c r="E25" s="7"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
+          <t xml:space="preserve">照合するコンテナ内パスを明示指定。シェルの無いコンテナでも docker cp で取り出して照合する。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
     <row r="26" ht="33.0" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-dir DIR</t>
+          <t xml:space="preserve">--copy-artifact-search-dir DIR</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリのパス</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -3594,331 +3614,339 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
+          <t xml:space="preserve">コンテナ内の探索起点を絞る (探索時間の短縮)。指定すると取り込み検証を有効にする</t>
         </is>
       </c>
     </row>
     <row r="27" ht="33.0" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.1 ビルド関連</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-secret-id ID</t>
+          <t xml:space="preserve">--copy-artifact-required</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">英数字と . _ -</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cacerts</t>
-        </is>
-      </c>
-      <c r="E27" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コピーしたファイルがコンテナ内に見つからない場合もエラーとする (既定は警告のみ)。指定すると取り込み検証を有効にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="49.5" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle PATH</t>
+          <t xml:space="preserve">--jboss-password-param NAME</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパス</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一時ファイル</t>
+          <t xml:space="preserve">SSM パラメータ名</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="33.0" customHeight="1">
+          <t xml:space="preserve">パラメータストアから取得。このとき AWS 認証が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="49.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+          <t xml:space="preserve">--jboss-password VALUE</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+          <t xml:space="preserve">パスワード文字列</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="33.0" customHeight="1">
+          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="49.5" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-glob PATTERN</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">glob パターン</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">*.crt と *.pem</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+        </is>
+      </c>
+      <c r="E30" s="7"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="33.0" customHeight="1">
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="49.5" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-jboss-password</t>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">シークレット id</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jboss_master_password</t>
         </is>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="33.0" customHeight="1">
+          <t xml:space="preserve">compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="49.5" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-mask</t>
+          <t xml:space="preserve">--region REGION</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">AWS リージョン名</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ap-northeast-1 (env AWS_REGION)</t>
         </is>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
+          <t xml:space="preserve">パラメータストア参照時のリージョン</t>
         </is>
       </c>
     </row>
     <row r="33" ht="33.0" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-config-file PATH</t>
+          <t xml:space="preserve">--cacert-dir DIR</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動探索)</t>
-        </is>
-      </c>
-      <c r="E33" s="7"/>
+          <t xml:space="preserve">ディレクトリのパス</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比較対象の standalone.xml</t>
+          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
         </is>
       </c>
     </row>
     <row r="34" ht="33.0" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-cli-path PATH</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">英数字と . _ -</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss-cli.sh</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名 / Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
     <row r="35" ht="33.0" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">tar のパス</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動探索)</t>
+          <t xml:space="preserve">一時ファイル</t>
         </is>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">elytron-tool.sh</t>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
         </is>
       </c>
     </row>
     <row r="36" ht="33.0" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-credential-store PATH</t>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(standalone.xml から特定)</t>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
         </is>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CredentialStore ファイル</t>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
         </is>
       </c>
     </row>
     <row r="37" ht="33.0" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.2-2 CA 証明書 (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-cwagent</t>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
+          <t xml:space="preserve">glob パターン</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
-        </is>
-      </c>
-      <c r="E37" s="7"/>
+          <t xml:space="preserve">*.crt と *.pem</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
     <row r="38" ht="33.0" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-verify-cwagent</t>
+          <t xml:space="preserve">--verify-jboss-password</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3928,53 +3956,53 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証を行わない</t>
+          <t xml:space="preserve">取得元から実行時に利用される値までの各段で、パスワードが一致するかを検証して出力する (6.5 参照)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="33.0" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-service NAME</t>
+          <t xml:space="preserve">--jboss-password-mask</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cwagent</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
+          <t xml:space="preserve">検証出力のパスワード文字列を伏字にする (判定・バイト長・16 進ダンプは表示)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="33.0" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-config-dir PATH</t>
+          <t xml:space="preserve">--jboss-config-file PATH</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3984,97 +4012,97 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/etc/cwagentconfig</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
+          <t xml:space="preserve">比較対象の standalone.xml</t>
         </is>
       </c>
     </row>
     <row r="41" ht="33.0" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
+          <t xml:space="preserve">--jboss-cli-path PATH</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">列挙</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">auto</t>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
+          <t xml:space="preserve">jboss-cli.sh</t>
         </is>
       </c>
     </row>
     <row r="42" ht="33.0" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-report</t>
+          <t xml:space="preserve">--jboss-elytron-tool PATH</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動探索)</t>
         </is>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
+          <t xml:space="preserve">elytron-tool.sh</t>
         </is>
       </c>
     </row>
     <row r="43" ht="33.0" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
+          <t xml:space="preserve">4.3 マスターパスワードの伝搬検証</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-delivery-report</t>
+          <t xml:space="preserve">--jboss-credential-store PATH</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(standalone.xml から特定)</t>
         </is>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達レポートを行わない (既定)</t>
+          <t xml:space="preserve">CredentialStore ファイル</t>
         </is>
       </c>
     </row>
@@ -4086,23 +4114,23 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--verify-cwagent</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">cwagent サービスが未定義でも検証し、見つからなければ NG とする</t>
         </is>
       </c>
     </row>
@@ -4114,23 +4142,23 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--no-verify-cwagent</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E45" s="7"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">検証を行わない</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4170,7 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-service NAME</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -4152,13 +4180,13 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">cwagent</t>
         </is>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">CloudWatch Agent の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -4170,23 +4198,23 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-config-dir PATH</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">/etc/cwagentconfig</t>
         </is>
       </c>
       <c r="E47" s="7"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">設定ファイルの注入先ディレクトリ</t>
         </is>
       </c>
     </row>
@@ -4198,23 +4226,23 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-required</t>
+          <t xml:space="preserve">--cwagent-delivery-target auto\|mock\|aws</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">列挙</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">auto</t>
         </is>
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
+          <t xml:space="preserve">送達確認先。auto は logs.endpoint_override の有無で判定</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4254,7 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4242,7 +4270,7 @@
       <c r="E49" s="7"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
+          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4282,7 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-create-log-group</t>
+          <t xml:space="preserve">--no-cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4270,231 +4298,203 @@
       <c r="E50" s="7"/>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
+          <t xml:space="preserve">送達レポートを行わない (既定)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="33.0" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-startup</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c r="E51" s="7"/>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="33.0" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(対象全体)</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="E52" s="7"/>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
     <row r="53" ht="33.0" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">拡張正規表現</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
+        </is>
+      </c>
+      <c r="E53" s="7"/>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
     <row r="54" ht="33.0" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+        </is>
+      </c>
+      <c r="E54" s="7"/>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
     <row r="55" ht="33.0" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--cwagent-required</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E55" s="7"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
         </is>
       </c>
     </row>
     <row r="56" ht="33.0" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E56" s="7"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="33.0" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-healthy</t>
+          <t xml:space="preserve">--no-cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
+      <c r="E57" s="7"/>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
+          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
         </is>
       </c>
     </row>
@@ -4506,27 +4506,27 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--verify-startup</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--allow-service-exit NAME</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4546,9 +4546,9 @@
           <t xml:space="preserve">サービス名</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4570,27 +4570,27 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-pull-images</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">拡張正規表現</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -4602,17 +4602,17 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -4634,17 +4634,17 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -4666,17 +4666,17 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-up-retry</t>
+          <t xml:space="preserve">--wait-healthy</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
+          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
         </is>
       </c>
     </row>
@@ -4730,17 +4730,17 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4762,27 +4762,27 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--recreate-containers</t>
+          <t xml:space="preserve">--allow-service-exit NAME</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
+          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-recreate-containers</t>
+          <t xml:space="preserve">--no-pull-images</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
+          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
         </is>
       </c>
     </row>
@@ -4826,27 +4826,27 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4858,17 +4858,17 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">0 以上の整数</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -4890,27 +4890,27 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--up-retry N</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--no-up-retry</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
         </is>
       </c>
     </row>
@@ -4954,223 +4954,251 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose up の再試行間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="33.0" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--recreate-containers</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="33.0" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-recreate-containers</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="33.0" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-startup-logs</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="33.0" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="33.0" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="33.0" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="33.0" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="19.5" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E73" s="7"/>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="19.5" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B74" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E74" s="7"/>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="19.5" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="E75" s="7"/>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIME タイプ</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="E76" s="7"/>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="19.5" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B77" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E77" s="7"/>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="19.5" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key=value&amp;...</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E78" s="7"/>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="19.5" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
-        </is>
-      </c>
-      <c r="E79" s="7"/>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
@@ -5182,23 +5210,23 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">URL</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -5210,203 +5238,203 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E81" s="7"/>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
     <row r="82" ht="19.5" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">HTTP メソッド</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストメソッド</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
+          <t xml:space="preserve">MIME タイプ</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E83" s="7"/>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="33.0" customHeight="1">
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">JSON 文字列</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="19.5" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">key=value&amp;...</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-after-interaction</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E86" s="7"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="87" ht="19.5" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--remove-volumes</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="19.5" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-volumes</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -5422,7 +5450,7 @@
       <c r="E88" s="7"/>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
         </is>
       </c>
     </row>
@@ -5434,27 +5462,27 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--usage-check-script PATH</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動解決)</t>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="19.5" customHeight="1">
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="33.0" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -5462,99 +5490,91 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-free-path DIR</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定の 7 か所)</t>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="E90" s="7"/>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="91" ht="33.0" customHeight="1">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1〜65535</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E91" s="7"/>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="19.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="33.0" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E92" s="7"/>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="19.5" customHeight="1">
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="33.0" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--keep-container-after-interaction</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -5562,31 +5582,27 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E93" s="7"/>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
         </is>
       </c>
     </row>
     <row r="94" ht="19.5" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--remove-volumes</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5599,26 +5615,22 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="E94" s="7"/>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
         </is>
       </c>
     </row>
     <row r="95" ht="33.0" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--keep-volumes</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5626,83 +5638,71 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E95" s="7"/>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
         </is>
       </c>
     </row>
     <row r="96" ht="19.5" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--usage-check-script PATH</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(自動解決)</t>
+        </is>
+      </c>
+      <c r="E96" s="7"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="33.0" customHeight="1">
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="19.5" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--disk-free-path DIR</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">ディレクトリ</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(既定の 7 か所)</t>
+        </is>
+      </c>
+      <c r="E97" s="7"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
@@ -5734,11 +5734,11 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="33.0" customHeight="1">
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="19.5" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--env-list-file FILE</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -5761,16 +5761,16 @@
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="66.0" customHeight="1">
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="19.5" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5778,17 +5778,17 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
@@ -5798,11 +5798,11 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析のテキストは --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="19.5" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -5818,9 +5818,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -5830,11 +5830,11 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] に残る)。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="19.5" customHeight="1">
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="33.0" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-display</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -5850,9 +5850,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -5862,11 +5862,11 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="33.0" customHeight="1">
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="19.5" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5874,17 +5874,17 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
         </is>
       </c>
     </row>
@@ -5906,17 +5906,17 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -5926,11 +5926,11 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="19.5" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="33.0" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5938,17 +5938,17 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -5970,59 +5970,59 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="66.0" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="33.0" customHeight="1">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B107" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析のテキストは --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -6034,17 +6034,17 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-display</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] に残る)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
@@ -6086,11 +6086,11 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="49.5" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="33.0" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6130,17 +6130,17 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -6162,17 +6162,17 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -6194,17 +6194,17 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6226,17 +6226,17 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6258,17 +6258,17 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
+          <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -6310,11 +6310,11 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="33.0" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="49.5" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -6337,112 +6337,120 @@
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="33.0" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="19.5" customHeight="1">
-      <c r="A118" s="11" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="19.5" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E118" s="7" t="inlineStr">
+      <c r="E119" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="33.0" customHeight="1">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
-        </is>
-      </c>
-      <c r="B119" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E119" s="7"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
     <row r="120" ht="33.0" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E120" s="7"/>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="121" ht="33.0" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -6455,22 +6463,26 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E121" s="7"/>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
         </is>
       </c>
     </row>
     <row r="122" ht="33.0" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -6483,198 +6495,290 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E122" s="7"/>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="33.0" customHeight="1">
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="19.5" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-undertow-analysis</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E123" s="7"/>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="124" ht="33.0" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E124" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="125" ht="19.5" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C125" s="3"/>
-      <c r="D125" s="3"/>
-      <c r="E125" s="7"/>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="126" ht="33.0" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C126" s="3"/>
-      <c r="D126" s="3"/>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E126" s="7"/>
-      <c r="F126" s="3"/>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="33.0" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
-        </is>
-      </c>
-      <c r="C127" s="3"/>
-      <c r="D127" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E127" s="7"/>
-      <c r="F127" s="3"/>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="33.0" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
-        </is>
-      </c>
-      <c r="C128" s="3"/>
-      <c r="D128" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E128" s="7"/>
-      <c r="F128" s="3"/>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="33.0" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
-        </is>
-      </c>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E129" s="7"/>
-      <c r="F129" s="3"/>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="33.0" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
-        </is>
-      </c>
-      <c r="C130" s="3"/>
-      <c r="D130" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E130" s="7"/>
-      <c r="F130" s="3"/>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="33.0" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C131" s="3"/>
-      <c r="D131" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E131" s="7"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="19.5" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C132" s="3"/>
@@ -6682,109 +6786,89 @@
       <c r="E132" s="7"/>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
     <row r="133" ht="33.0" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="7"/>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
-        </is>
-      </c>
+      <c r="F133" s="3"/>
     </row>
     <row r="134" ht="33.0" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="7"/>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
-        </is>
-      </c>
+      <c r="F134" s="3"/>
     </row>
     <row r="135" ht="33.0" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="7"/>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
-        </is>
-      </c>
+      <c r="F135" s="3"/>
     </row>
     <row r="136" ht="33.0" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="7"/>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F136" s="3"/>
     </row>
     <row r="137" ht="33.0" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="7"/>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F137" s="3"/>
     </row>
     <row r="138" ht="33.0" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
@@ -6794,7 +6878,7 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C138" s="3"/>
@@ -6802,7 +6886,7 @@
       <c r="E138" s="7"/>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6898,7 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C139" s="3"/>
@@ -6822,7 +6906,7 @@
       <c r="E139" s="7"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6918,7 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C140" s="3"/>
@@ -6842,12 +6926,152 @@
       <c r="E140" s="7"/>
       <c r="F140" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="33.0" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="33.0" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="33.0" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="7"/>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="33.0" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="7"/>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="33.0" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="33.0" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="7"/>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="33.0" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="7"/>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F140"/>
+  <autoFilter ref="A4:F147"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">143 件</t>
+          <t xml:space="preserve">154 件</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="33.0" customHeight="1">
+    <row r="49" ht="49.5" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-report</t>
+          <t xml:space="preserve">--cwagent-verify-display</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4270,7 +4270,7 @@
       <c r="E49" s="7"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
+          <t xml:space="preserve">ビルド・デプロイ後の「CloudWatch Agent の送信状況チェック」「cwagent の警告・エラー」「cwagent のログ送信検証」を画面へ表示する (既定では表示しない)</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-delivery-report</t>
+          <t xml:space="preserve">--no-cwagent-verify-display</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -4298,7 +4298,7 @@
       <c r="E50" s="7"/>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達レポートを行わない (既定)</t>
+          <t xml:space="preserve">上記 3 つを画面へ表示しない (既定)</t>
         </is>
       </c>
     </row>
@@ -4310,23 +4310,23 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
+          <t xml:space="preserve">--cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E51" s="7"/>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達を待ち合わせて送達レポートを表示する (既定では行わない)</t>
         </is>
       </c>
     </row>
@@ -4338,23 +4338,23 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
+          <t xml:space="preserve">--no-cwagent-delivery-report</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
+          <t xml:space="preserve">送達レポートを行わない (既定)</t>
         </is>
       </c>
     </row>
@@ -4366,23 +4366,23 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-service NAME</t>
+          <t xml:space="preserve">--cwagent-delivery-timeout SEC</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
+          <t xml:space="preserve">送達を待つ最大秒数 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -4394,23 +4394,23 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-mock-port PORT</t>
+          <t xml:space="preserve">--cwagent-delivery-interval SEC</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
+          <t xml:space="preserve">送達確認のポーリング間隔 (--cwagent-delivery-report 指定時に使用)</t>
         </is>
       </c>
     </row>
@@ -4422,23 +4422,23 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-required</t>
+          <t xml:space="preserve">--cwagent-mock-service NAME</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(endpoint_override から解決)</t>
         </is>
       </c>
       <c r="E55" s="7"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs の Compose サービス名</t>
         </is>
       </c>
     </row>
@@ -4450,23 +4450,23 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-mock-port PORT</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(フラグ)</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1〜65535</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(endpoint_override から解決、既定 8080)</t>
         </is>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
+          <t xml:space="preserve">偽装 CloudWatch Logs のコンテナ側ポート</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cwagent-create-log-group</t>
+          <t xml:space="preserve">--cwagent-required</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -4488,30 +4488,30 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
+          <t xml:space="preserve">検証 NG を終了コード 1 として扱う</t>
         </is>
       </c>
     </row>
     <row r="58" ht="33.0" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-startup</t>
+          <t xml:space="preserve">--cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">(フラグ)</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -4519,46 +4519,38 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
+      <c r="E58" s="7"/>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
+          <t xml:space="preserve">実 CloudWatch Logs 宛ての構成で、設定ファイルの log_group_name のロググループが存在しなければ自動作成する (既定では作成しない)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="33.0" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+          <t xml:space="preserve">4.3.1 CloudWatch Agent (cwagent) のログ送信検証</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-service NAME</t>
+          <t xml:space="preserve">--no-cwagent-create-log-group</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
-        </is>
-      </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(対象全体)</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(フラグ)</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E59" s="7"/>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
+          <t xml:space="preserve">ロググループの自動作成を行わない (既定)。存在しない場合は NG として報告するだけにする</t>
         </is>
       </c>
     </row>
@@ -4570,27 +4562,27 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-pattern P</t>
+          <t xml:space="preserve">--verify-startup</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">拡張正規表現</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WFLYSRV0025:</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了とみなすログのパターン</t>
+          <t xml:space="preserve">ビルド後にコンテナを起動し、起動完了をログから確認</t>
         </is>
       </c>
     </row>
@@ -4602,27 +4594,27 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-timeout SEC</t>
+          <t xml:space="preserve">--startup-service NAME</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">(対象全体)</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動完了を待つ最大秒数</t>
+          <t xml:space="preserve">起動完了チェックの対象。指定すると --verify-startup を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4634,17 +4626,17 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-interval SEC</t>
+          <t xml:space="preserve">--startup-log-pattern P</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">拡張正規表現</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">WFLYSRV0025:</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -4654,7 +4646,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ポーリング間隔</t>
+          <t xml:space="preserve">起動完了とみなすログのパターン</t>
         </is>
       </c>
     </row>
@@ -4666,17 +4658,17 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--startup-log-lines N\|all</t>
+          <t xml:space="preserve">--startup-timeout SEC</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
@@ -4686,7 +4678,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
+          <t xml:space="preserve">起動完了を待つ最大秒数</t>
         </is>
       </c>
     </row>
@@ -4698,27 +4690,27 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-healthy</t>
+          <t xml:space="preserve">--startup-interval SEC</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
+          <t xml:space="preserve">ポーリング間隔</t>
         </is>
       </c>
     </row>
@@ -4730,17 +4722,17 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait-timeout SEC</t>
+          <t xml:space="preserve">--startup-log-lines N\|all</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
@@ -4750,7 +4742,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
+          <t xml:space="preserve">表示するログ行数 (末尾 N 行 / 全行)</t>
         </is>
       </c>
     </row>
@@ -4762,27 +4754,27 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--allow-service-exit NAME</t>
+          <t xml:space="preserve">--wait-healthy</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サービス名</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
+          <t xml:space="preserve">compose up に --wait を付け、healthy になるまで compose 側で待つ</t>
         </is>
       </c>
     </row>
@@ -4794,27 +4786,27 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-pull-images</t>
+          <t xml:space="preserve">--wait-timeout SEC</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
+          <t xml:space="preserve">--wait の最大待機秒数。指定すると --wait-healthy を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -4826,27 +4818,27 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry N</t>
+          <t xml:space="preserve">--allow-service-exit NAME</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">サービス名</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
+          <t xml:space="preserve">起動確認中に停止していても失敗扱いにしないサービス</t>
         </is>
       </c>
     </row>
@@ -4858,27 +4850,27 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--pull-retry-interval SEC</t>
+          <t xml:space="preserve">--no-pull-images</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前取得の再試行間隔</t>
+          <t xml:space="preserve">compose up の前に行うイメージの事前取得 (compose pull) を行わない</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4882,7 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry N</t>
+          <t xml:space="preserve">--pull-retry N</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -4900,7 +4892,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -4910,7 +4902,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
+          <t xml:space="preserve">事前取得が一過性のエラーで失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4922,27 +4914,27 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-up-retry</t>
+          <t xml:space="preserve">--pull-retry-interval SEC</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
+          <t xml:space="preserve">事前取得の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4946,7 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--up-retry-interval SEC</t>
+          <t xml:space="preserve">--up-retry N</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -4964,7 +4956,7 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -4974,7 +4966,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose up の再試行間隔</t>
+          <t xml:space="preserve">compose up が一過性の理由で失敗したときの再試行回数</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4978,7 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--recreate-containers</t>
+          <t xml:space="preserve">--no-up-retry</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -5006,7 +4998,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
+          <t xml:space="preserve">compose up の再試行を行わない (--up-retry 0 と同じ)</t>
         </is>
       </c>
     </row>
@@ -5018,27 +5010,27 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-recreate-containers</t>
+          <t xml:space="preserve">--up-retry-interval SEC</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0 以上の整数</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
+          <t xml:space="preserve">compose up の再試行間隔</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5042,7 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-startup-logs</t>
+          <t xml:space="preserve">--recreate-containers</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -5070,7 +5062,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
+          <t xml:space="preserve">前回の実行が残したコンテナを、状態にかかわらず --force-recreate で作り直す</t>
         </is>
       </c>
     </row>
@@ -5082,27 +5074,27 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--shutdown-timeout SEC</t>
+          <t xml:space="preserve">--no-recreate-containers</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
+          <t xml:space="preserve">前回の実行が残したコンテナの点検と作り直しを行わない (従来の動作)</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5106,7 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-shutdown-logs</t>
+          <t xml:space="preserve">--suppress-startup-logs</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -5134,7 +5126,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+          <t xml:space="preserve">起動ログの表示を抑制 (判定は継続。失敗時は表示される)</t>
         </is>
       </c>
     </row>
@@ -5146,27 +5138,27 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-removed-logs</t>
+          <t xml:space="preserve">--shutdown-timeout SEC</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+          <t xml:space="preserve">エラー終了時の SIGTERM から SIGKILL までの猶予秒数 (ECS の StopTimeout 既定と同じ)</t>
         </is>
       </c>
     </row>
@@ -5178,83 +5170,91 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-shutdown-logs</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エラー終了時の SIGTERM 停止と終了ログ取得を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="33.0" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--suppress-removed-logs</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose down / compose stop の Removed 等の出力を抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="33.0" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 起動確認 (JBoss EAP / WildFly)</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--keep-container</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">確認後もコンテナを停止・削除しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="19.5" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E80" s="7"/>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="19.5" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B81" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E81" s="7"/>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -5266,23 +5266,23 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-method METHOD</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
+          <t xml:space="preserve">URL</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストメソッド</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -5294,23 +5294,23 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIME タイプ</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動)</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E83" s="7"/>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -5322,23 +5322,23 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">HTTP メソッド</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -5350,23 +5350,23 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">key=value&amp;...</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">MIME タイプ</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -5378,23 +5378,23 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">JSON 文字列</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E86" s="7"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
         </is>
       </c>
     </row>
@@ -5406,23 +5406,23 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">key=value&amp;...</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
         </is>
       </c>
     </row>
@@ -5434,83 +5434,83 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E88" s="7"/>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
         </is>
       </c>
     </row>
     <row r="89" ht="19.5" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="19.5" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
-        </is>
-      </c>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E90" s="7"/>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="33.0" customHeight="1">
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="19.5" customHeight="1">
       <c r="A91" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -5518,23 +5518,23 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
         </is>
       </c>
     </row>
@@ -5546,23 +5546,23 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="E92" s="7"/>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
@@ -5574,27 +5574,27 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-after-interaction</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1〜65535</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
         </is>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="19.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="33.0" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--remove-volumes</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5618,7 +5618,7 @@
       <c r="E94" s="7"/>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-volumes</t>
+          <t xml:space="preserve">--keep-container-after-interaction</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5646,7 +5646,7 @@
       <c r="E95" s="7"/>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
+          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
         </is>
       </c>
     </row>
@@ -5658,27 +5658,27 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--usage-check-script PATH</t>
+          <t xml:space="preserve">--remove-volumes</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動解決)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E96" s="7"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="19.5" customHeight="1">
+          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="33.0" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -5686,119 +5686,111 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-free-path DIR</t>
+          <t xml:space="preserve">--keep-volumes</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(既定の 7 か所)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="33.0" customHeight="1">
+          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--usage-check-script PATH</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(自動解決)</t>
+        </is>
+      </c>
+      <c r="E98" s="7"/>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
         </is>
       </c>
     </row>
     <row r="99" ht="19.5" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-free-path DIR</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリ</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定の 7 か所)</t>
+        </is>
+      </c>
+      <c r="E99" s="7"/>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="33.0" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="19.5" customHeight="1">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
         </is>
       </c>
     </row>
@@ -5810,59 +5802,59 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--env-list-file FILE</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="33.0" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5866,7 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -5882,9 +5874,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true (既定)</t>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -5894,7 +5886,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -5906,17 +5898,17 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -5926,11 +5918,11 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="33.0" customHeight="1">
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="19.5" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5938,17 +5930,17 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
@@ -5958,7 +5950,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
         </is>
       </c>
     </row>
@@ -5970,31 +5962,31 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="66.0" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="33.0" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6002,17 +5994,17 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
@@ -6022,7 +6014,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。Java 例外解析の Excel と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析のテキストは --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report 併用時のみ保存</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -6034,59 +6026,59 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="99.0" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない (結果は全量レポート [10] に残る)。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="19.5" customHeight="1">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B109" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-deploy-exception-display</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -6098,17 +6090,17 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--deploy-exception-display</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -6118,11 +6110,11 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="33.0" customHeight="1">
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="19.5" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6130,17 +6122,17 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -6150,11 +6142,11 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="19.5" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="49.5" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6162,17 +6154,17 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--deploy-exception-report</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
@@ -6182,7 +6174,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6186,7 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--no-deploy-exception-report</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -6204,7 +6196,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
@@ -6214,7 +6206,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
+          <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6218,7 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -6246,7 +6238,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6250,7 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -6268,7 +6260,7 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -6278,7 +6270,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -6290,59 +6282,59 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="33.0" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E116" s="7" t="inlineStr">
+      <c r="E117" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="49.5" customHeight="1">
-      <c r="A117" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B117" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6354,17 +6346,17 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--readonly-analysis-display</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ で始まるパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
@@ -6374,11 +6366,11 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="19.5" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="33.0" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6386,7 +6378,7 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
+          <t xml:space="preserve">--no-readonly-analysis-display</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -6396,7 +6388,7 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
@@ -6406,11 +6398,11 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="33.0" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="49.5" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6418,17 +6410,17 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
+          <t xml:space="preserve">--readonly-analysis-report</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
@@ -6438,7 +6430,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6442,7 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
+          <t xml:space="preserve">--no-readonly-analysis-report</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -6460,7 +6452,7 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
@@ -6470,7 +6462,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力だけを抑制する。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
         </is>
       </c>
     </row>
@@ -6482,219 +6474,231 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="33.0" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="19.5" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-readonly-analysis</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E122" s="7" t="inlineStr">
+      <c r="E124" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="19.5" customHeight="1">
-      <c r="A123" s="11" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="49.5" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="33.0" customHeight="1">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B124" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="19.5" customHeight="1">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B125" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="126" ht="33.0" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="19.5" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E126" s="7"/>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="33.0" customHeight="1">
-      <c r="A127" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B127" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(オプション不要)</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E127" s="7"/>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
     <row r="128" ht="33.0" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E128" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="129" ht="33.0" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--undertow-analysis-display</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -6707,50 +6711,58 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E129" s="7"/>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">分析結果をダイアログの操作後に画面へも出力する (既定では画面へ出さない)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="130" ht="33.0" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E130" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
         </is>
       </c>
     </row>
     <row r="131" ht="33.0" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -6763,222 +6775,354 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E131" s="7"/>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
         </is>
       </c>
     </row>
     <row r="132" ht="19.5" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C132" s="3"/>
-      <c r="D132" s="3"/>
-      <c r="E132" s="7"/>
+          <t xml:space="preserve">--no-undertow-analysis</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="133" ht="33.0" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C133" s="3"/>
-      <c r="D133" s="3"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="3"/>
-    </row>
-    <row r="134" ht="33.0" customHeight="1">
+          <t xml:space="preserve">--cert-check-text FILE</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="19.5" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
-        </is>
-      </c>
-      <c r="C134" s="3"/>
-      <c r="D134" s="3"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="3"/>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="33.0" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
-        </is>
-      </c>
-      <c r="C135" s="3"/>
-      <c r="D135" s="3"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="3"/>
-    </row>
-    <row r="136" ht="33.0" customHeight="1">
+          <t xml:space="preserve">--jboss-module-list-text FILE</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss モジュール一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-jboss-module-list-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="19.5" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
-        </is>
-      </c>
-      <c r="C136" s="3"/>
-      <c r="D136" s="3"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="3"/>
+          <t xml:space="preserve">--no-jboss-module-list-text</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss モジュール一覧のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="33.0" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
-        </is>
-      </c>
-      <c r="C137" s="3"/>
-      <c r="D137" s="3"/>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E137" s="7"/>
-      <c r="F137" s="3"/>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="33.0" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C138" s="3"/>
-      <c r="D138" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E138" s="7"/>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
     <row r="139" ht="33.0" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C139" s="3"/>
-      <c r="D139" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E139" s="7"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="140" ht="33.0" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
-        </is>
-      </c>
-      <c r="C140" s="3"/>
-      <c r="D140" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E140" s="7"/>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="141" ht="33.0" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C141" s="3"/>
-      <c r="D141" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E141" s="7"/>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="142" ht="33.0" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C142" s="3"/>
-      <c r="D142" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E142" s="7"/>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="19.5" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C143" s="3"/>
@@ -6986,92 +7130,292 @@
       <c r="E143" s="7"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
     <row r="144" ht="33.0" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="7"/>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F144" s="3"/>
     </row>
     <row r="145" ht="33.0" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="7"/>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
-        </is>
-      </c>
+      <c r="F145" s="3"/>
     </row>
     <row r="146" ht="33.0" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="7"/>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F146" s="3"/>
     </row>
     <row r="147" ht="33.0" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="7"/>
-      <c r="F147" s="3" t="inlineStr">
+      <c r="F147" s="3"/>
+    </row>
+    <row r="148" ht="33.0" customHeight="1">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--noreport</t>
+        </is>
+      </c>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="3"/>
+    </row>
+    <row r="149" ht="33.0" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="33.0" customHeight="1">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="33.0" customHeight="1">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree</t>
+        </is>
+      </c>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="33.0" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="7"/>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="33.0" customHeight="1">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="33.0" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="33.0" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="33.0" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B156" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="33.0" customHeight="1">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="33.0" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F147"/>
+  <autoFilter ref="A4:F158"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -8950,7 +9294,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="132.0" customHeight="1">
+    <row r="13" ht="148.5" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -8968,7 +9312,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--usage-check-script のパスを読み取れない、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正、--copy-artifact-path / --copy-artifact-search-dir が絶対パスでない、--remove-volumes と --keep-volumes の同時指定</t>
+          <t xml:space="preserve">不明なオプション、値の欠落、数値が 1 未満 (ビルド監視の各値は 0 未満か非数値)、--keep-container-mode の不正値、--usage-check-script のパスを読み取れない、--jboss-http-port / --cwagent-mock-port の範囲外、--cwagent-delivery-target の不正値、--cwagent-config-dir が絶対パスでない、--deploy-exception-excel が .xlsx でない、--deploy-exception-excel と --deploy-exception-text が同一パス、--readonly-analysis-excel が .xlsx でない、--readonly-analysis-excel と --readonly-analysis-text が同一パス、--readonly-analysis-display と --no-readonly-analysis の同時指定、オプションの排他違反、--startup-service が --compose-service に含まれない、起動対象が base のみ、--copy-file の書式不正、--copy-artifact-path / --copy-artifact-search-dir が絶対パスでない、--remove-volumes と --keep-volumes の同時指定</t>
         </is>
       </c>
     </row>
@@ -10966,7 +11310,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="99.0" customHeight="1">
+    <row r="53" ht="115.5" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -10979,40 +11323,43 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイ結果ファイルへ Java 例外解析を残す
+          <t xml:space="preserve">全量レポートへ Java 例外解析を残す
 (reports/build_and_verify_&lt;日時&gt;.txt … [10] に例外解析の全文。
-画面表示も Excel / テキストの出力も行わない ← 既定)</t>
+--deploy-exception-report が無ければ [10] へは記載しない ← 既定。
+画面表示も Excel / テキストの出力も行わない)</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
-    --compose-service app --startup-service app \
-    --report-dir ./reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="66.0" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">build_and_verify.sh</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-2</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">解析結果を画面でも読む (既定は非表示)</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
     --report-dir ./reports \
+    --deploy-exception-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="82.5" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-2</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">解析結果を画面でも読む (既定は非表示)</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --compose-service app --startup-service app \
+    --report-dir ./reports \
+    --deploy-exception-report \
     --deploy-exception-display</t>
         </is>
       </c>
@@ -11065,7 +11412,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="165.0" customHeight="1">
+    <row r="57" ht="198.0" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -11081,6 +11428,7 @@
           <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
 既定で毎回実行される。--report-dir があれば
 reports/build_and_verify_&lt;日時&gt;_readonly_filesystem.xlsx / .txt も出力される
+(全量レポート [11] へ載せるには --readonly-analysis-report を併用する)
 Dockerfile のビルド時に書くだけのディレクトリは「ビルド時のみ」として
 対象から外し、entrypoint.sh などが起動のたびに書く場所を「要対応」に挙げる</t>
         </is>
@@ -11089,7 +11437,8 @@
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
-    --report-dir ./reports</t>
+    --report-dir ./reports \
+    --readonly-analysis-report</t>
         </is>
       </c>
     </row>
@@ -11118,7 +11467,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="33.0" customHeight="1">
+    <row r="59" ht="66.0" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -11131,62 +11480,87 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面でも読む
+既定では画面へ出さず、Excel / テキストへ残すだけ</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --compose-service app --startup-service app \
+    --readonly-analysis-display</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="33.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17-8</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの分析を行わない</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-readonly-analysis</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="66.0" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="61" ht="66.0" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
 進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="33.0" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
+    <row r="62" ht="33.0" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D61"/>
+  <autoFilter ref="A4:D62"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">154 件</t>
+          <t xml:space="preserve">156 件</t>
         </is>
       </c>
     </row>
@@ -6949,68 +6949,76 @@
     <row r="137" ht="33.0" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--truststore-inventory-text FILE</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E137" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">トラストストア一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-truststore-inventory-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="138" ht="33.0" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-truststore-inventory-text</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E138" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">トラストストア一覧のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="139" ht="33.0" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -7026,7 +7034,7 @@
       <c r="E139" s="7"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -7038,23 +7046,23 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E140" s="7"/>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -7066,23 +7074,23 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E141" s="7"/>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
@@ -7094,7 +7102,7 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--prune-build-cache</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -7110,61 +7118,85 @@
       <c r="E142" s="7"/>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="19.5" customHeight="1">
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="33.0" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C143" s="3"/>
-      <c r="D143" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E143" s="7"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="144" ht="33.0" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C144" s="3"/>
-      <c r="D144" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E144" s="7"/>
-      <c r="F144" s="3"/>
-    </row>
-    <row r="145" ht="33.0" customHeight="1">
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="19.5" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="7"/>
-      <c r="F145" s="3"/>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="33.0" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
@@ -7174,7 +7206,7 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C146" s="3"/>
@@ -7190,7 +7222,7 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C147" s="3"/>
@@ -7206,7 +7238,7 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C148" s="3"/>
@@ -7217,42 +7249,34 @@
     <row r="149" ht="33.0" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="7"/>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
+      <c r="F149" s="3"/>
     </row>
     <row r="150" ht="33.0" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="7"/>
-      <c r="F150" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
-        </is>
-      </c>
+      <c r="F150" s="3"/>
     </row>
     <row r="151" ht="33.0" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
@@ -7262,7 +7286,7 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C151" s="3"/>
@@ -7270,7 +7294,7 @@
       <c r="E151" s="7"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7306,7 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C152" s="3"/>
@@ -7290,7 +7314,7 @@
       <c r="E152" s="7"/>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7326,7 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C153" s="3"/>
@@ -7310,7 +7334,7 @@
       <c r="E153" s="7"/>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7346,7 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C154" s="3"/>
@@ -7330,7 +7354,7 @@
       <c r="E154" s="7"/>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7366,7 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C155" s="3"/>
@@ -7350,7 +7374,7 @@
       <c r="E155" s="7"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7386,7 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--directory-tree-depth N</t>
         </is>
       </c>
       <c r="C156" s="3"/>
@@ -7370,7 +7394,7 @@
       <c r="E156" s="7"/>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7406,7 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-file-limit N</t>
         </is>
       </c>
       <c r="C157" s="3"/>
@@ -7390,7 +7414,7 @@
       <c r="E157" s="7"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7426,7 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--directory-file-limit all</t>
         </is>
       </c>
       <c r="C158" s="3"/>
@@ -7410,12 +7434,52 @@
       <c r="E158" s="7"/>
       <c r="F158" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="33.0" customHeight="1">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B159" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="33.0" customHeight="1">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F158"/>
+  <autoFilter ref="A4:F160"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">156 件</t>
+          <t xml:space="preserve">162 件</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="33.0" customHeight="1">
+    <row r="106" ht="49.5" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5962,17 +5962,17 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--directory-tree-excel</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -5982,11 +5982,11 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ディレクトリのみのツリーを Excel ブック (.xlsx) へ追加出力する。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="19.5" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -5994,17 +5994,17 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">上記の Excel 出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6026,12 +6026,12 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -6041,16 +6041,16 @@
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="99.0" customHeight="1">
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する。指定すると Excel 出力を有効にする (--report-dir が無くても出力できる)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="33.0" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6058,17 +6058,17 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -6090,17 +6090,17 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非表示)</t>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="19.5" customHeight="1">
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="33.0" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6122,59 +6122,59 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-display</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="99.0" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="49.5" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B112" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-report</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリのみのツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -6186,123 +6186,123 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="19.5" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="49.5" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-report</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="33.0" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--no-deploy-exception-report</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="E113" s="7" t="inlineStr">
+      <c r="E116" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="33.0" customHeight="1">
-      <c r="A114" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B114" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="33.0" customHeight="1">
-      <c r="A115" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B115" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし。指定時のみ出力)</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="19.5" customHeight="1">
-      <c r="A116" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B116" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -6314,17 +6314,17 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6346,91 +6346,91 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-display</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="19.5" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="33.0" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="33.0" customHeight="1">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B119" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis-display</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="49.5" customHeight="1">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B120" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-report</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis-report</t>
+          <t xml:space="preserve">--readonly-analysis-display</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -6450,9 +6450,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6474,123 +6474,123 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-readonly-analysis-display</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="49.5" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--readonly-analysis-report</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="33.0" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-readonly-analysis-report</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="33.0" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E122" s="7" t="inlineStr">
+      <c r="E125" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="33.0" customHeight="1">
-      <c r="A123" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B123" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="19.5" customHeight="1">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B124" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="49.5" customHeight="1">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B125" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6602,17 +6602,17 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
+          <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -6654,11 +6654,11 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="33.0" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="49.5" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6698,59 +6698,59 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-display</t>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="19.5" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E129" s="7" t="inlineStr">
+      <c r="E130" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">分析結果をダイアログの操作後に画面へも出力する (既定では画面へ出さない)。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="33.0" customHeight="1">
-      <c r="A130" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B130" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
@@ -6762,59 +6762,59 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="33.0" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-analysis-display</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E131" s="7" t="inlineStr">
+      <c r="E132" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="19.5" customHeight="1">
-      <c r="A132" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B132" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
+          <t xml:space="preserve">分析結果をダイアログの操作後に画面へも出力する (既定では画面へ出さない)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6826,155 +6826,155 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="33.0" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="19.5" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-analysis</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="33.0" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E133" s="7" t="inlineStr">
+      <c r="E136" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="19.5" customHeight="1">
-      <c r="A134" s="11" t="inlineStr">
+    <row r="137" ht="19.5" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--no-cert-check-text</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E134" s="7" t="inlineStr">
+      <c r="E137" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="33.0" customHeight="1">
-      <c r="A135" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B135" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-module-list-text FILE</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBoss モジュール一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-jboss-module-list-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="19.5" customHeight="1">
-      <c r="A136" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B136" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-jboss-module-list-text</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBoss モジュール一覧のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="33.0" customHeight="1">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B137" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--truststore-inventory-text FILE</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">トラストストア一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-truststore-inventory-text とは排他</t>
         </is>
       </c>
     </row>
@@ -6986,95 +6986,103 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-truststore-inventory-text</t>
+          <t xml:space="preserve">--jboss-module-list-text FILE</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss モジュール一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-jboss-module-list-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="19.5" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-jboss-module-list-text</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D138" s="3" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E138" s="7" t="inlineStr">
+      <c r="E139" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">トラストストア一覧のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="33.0" customHeight="1">
-      <c r="A139" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
-        </is>
-      </c>
-      <c r="B139" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E139" s="7"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">JBoss モジュール一覧のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="140" ht="33.0" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--truststore-inventory-text FILE</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D140" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E140" s="7"/>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">トラストストア一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-truststore-inventory-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="141" ht="33.0" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-truststore-inventory-text</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -7087,22 +7095,26 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E141" s="7"/>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">トラストストア一覧のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="142" ht="33.0" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -7118,7 +7130,7 @@
       <c r="E142" s="7"/>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -7130,23 +7142,23 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E143" s="7"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7170,7 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -7174,77 +7186,113 @@
       <c r="E144" s="7"/>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="19.5" customHeight="1">
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="33.0" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C145" s="3"/>
-      <c r="D145" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E145" s="7"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="146" ht="33.0" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C146" s="3"/>
-      <c r="D146" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E146" s="7"/>
-      <c r="F146" s="3"/>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="33.0" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
-        </is>
-      </c>
-      <c r="C147" s="3"/>
-      <c r="D147" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E147" s="7"/>
-      <c r="F147" s="3"/>
-    </row>
-    <row r="148" ht="33.0" customHeight="1">
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="19.5" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="7"/>
-      <c r="F148" s="3"/>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="33.0" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
@@ -7254,7 +7302,7 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C149" s="3"/>
@@ -7270,7 +7318,7 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C150" s="3"/>
@@ -7281,62 +7329,50 @@
     <row r="151" ht="33.0" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="7"/>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
+      <c r="F151" s="3"/>
     </row>
     <row r="152" ht="33.0" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="7"/>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
-        </is>
-      </c>
+      <c r="F152" s="3"/>
     </row>
     <row r="153" ht="33.0" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="7"/>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
-        </is>
-      </c>
+      <c r="F153" s="3"/>
     </row>
     <row r="154" ht="33.0" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
@@ -7346,7 +7382,7 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C154" s="3"/>
@@ -7354,7 +7390,7 @@
       <c r="E154" s="7"/>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7402,7 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C155" s="3"/>
@@ -7374,7 +7410,7 @@
       <c r="E155" s="7"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7422,7 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C156" s="3"/>
@@ -7394,7 +7430,7 @@
       <c r="E156" s="7"/>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7442,7 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C157" s="3"/>
@@ -7414,7 +7450,7 @@
       <c r="E157" s="7"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7462,7 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C158" s="3"/>
@@ -7434,7 +7470,7 @@
       <c r="E158" s="7"/>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7482,7 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree-excel</t>
         </is>
       </c>
       <c r="C159" s="3"/>
@@ -7454,7 +7490,7 @@
       <c r="E159" s="7"/>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">ディレクトリのみのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象)</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7502,7 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
         </is>
       </c>
       <c r="C160" s="3"/>
@@ -7474,12 +7510,132 @@
       <c r="E160" s="7"/>
       <c r="F160" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="33.0" customHeight="1">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+        </is>
+      </c>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="7"/>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="33.0" customHeight="1">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="7"/>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="33.0" customHeight="1">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="33.0" customHeight="1">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B164" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="7"/>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="33.0" customHeight="1">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="33.0" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B166" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="7"/>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F160"/>
+  <autoFilter ref="A4:F166"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -5982,7 +5982,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリのみのツリーを Excel ブック (.xlsx) へ追加出力する。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブック (.xlsx) へ追加出力する。リンク先は右端の列へ並べる。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリのみのツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       <c r="E159" s="7"/>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリのみのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象)</t>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
         </is>
       </c>
     </row>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">162 件</t>
+          <t xml:space="preserve">168 件</t>
         </is>
       </c>
     </row>
@@ -7274,115 +7274,183 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="19.5" customHeight="1">
+    <row r="148" ht="66.0" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
+          <t xml:space="preserve">--suppress-syslog</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E148" s="7"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="33.0" customHeight="1">
+          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="49.5" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C149" s="3"/>
-      <c r="D149" s="3"/>
+          <t xml:space="preserve">--no-suppress-syslog</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E149" s="7"/>
-      <c r="F149" s="3"/>
-    </row>
-    <row r="150" ht="33.0" customHeight="1">
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="49.5" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
-        </is>
-      </c>
-      <c r="C150" s="3"/>
-      <c r="D150" s="3"/>
+          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file / local</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file</t>
+        </is>
+      </c>
       <c r="E150" s="7"/>
-      <c r="F150" s="3"/>
-    </row>
-    <row r="151" ht="33.0" customHeight="1">
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="49.5" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
-        </is>
-      </c>
-      <c r="C151" s="3"/>
-      <c r="D151" s="3"/>
+          <t xml:space="preserve">--syslog-audit</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E151" s="7"/>
-      <c r="F151" s="3"/>
-    </row>
-    <row r="152" ht="33.0" customHeight="1">
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="49.5" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
-        </is>
-      </c>
-      <c r="C152" s="3"/>
-      <c r="D152" s="3"/>
+          <t xml:space="preserve">--no-syslog-audit</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E152" s="7"/>
-      <c r="F152" s="3"/>
-    </row>
-    <row r="153" ht="33.0" customHeight="1">
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">増加量の計測を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="49.5" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
-        </is>
-      </c>
-      <c r="C153" s="3"/>
-      <c r="D153" s="3"/>
+          <t xml:space="preserve">--syslog-audit-file FILE</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/var/log/messages</t>
+        </is>
+      </c>
       <c r="E153" s="7"/>
-      <c r="F153" s="3"/>
-    </row>
-    <row r="154" ht="33.0" customHeight="1">
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="19.5" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C154" s="3"/>
@@ -7390,109 +7458,89 @@
       <c r="E154" s="7"/>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
     <row r="155" ht="33.0" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="7"/>
-      <c r="F155" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
-        </is>
-      </c>
+      <c r="F155" s="3"/>
     </row>
     <row r="156" ht="33.0" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="7"/>
-      <c r="F156" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
-        </is>
-      </c>
+      <c r="F156" s="3"/>
     </row>
     <row r="157" ht="33.0" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="7"/>
-      <c r="F157" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
-        </is>
-      </c>
+      <c r="F157" s="3"/>
     </row>
     <row r="158" ht="33.0" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="7"/>
-      <c r="F158" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
-        </is>
-      </c>
+      <c r="F158" s="3"/>
     </row>
     <row r="159" ht="33.0" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="7"/>
-      <c r="F159" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
-        </is>
-      </c>
+      <c r="F159" s="3"/>
     </row>
     <row r="160" ht="33.0" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
@@ -7502,7 +7550,7 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C160" s="3"/>
@@ -7510,7 +7558,7 @@
       <c r="E160" s="7"/>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7570,7 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C161" s="3"/>
@@ -7530,7 +7578,7 @@
       <c r="E161" s="7"/>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7590,7 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C162" s="3"/>
@@ -7550,7 +7598,7 @@
       <c r="E162" s="7"/>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7610,7 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C163" s="3"/>
@@ -7570,7 +7618,7 @@
       <c r="E163" s="7"/>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7630,7 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C164" s="3"/>
@@ -7590,7 +7638,7 @@
       <c r="E164" s="7"/>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7650,7 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree-excel</t>
         </is>
       </c>
       <c r="C165" s="3"/>
@@ -7610,7 +7658,7 @@
       <c r="E165" s="7"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7670,7 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
         </is>
       </c>
       <c r="C166" s="3"/>
@@ -7630,12 +7678,132 @@
       <c r="E166" s="7"/>
       <c r="F166" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="33.0" customHeight="1">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+        </is>
+      </c>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="33.0" customHeight="1">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B168" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="33.0" customHeight="1">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B169" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="7"/>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="33.0" customHeight="1">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B170" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="7"/>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="33.0" customHeight="1">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B171" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+      <c r="E171" s="7"/>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="33.0" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B172" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="7"/>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F166"/>
+  <autoFilter ref="A4:F172"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -6146,7 +6146,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="99.0" customHeight="1">
+    <row r="112" ht="115.5" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
         </is>
       </c>
     </row>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">168 件</t>
+          <t xml:space="preserve">183 件</t>
         </is>
       </c>
     </row>
@@ -5258,351 +5258,399 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="19.5" customHeight="1">
+    <row r="82" ht="33.0" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--verify-url URL</t>
+          <t xml:space="preserve">--no-ecs-circuit-breaker</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E82" s="7"/>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="19.5" customHeight="1">
+          <t xml:space="preserve">再現を一切行わない (従来どおり、unhealthy でもコンテナを止めない)。画面・テキスト・全量レポート [14] のすべてを止める</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="33.0" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--expect-status CODE</t>
+          <t xml:space="preserve">--ecs-circuit-breaker</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E83" s="7"/>
+          <t xml:space="preserve">(既定で有効)</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="19.5" customHeight="1">
+          <t xml:space="preserve">再現を行う (--no-ecs-circuit-breaker の打ち消し)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="66.0" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-method METHOD</t>
+          <t xml:space="preserve">--ecs-essential-service NAME</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP メソッド</t>
+          <t xml:space="preserve">サービス名</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="E84" s="7"/>
+          <t xml:space="preserve">--startup-service → --compose-service → 起動中の全サービス</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可 (繰り返し / カンマ区切り)</t>
+        </is>
+      </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="19.5" customHeight="1">
+          <t xml:space="preserve">必須コンテナ (essential=true 相当) として扱うサービス。ECS はタスク内の全コンテナを止めるが、ここではこの一覧だけを停止する</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="33.0" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
+          <t xml:space="preserve">--ecs-circuit-breaker-threshold N</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIME タイプ</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="E85" s="7"/>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="19.5" customHeight="1">
+          <t xml:space="preserve">サーキットブレーカが開くまでの失敗タスク数 (ECS の「必要数の 0.5 倍・最小 3・最大 200」に合わせた既定値)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="33.0" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
+          <t xml:space="preserve">--ecs-stop-timeout SEC</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSON 文字列</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E86" s="7"/>
+          <t xml:space="preserve">1 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="19.5" customHeight="1">
+          <t xml:space="preserve">SIGTERM から SIGKILL までの猶予 (ECS の stopTimeout / ECS_CONTAINER_STOP_TIMEOUT の既定と同じ)。短くすると reload との重なりを作りやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="33.0" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
+          <t xml:space="preserve">--ecs-circuit-breaker-reload-delay SEC</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">key=value&amp;...</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E87" s="7"/>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="19.5" customHeight="1">
+          <t xml:space="preserve">:reload を実行してから停止を始めるまでの秒数。0 で同時</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="33.0" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--no-ecs-circuit-breaker-reload</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60</t>
-        </is>
-      </c>
-      <c r="E88" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="19.5" customHeight="1">
+          <t xml:space="preserve">:reload を挟まず停止だけを再現する (切断の要因を切り分けるとき)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="33.0" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--ecs-circuit-breaker-replace-timeout SEC</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E89" s="7"/>
+          <t xml:space="preserve">0 (自動)</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="19.5" customHeight="1">
+          <t xml:space="preserve">置き換えたタスクの healthy / unhealthy 判定を待つ秒数。0 なら start_period + interval × (retries + 1) を計算し 30〜300 秒へ収める</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="33.0" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--ecs-server-log PATH</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動検出)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">server.log の場所。既定は $JBOSS_HOME/standalone/log/server.log を探す</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="33.0" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--ecs-circuit-breaker-drill</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E90" s="7"/>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="19.5" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
-        </is>
-      </c>
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bash / http / logs</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E91" s="7"/>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
+          <t xml:space="preserve">必須コンテナが unhealthy にならなくても、動作確認をすべて終えた後に 1 回だけ意図的に再現する (置き換えは行わない)</t>
         </is>
       </c>
     </row>
     <row r="92" ht="33.0" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--ecs-circuit-breaker-text FILE</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
-        </is>
-      </c>
-      <c r="E92" s="7"/>
+          <t xml:space="preserve">(--report-dir 配下へ自動命名)</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
+          <t xml:space="preserve">再現結果のテキスト出力先</t>
         </is>
       </c>
     </row>
     <row r="93" ht="33.0" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--no-ecs-circuit-breaker-text</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
-        </is>
-      </c>
-      <c r="E93" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+          <t xml:space="preserve">テキストファイルへの出力を行わない</t>
         </is>
       </c>
     </row>
     <row r="94" ht="33.0" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--ecs-circuit-breaker-display</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5610,27 +5658,31 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E94" s="7"/>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定で有効)</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+          <t xml:space="preserve">再現結果を画面へ出す</t>
         </is>
       </c>
     </row>
     <row r="95" ht="33.0" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-after-interaction</t>
+          <t xml:space="preserve">--no-ecs-circuit-breaker-display</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5643,22 +5695,26 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E95" s="7"/>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="19.5" customHeight="1">
+          <t xml:space="preserve">画面への出力を抑制する (テキストと全量レポートへは出す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="33.0" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--remove-volumes</t>
+          <t xml:space="preserve">--no-ecs-circuit-breaker-save-server-log</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -5671,143 +5727,143 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E96" s="7"/>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="33.0" customHeight="1">
+          <t xml:space="preserve">切れたままの server.log をファイルとして残さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="19.5" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-volumes</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">URL</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
     <row r="98" ht="19.5" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--usage-check-script PATH</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動解決)</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E98" s="7"/>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
     <row r="99" ht="19.5" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-free-path DIR</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ</t>
+          <t xml:space="preserve">HTTP メソッド</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定の 7 か所)</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストメソッド</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="19.5" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">MIME タイプ</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(自動)</t>
+        </is>
+      </c>
+      <c r="E100" s="7"/>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
     <row r="101" ht="19.5" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">JSON 文字列</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -5815,122 +5871,106 @@
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="E101" s="7"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
         </is>
       </c>
     </row>
     <row r="102" ht="19.5" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">key=value&amp;...</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E102" s="7"/>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
         </is>
       </c>
     </row>
     <row r="103" ht="19.5" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c r="E103" s="7"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="33.0" customHeight="1">
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="19.5" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E104" s="7"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+          <t xml:space="preserve">リトライ間隔</t>
         </is>
       </c>
     </row>
     <row r="105" ht="19.5" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -5938,595 +5978,555 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E105" s="7"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="49.5" customHeight="1">
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="19.5" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">bash / http / logs</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E106" s="7"/>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブック (.xlsx) へ追加出力する。リンク先は右端の列へ並べる。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="19.5" customHeight="1">
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="33.0" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(ログから検出)</t>
+        </is>
+      </c>
+      <c r="E107" s="7"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
     <row r="108" ht="33.0" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1〜65535</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+        </is>
+      </c>
+      <c r="E108" s="7"/>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する。指定すると Excel 出力を有効にする (--report-dir が無くても出力できる)</t>
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
         </is>
       </c>
     </row>
     <row r="109" ht="33.0" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E109" s="7"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
         </is>
       </c>
     </row>
     <row r="110" ht="33.0" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--keep-container-after-interaction</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E110" s="7"/>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="33.0" customHeight="1">
+          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="19.5" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--remove-volumes</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E111" s="7"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="115.5" customHeight="1">
+          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="33.0" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--keep-volumes</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E112" s="7"/>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="33.0" customHeight="1">
+          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="19.5" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
+          <t xml:space="preserve">--usage-check-script PATH</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(自動解決)</t>
+        </is>
+      </c>
+      <c r="E113" s="7"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
         </is>
       </c>
     </row>
     <row r="114" ht="19.5" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--disk-free-path DIR</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリ</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定の 7 か所)</t>
+        </is>
+      </c>
+      <c r="E114" s="7"/>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="33.0" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-deploy-exception-display</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="19.5" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-file FILE</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="19.5" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="49.5" customHeight="1">
-      <c r="A115" s="11" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="19.5" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-report</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D115" s="8" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="33.0" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
-      <c r="E115" s="7" t="inlineStr">
+      <c r="E119" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="33.0" customHeight="1">
-      <c r="A116" s="11" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="19.5" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-deploy-exception-report</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="33.0" customHeight="1">
-      <c r="A117" s="11" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="49.5" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブック (.xlsx) へ追加出力する。リンク先は右端の列へ並べる。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="19.5" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の Excel 出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="33.0" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="33.0" customHeight="1">
-      <c r="A118" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B118" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし。指定時のみ出力)</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="19.5" customHeight="1">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B119" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 以上の整数</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="33.0" customHeight="1">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B120" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="33.0" customHeight="1">
-      <c r="A121" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B121" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-display</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="33.0" customHeight="1">
-      <c r="A122" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B122" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis-display</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="49.5" customHeight="1">
-      <c r="A123" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B123" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-report</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する。指定すると Excel 出力を有効にする (--report-dir が無くても出力できる)</t>
         </is>
       </c>
     </row>
@@ -6538,17 +6538,17 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis-report</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -6570,17 +6570,17 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -6602,12 +6602,12 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -6617,140 +6617,140 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="115.5" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="19.5" customHeight="1">
-      <c r="A127" s="11" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="33.0" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="inlineStr">
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="49.5" customHeight="1">
-      <c r="A128" s="11" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="19.5" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="33.0" customHeight="1">
-      <c r="A129" s="11" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="49.5" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D129" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-report</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="19.5" customHeight="1">
-      <c r="A130" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B130" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
+          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6762,17 +6762,17 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
+          <t xml:space="preserve">--no-deploy-exception-report</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+          <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
         </is>
       </c>
     </row>
@@ -6794,17 +6794,17 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-display</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">分析結果をダイアログの操作後に画面へも出力する (既定では画面へ出さない)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -6826,91 +6826,91 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="19.5" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="33.0" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="33.0" customHeight="1">
-      <c r="A134" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B134" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="19.5" customHeight="1">
-      <c r="A135" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B135" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
+          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6922,17 +6922,17 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
+          <t xml:space="preserve">--readonly-analysis-display</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
@@ -6942,11 +6942,11 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="19.5" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="33.0" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
+          <t xml:space="preserve">--no-readonly-analysis-display</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
@@ -6974,11 +6974,11 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="33.0" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="49.5" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6986,17 +6986,17 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-module-list-text FILE</t>
+          <t xml:space="preserve">--readonly-analysis-report</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
@@ -7006,11 +7006,11 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBoss モジュール一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-jboss-module-list-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="19.5" customHeight="1">
+          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="33.0" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-jboss-module-list-text</t>
+          <t xml:space="preserve">--no-readonly-analysis-report</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBoss モジュール一覧のテキスト出力を行わない (画面表示だけにする)</t>
+          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
         </is>
       </c>
     </row>
@@ -7050,12 +7050,12 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--truststore-inventory-text FILE</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">トラストストア一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-truststore-inventory-text とは排他</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -7082,156 +7082,172 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-truststore-inventory-text</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="19.5" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-readonly-analysis</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E141" s="7" t="inlineStr">
+      <c r="E142" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">トラストストア一覧のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="33.0" customHeight="1">
-      <c r="A142" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
-        </is>
-      </c>
-      <c r="B142" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E142" s="7"/>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="33.0" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="49.5" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E143" s="7"/>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="144" ht="33.0" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="19.5" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E144" s="7"/>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="33.0" customHeight="1">
-      <c r="A145" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B145" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--prune-build-cache</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E145" s="7"/>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
     <row r="146" ht="33.0" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -7239,22 +7255,26 @@
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E146" s="7"/>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="147" ht="33.0" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--undertow-analysis-display</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -7267,22 +7287,26 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E147" s="7"/>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="66.0" customHeight="1">
+          <t xml:space="preserve">分析結果をダイアログの操作後に画面へも出力する (既定では画面へ出さない)。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="33.0" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-syslog</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -7292,25 +7316,29 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E148" s="7"/>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="49.5" customHeight="1">
+          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="33.0" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-suppress-syslog</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -7323,106 +7351,122 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E149" s="7"/>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="49.5" customHeight="1">
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="19.5" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+          <t xml:space="preserve">--no-undertow-analysis</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">json-file / local</t>
-        </is>
-      </c>
-      <c r="D150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">json-file</t>
-        </is>
-      </c>
-      <c r="E150" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="49.5" customHeight="1">
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="33.0" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-audit</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="19.5" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D151" s="3" t="inlineStr">
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E151" s="7"/>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="49.5" customHeight="1">
-      <c r="A152" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B152" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-syslog-audit</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D152" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E152" s="7"/>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">増加量の計測を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="49.5" customHeight="1">
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="33.0" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-audit-file FILE</t>
+          <t xml:space="preserve">--jboss-module-list-text FILE</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -7430,307 +7474,463 @@
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/var/log/messages</t>
-        </is>
-      </c>
-      <c r="E153" s="7"/>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
+          <t xml:space="preserve">JBoss モジュール一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-jboss-module-list-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="154" ht="19.5" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C154" s="3"/>
-      <c r="D154" s="3"/>
-      <c r="E154" s="7"/>
+          <t xml:space="preserve">--no-jboss-module-list-text</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">JBoss モジュール一覧のテキスト出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="155" ht="33.0" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C155" s="3"/>
-      <c r="D155" s="3"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="3"/>
+          <t xml:space="preserve">--truststore-inventory-text FILE</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トラストストア一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-truststore-inventory-text とは排他</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="33.0" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
-        </is>
-      </c>
-      <c r="C156" s="3"/>
-      <c r="D156" s="3"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="3"/>
+          <t xml:space="preserve">--no-truststore-inventory-text</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トラストストア一覧のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="33.0" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
-        </is>
-      </c>
-      <c r="C157" s="3"/>
-      <c r="D157" s="3"/>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E157" s="7"/>
-      <c r="F157" s="3"/>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="33.0" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
-        </is>
-      </c>
-      <c r="C158" s="3"/>
-      <c r="D158" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E158" s="7"/>
-      <c r="F158" s="3"/>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="33.0" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
-        </is>
-      </c>
-      <c r="C159" s="3"/>
-      <c r="D159" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E159" s="7"/>
-      <c r="F159" s="3"/>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="33.0" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C160" s="3"/>
-      <c r="D160" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E160" s="7"/>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
     <row r="161" ht="33.0" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C161" s="3"/>
-      <c r="D161" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E161" s="7"/>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
         </is>
       </c>
     </row>
     <row r="162" ht="33.0" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
-        </is>
-      </c>
-      <c r="C162" s="3"/>
-      <c r="D162" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E162" s="7"/>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="66.0" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C163" s="3"/>
-      <c r="D163" s="3"/>
+          <t xml:space="preserve">--suppress-syslog</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E163" s="7"/>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="33.0" customHeight="1">
+          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="49.5" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C164" s="3"/>
-      <c r="D164" s="3"/>
+          <t xml:space="preserve">--no-suppress-syslog</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E164" s="7"/>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="33.0" customHeight="1">
+          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="49.5" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
-        </is>
-      </c>
-      <c r="C165" s="3"/>
-      <c r="D165" s="3"/>
+          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file / local</t>
+        </is>
+      </c>
+      <c r="D165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file</t>
+        </is>
+      </c>
       <c r="E165" s="7"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="49.5" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
-        </is>
-      </c>
-      <c r="C166" s="3"/>
-      <c r="D166" s="3"/>
+          <t xml:space="preserve">--syslog-audit</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E166" s="7"/>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="33.0" customHeight="1">
+          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="49.5" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
-        </is>
-      </c>
-      <c r="C167" s="3"/>
-      <c r="D167" s="3"/>
+          <t xml:space="preserve">--no-syslog-audit</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E167" s="7"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="33.0" customHeight="1">
+          <t xml:space="preserve">増加量の計測を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="49.5" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
-        </is>
-      </c>
-      <c r="C168" s="3"/>
-      <c r="D168" s="3"/>
+          <t xml:space="preserve">--syslog-audit-file FILE</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D168" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/var/log/messages</t>
+        </is>
+      </c>
       <c r="E168" s="7"/>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="33.0" customHeight="1">
+          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="19.5" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C169" s="3"/>
@@ -7738,72 +7938,352 @@
       <c r="E169" s="7"/>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
     <row r="170" ht="33.0" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="7"/>
-      <c r="F170" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
-        </is>
-      </c>
+      <c r="F170" s="3"/>
     </row>
     <row r="171" ht="33.0" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="7"/>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F171" s="3"/>
     </row>
     <row r="172" ht="33.0" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="7"/>
-      <c r="F172" s="3" t="inlineStr">
+      <c r="F172" s="3"/>
+    </row>
+    <row r="173" ht="33.0" customHeight="1">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+        </is>
+      </c>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-L 深さ</t>
+        </is>
+      </c>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="3"/>
+    </row>
+    <row r="174" ht="33.0" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+        </is>
+      </c>
+      <c r="B174" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--noreport</t>
+        </is>
+      </c>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="7"/>
+      <c r="F174" s="3"/>
+    </row>
+    <row r="175" ht="33.0" customHeight="1">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(未指定)</t>
+        </is>
+      </c>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="7"/>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="33.0" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="7"/>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="33.0" customHeight="1">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B177" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree</t>
+        </is>
+      </c>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="7"/>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="33.0" customHeight="1">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B178" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="33.0" customHeight="1">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="7"/>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="33.0" customHeight="1">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B180" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="7"/>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="33.0" customHeight="1">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B181" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="7"/>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="33.0" customHeight="1">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B182" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+        </is>
+      </c>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="7"/>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="33.0" customHeight="1">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B183" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="7"/>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="33.0" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="7"/>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="33.0" customHeight="1">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B185" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+      <c r="E185" s="7"/>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="33.0" customHeight="1">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B186" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
+      <c r="E186" s="7"/>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="33.0" customHeight="1">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B187" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
+      <c r="E187" s="7"/>
+      <c r="F187" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F172"/>
+  <autoFilter ref="A4:F187"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -11947,8 +12427,127 @@
         </is>
       </c>
     </row>
+    <row r="63" ht="132.0" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECS サーキットブレーカによるタスク停止の再現 (既定で有効)
+必須コンテナの healthcheck が unhealthy になった実行でだけ動く。
+SIGTERM → stopTimeout → SIGKILL を jboss-cli の :reload と重ね、
+停止前後の server.log を突き合わせて切れ方まで判定する</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --compose-service app --startup-service app \
+    --report-dir ./reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="66.0" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20-2</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常に起動する構成でも、事象を手元で起こしてみる
+(動作確認をすべて終えた後に 1 回だけ停止する。置き換えは行わない)</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --compose-service app --startup-service app \
+    --ecs-circuit-breaker-drill --report-dir ./reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="33.0" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20-3</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SIGKILL を早めて reload との重なりを作りやすくする</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup \
+    --ecs-stop-timeout 5 --ecs-circuit-breaker-reload-delay 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="33.0" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20-4</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">切断の要因を切り分ける (reload を挟まず、停止だけを再現する)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-ecs-circuit-breaker-reload</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="33.0" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20-5</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">再現を行わない (従来どおり、unhealthy でも止めない)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-ecs-circuit-breaker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D62"/>
+  <autoFilter ref="A4:D67"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">183 件</t>
+          <t xml:space="preserve">193 件</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="33.0" customHeight="1">
+    <row r="90" ht="49.5" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
@@ -5522,27 +5522,27 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--ecs-server-log PATH</t>
+          <t xml:space="preserve">--ecs-circuit-breaker-watch</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内の絶対パス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(自動検出)</t>
+          <t xml:space="preserve">--ecs-essential-service 指定時は有効</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">server.log の場所。既定は $JBOSS_HOME/standalone/log/server.log を探す</t>
+          <t xml:space="preserve">起動完了ログを検出した後も、必須コンテナの healthcheck が healthy / unhealthy のどちらになるかを待つ。start_period が長い構成では判定が起動完了ログより後に出るため、待たないと再現が始まらない</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--ecs-circuit-breaker-drill</t>
+          <t xml:space="preserve">--no-ecs-circuit-breaker-watch</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">必須コンテナが unhealthy にならなくても、動作確認をすべて終えた後に 1 回だけ意図的に再現する (置き換えは行わない)</t>
+          <t xml:space="preserve">判定を待たない (--ecs-essential-service 指定時の既定を打ち消す)</t>
         </is>
       </c>
     </row>
@@ -5586,17 +5586,17 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--ecs-circuit-breaker-text FILE</t>
+          <t xml:space="preserve">--ecs-circuit-breaker-watch-timeout SEC</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(--report-dir 配下へ自動命名)</t>
+          <t xml:space="preserve">0 (自動)</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -5606,11 +5606,11 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">再現結果のテキスト出力先</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="33.0" customHeight="1">
+          <t xml:space="preserve">判定を待つ秒数。0 なら start_period の残り + interval × retries を計算し 30〜900 秒へ収める</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="66.0" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-ecs-circuit-breaker-text</t>
+          <t xml:space="preserve">--ecs-circuit-breaker-ignore-start-period</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">テキストファイルへの出力を行わない</t>
+          <t xml:space="preserve">start_period の間の healthcheck 失敗も数え、retries 回続けて失敗した時点で unhealthy とみなす (.State.Health.Log の終了コードで数える)。docker / ECS の仕様より早く判定するため、start_period が長い構成でも待たずに再現できる</t>
         </is>
       </c>
     </row>
@@ -5650,27 +5650,27 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--ecs-circuit-breaker-display</t>
+          <t xml:space="preserve">--ecs-server-log PATH</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">コンテナ内の絶対パス</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(既定で有効)</t>
+          <t xml:space="preserve">(自動検出)</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">再現結果を画面へ出す</t>
+          <t xml:space="preserve">server.log の場所。既定は $JBOSS_HOME/standalone/log/server.log を探す</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-ecs-circuit-breaker-display</t>
+          <t xml:space="preserve">--ecs-circuit-breaker-drill</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面への出力を抑制する (テキストと全量レポートへは出す)</t>
+          <t xml:space="preserve">必須コンテナが unhealthy にならなくても、動作確認をすべて終えた後に 1 回だけ意図的に再現する (置き換えは行わない)</t>
         </is>
       </c>
     </row>
@@ -5714,139 +5714,155 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--ecs-circuit-breaker-text FILE</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(--report-dir 配下へ自動命名)</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">再現結果のテキスト出力先</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="33.0" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-ecs-circuit-breaker-text</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">テキストファイルへの出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="33.0" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--ecs-circuit-breaker-display</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定で有効)</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">再現結果を画面へ出す</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="33.0" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-ecs-circuit-breaker-display</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面への出力を抑制する (テキストと全量レポートへは出す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="33.0" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4-2 ECS サーキットブレーカによるタスク停止の再現</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--no-ecs-circuit-breaker-save-server-log</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">切れたままの server.log をファイルとして残さない</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="19.5" customHeight="1">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--verify-url URL</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URL</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E97" s="7"/>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="19.5" customHeight="1">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--expect-status CODE</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP ステータスコード</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200</t>
-        </is>
-      </c>
-      <c r="E98" s="7"/>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待するステータスコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="19.5" customHeight="1">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B99" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-method METHOD</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP メソッド</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GET</t>
-        </is>
-      </c>
-      <c r="E99" s="7"/>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リクエストメソッド</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="19.5" customHeight="1">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 URL 応答確認</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--url-content-type TYPE</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIME タイプ</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動)</t>
-        </is>
-      </c>
-      <c r="E100" s="7"/>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5874,12 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-json JSON</t>
+          <t xml:space="preserve">--verify-url URL</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSON 文字列</t>
+          <t xml:space="preserve">URL</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -5874,7 +5890,7 @@
       <c r="E101" s="7"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
+          <t xml:space="preserve">起動確認後にこの URL へリクエストして応答を確認</t>
         </is>
       </c>
     </row>
@@ -5886,23 +5902,23 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-body-form DATA</t>
+          <t xml:space="preserve">--expect-status CODE</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">key=value&amp;...</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">HTTP ステータスコード</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="E102" s="7"/>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+          <t xml:space="preserve">期待するステータスコード</t>
         </is>
       </c>
     </row>
@@ -5914,23 +5930,23 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-timeout SEC</t>
+          <t xml:space="preserve">--url-method METHOD</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">HTTP メソッド</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">GET</t>
         </is>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+          <t xml:space="preserve">リクエストメソッド</t>
         </is>
       </c>
     </row>
@@ -5942,23 +5958,23 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-interval SEC</t>
+          <t xml:space="preserve">--url-content-type TYPE</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">MIME タイプ</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">(自動)</t>
         </is>
       </c>
       <c r="E104" s="7"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">リトライ間隔</t>
+          <t xml:space="preserve">Content-Type ヘッダ。--verify-url と併用必須</t>
         </is>
       </c>
     </row>
@@ -5970,40 +5986,40 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--url-insecure</t>
+          <t xml:space="preserve">--url-body-json JSON</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">JSON 文字列</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+          <t xml:space="preserve">リクエストボディ。未指定時 Content-Type: application/json を自動設定</t>
         </is>
       </c>
     </row>
     <row r="106" ht="19.5" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-mode MODE</t>
+          <t xml:space="preserve">--url-body-form DATA</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bash / http / logs</t>
+          <t xml:space="preserve">key=value&amp;...</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -6014,75 +6030,75 @@
       <c r="E106" s="7"/>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リクエストボディ。未指定時 application/x-www-form-urlencoded を自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="19.5" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-context-root ROOT</t>
+          <t xml:space="preserve">--url-timeout SEC</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテキストルートのパス</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出)</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="33.0" customHeight="1">
+          <t xml:space="preserve">期待応答を得るまでの最大秒数</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="19.5" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-http-port PORT</t>
+          <t xml:space="preserve">--url-interval SEC</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜65535</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ログから検出。既定 8080)</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E108" s="7"/>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="33.0" customHeight="1">
+          <t xml:space="preserve">リトライ間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="19.5" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
+          <t xml:space="preserve">4.5 URL 応答確認</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--exit-on-deploy-error</t>
+          <t xml:space="preserve">--url-insecure</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -6098,11 +6114,11 @@
       <c r="E109" s="7"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="33.0" customHeight="1">
+          <t xml:space="preserve">TLS 証明書検証を無効化 (curl -k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="19.5" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -6110,27 +6126,27 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-container-after-interaction</t>
+          <t xml:space="preserve">--keep-container-mode MODE</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">bash / http / logs</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E110" s="7"/>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="19.5" customHeight="1">
+          <t xml:space="preserve">指定すると --verify-startup と --keep-container を暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="33.0" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -6138,23 +6154,23 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--remove-volumes</t>
+          <t xml:space="preserve">--jboss-context-root ROOT</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">コンテキストルートのパス</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出)</t>
         </is>
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
+          <t xml:space="preserve">http モード専用。URL 全体は指定不可</t>
         </is>
       </c>
     </row>
@@ -6166,27 +6182,27 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--keep-volumes</t>
+          <t xml:space="preserve">--jboss-http-port PORT</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1〜65535</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ログから検出。既定 8080)</t>
         </is>
       </c>
       <c r="E112" s="7"/>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="19.5" customHeight="1">
+          <t xml:space="preserve">http モード専用。公開ポートがあれば自動変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="33.0" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -6194,27 +6210,27 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--usage-check-script PATH</t>
+          <t xml:space="preserve">--exit-on-deploy-error</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(自動解決)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E113" s="7"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="19.5" customHeight="1">
+          <t xml:space="preserve">デプロイエラーを検出しても調査用の対話操作へ入らず、従来どおり終了する (→ 5.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="33.0" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 起動維持後の対話操作</t>
@@ -6222,343 +6238,303 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-free-path DIR</t>
+          <t xml:space="preserve">--keep-container-after-interaction</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリ</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(既定の 7 か所)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E114" s="7"/>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="33.0" customHeight="1">
+          <t xml:space="preserve">対話操作をすべて終えても完全クリーンアップを行わず、従来どおりコンテナを残す (→ 5.4-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="19.5" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--remove-volumes</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E115" s="7"/>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="19.5" customHeight="1">
+          <t xml:space="preserve">この実行が行うすべての compose down に --volumes を付ける (→ 5.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="33.0" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--keep-volumes</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E116" s="7"/>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+          <t xml:space="preserve">対話操作の終了後の後始末でもボリュームを削除しない (従来の動作)。--remove-volumes とは排他</t>
         </is>
       </c>
     </row>
     <row r="117" ht="19.5" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--usage-check-script PATH</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(自動解決)</t>
+        </is>
+      </c>
+      <c r="E117" s="7"/>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+          <t xml:space="preserve">完全クリアに使う docker-usage-check.sh のパス。読み取れない場合は exit 2</t>
         </is>
       </c>
     </row>
     <row r="118" ht="19.5" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6 起動維持後の対話操作</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--disk-free-path DIR</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">ディレクトリ</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(既定の 7 か所)</t>
+        </is>
+      </c>
+      <c r="E118" s="7"/>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+          <t xml:space="preserve">終了時の空き容量一覧へ表示するディレクトリを追加 (繰り返し指定可)</t>
         </is>
       </c>
     </row>
     <row r="119" ht="33.0" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-2 Valkey (Redis 互換) の操作・登録内容の確認</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--valkey-service NAME</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Compose サービス名</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動検出)</t>
+        </is>
+      </c>
+      <c r="E119" s="7"/>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valkey サーバーのサービス名 (→ 5.4-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="33.0" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6-2 Valkey (Redis 互換) の操作・登録内容の確認</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--valkey-port PORT</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1〜65535</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動検出。既定 6379)</t>
+        </is>
+      </c>
+      <c r="E120" s="7"/>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">接続先のコンテナ側ポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="33.0" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6-2 Valkey (Redis 互換) の操作・登録内容の確認</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--valkey-tls</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="19.5" customHeight="1">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B120" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(自動判定)</t>
+        </is>
+      </c>
+      <c r="E121" s="7"/>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TLS で接続する (openssl s_client を使う)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="33.0" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6-2 Valkey (Redis 互換) の操作・登録内容の確認</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-valkey-tls</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="49.5" customHeight="1">
-      <c r="A121" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B121" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブック (.xlsx) へ追加出力する。リンク先は右端の列へ並べる。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="19.5" customHeight="1">
-      <c r="A122" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B122" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(自動判定)</t>
+        </is>
+      </c>
+      <c r="E122" s="7"/>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない</t>
+          <t xml:space="preserve">平文で接続する (bash の /dev/tcp を使う)</t>
         </is>
       </c>
     </row>
     <row r="123" ht="33.0" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-2 Valkey (Redis 互換) の操作・登録内容の確認</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+          <t xml:space="preserve">--valkey-scan-pattern P</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">SCAN のパターン</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="E123" s="7"/>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する。指定すると Excel 出力を有効にする (--report-dir が無くても出力できる)</t>
+          <t xml:space="preserve">登録内容の一覧で使うパターン</t>
         </is>
       </c>
     </row>
     <row r="124" ht="33.0" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-2 Valkey (Redis 互換) の操作・登録内容の確認</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--print-valkey-shell-cli</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D124" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E124" s="7"/>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">代替シェル (valkey_shell_cli.sh) を標準出力へ書き出して終了</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6546,7 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -6580,7 +6556,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
@@ -6590,11 +6566,11 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="33.0" customHeight="1">
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="19.5" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6602,12 +6578,12 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--env-list-file FILE</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -6617,16 +6593,16 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="115.5" customHeight="1">
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="19.5" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6634,17 +6610,17 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir DIR</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
@@ -6654,11 +6630,11 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="19.5" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6666,7 +6642,7 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -6674,9 +6650,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
@@ -6686,11 +6662,11 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="19.5" customHeight="1">
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="33.0" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6698,7 +6674,7 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-display</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -6706,9 +6682,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
@@ -6718,11 +6694,11 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="49.5" customHeight="1">
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="19.5" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6730,7 +6706,7 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-report</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -6740,81 +6716,81 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="49.5" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
-      <c r="E130" s="7" t="inlineStr">
+      <c r="E131" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="33.0" customHeight="1">
-      <c r="A131" s="11" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブック (.xlsx) へ追加出力する。リンク先は右端の列へ並べる。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="19.5" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-deploy-exception-report</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr">
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="33.0" customHeight="1">
-      <c r="A132" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B132" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">上記の Excel 出力を行わない</t>
         </is>
       </c>
     </row>
@@ -6826,17 +6802,17 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
@@ -6846,11 +6822,11 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="19.5" customHeight="1">
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する。指定すると Excel 出力を有効にする (--report-dir が無くても出力できる)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="33.0" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -6858,17 +6834,17 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
@@ -6878,7 +6854,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -6890,17 +6866,17 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
@@ -6910,7 +6886,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -6922,155 +6898,155 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-display</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="115.5" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="33.0" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D136" s="8" t="inlineStr">
+      <c r="D138" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
-      <c r="E136" s="7" t="inlineStr">
+      <c r="E138" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="33.0" customHeight="1">
-      <c r="A137" s="11" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="19.5" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis-display</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="E137" s="7" t="inlineStr">
+      <c r="E139" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="49.5" customHeight="1">
-      <c r="A138" s="11" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="49.5" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-report</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-report</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D138" s="8" t="inlineStr">
+      <c r="D140" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
-      <c r="E138" s="7" t="inlineStr">
+      <c r="E140" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="33.0" customHeight="1">
-      <c r="A139" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B139" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis-report</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="33.0" customHeight="1">
-      <c r="A140" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B140" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -7082,155 +7058,155 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--no-deploy-exception-report</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="33.0" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="33.0" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="19.5" customHeight="1">
-      <c r="A142" s="11" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="19.5" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B142" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="33.0" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E142" s="7" t="inlineStr">
+      <c r="E145" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="49.5" customHeight="1">
-      <c r="A143" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B143" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="33.0" customHeight="1">
-      <c r="A144" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B144" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D144" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="19.5" customHeight="1">
-      <c r="A145" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B145" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
+          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
@@ -7242,17 +7218,17 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
+          <t xml:space="preserve">--readonly-analysis-display</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
@@ -7262,7 +7238,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7250,7 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-display</t>
+          <t xml:space="preserve">--no-readonly-analysis-display</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -7284,7 +7260,7 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr">
@@ -7294,11 +7270,11 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">分析結果をダイアログの操作後に画面へも出力する (既定では画面へ出さない)。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="33.0" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="49.5" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7306,7 +7282,7 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
+          <t xml:space="preserve">--readonly-analysis-report</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -7316,7 +7292,7 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr">
@@ -7326,7 +7302,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7314,7 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
+          <t xml:space="preserve">--no-readonly-analysis-report</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -7348,7 +7324,7 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr">
@@ -7358,11 +7334,11 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="19.5" customHeight="1">
+          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="33.0" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7370,17 +7346,17 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
@@ -7390,7 +7366,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7378,7 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -7422,7 +7398,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7410,7 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
+          <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -7454,11 +7430,11 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="33.0" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="49.5" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7466,12 +7442,12 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-module-list-text FILE</t>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -7481,76 +7457,76 @@
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="33.0" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBoss モジュール一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-jboss-module-list-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="19.5" customHeight="1">
-      <c r="A154" s="11" t="inlineStr">
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="19.5" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B154" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-jboss-module-list-text</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E154" s="7" t="inlineStr">
+      <c r="E155" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBoss モジュール一覧のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="33.0" customHeight="1">
-      <c r="A155" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B155" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--truststore-inventory-text FILE</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E155" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">トラストストア一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-truststore-inventory-text とは排他</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
@@ -7562,17 +7538,17 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-truststore-inventory-text</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
@@ -7582,19 +7558,19 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">トラストストア一覧のテキスト出力を行わない (画面表示だけにする)</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="157" ht="33.0" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--undertow-analysis-display</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -7607,50 +7583,58 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E157" s="7"/>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">分析結果をダイアログの操作後に画面へも出力する (既定では画面へ出さない)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="158" ht="33.0" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E158" s="7"/>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
         </is>
       </c>
     </row>
     <row r="159" ht="33.0" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -7663,22 +7647,26 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E159" s="7"/>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="33.0" customHeight="1">
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="19.5" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--no-undertow-analysis</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -7691,27 +7679,31 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E160" s="7"/>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
         </is>
       </c>
     </row>
     <row r="161" ht="33.0" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--cert-check-text FILE</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -7719,22 +7711,26 @@
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E161" s="7"/>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="33.0" customHeight="1">
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="19.5" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--no-cert-check-text</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -7747,370 +7743,490 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E162" s="7"/>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="66.0" customHeight="1">
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="33.0" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-syslog</t>
+          <t xml:space="preserve">--jboss-module-list-text FILE</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss モジュール一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-jboss-module-list-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="19.5" customHeight="1">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B164" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-jboss-module-list-text</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D163" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E163" s="7"/>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="49.5" customHeight="1">
-      <c r="A164" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B164" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-suppress-syslog</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss モジュール一覧のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="33.0" customHeight="1">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--truststore-inventory-text FILE</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トラストストア一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-truststore-inventory-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="33.0" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B166" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-truststore-inventory-text</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D164" s="3" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E164" s="7"/>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="49.5" customHeight="1">
-      <c r="A165" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B165" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">json-file / local</t>
-        </is>
-      </c>
-      <c r="D165" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">json-file</t>
-        </is>
-      </c>
-      <c r="E165" s="7"/>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="49.5" customHeight="1">
-      <c r="A166" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B166" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--syslog-audit</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トラストストア一覧のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="33.0" customHeight="1">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+        </is>
+      </c>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D166" s="3" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E166" s="7"/>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="49.5" customHeight="1">
-      <c r="A167" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B167" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-syslog-audit</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D167" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E167" s="7"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">増加量の計測を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="49.5" customHeight="1">
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="33.0" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-audit-file FILE</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/var/log/messages</t>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E168" s="7"/>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="19.5" customHeight="1">
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="33.0" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C169" s="3"/>
-      <c r="D169" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E169" s="7"/>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
     <row r="170" ht="33.0" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C170" s="3"/>
-      <c r="D170" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E170" s="7"/>
-      <c r="F170" s="3"/>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="33.0" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
-        </is>
-      </c>
-      <c r="C171" s="3"/>
-      <c r="D171" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E171" s="7"/>
-      <c r="F171" s="3"/>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="33.0" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
-        </is>
-      </c>
-      <c r="C172" s="3"/>
-      <c r="D172" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E172" s="7"/>
-      <c r="F172" s="3"/>
-    </row>
-    <row r="173" ht="33.0" customHeight="1">
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="66.0" customHeight="1">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
-        </is>
-      </c>
-      <c r="C173" s="3"/>
-      <c r="D173" s="3"/>
+          <t xml:space="preserve">--suppress-syslog</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D173" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E173" s="7"/>
-      <c r="F173" s="3"/>
-    </row>
-    <row r="174" ht="33.0" customHeight="1">
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="49.5" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
-        </is>
-      </c>
-      <c r="C174" s="3"/>
-      <c r="D174" s="3"/>
+          <t xml:space="preserve">--no-suppress-syslog</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E174" s="7"/>
-      <c r="F174" s="3"/>
-    </row>
-    <row r="175" ht="33.0" customHeight="1">
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="49.5" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C175" s="3"/>
-      <c r="D175" s="3"/>
+          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file / local</t>
+        </is>
+      </c>
+      <c r="D175" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file</t>
+        </is>
+      </c>
       <c r="E175" s="7"/>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="49.5" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C176" s="3"/>
-      <c r="D176" s="3"/>
+          <t xml:space="preserve">--syslog-audit</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E176" s="7"/>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="33.0" customHeight="1">
+          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="49.5" customHeight="1">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
-        </is>
-      </c>
-      <c r="C177" s="3"/>
-      <c r="D177" s="3"/>
+          <t xml:space="preserve">--no-syslog-audit</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E177" s="7"/>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="33.0" customHeight="1">
+          <t xml:space="preserve">増加量の計測を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="49.5" customHeight="1">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C178" s="3"/>
-      <c r="D178" s="3"/>
+          <t xml:space="preserve">--syslog-audit-file FILE</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D178" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/var/log/messages</t>
+        </is>
+      </c>
       <c r="E178" s="7"/>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="33.0" customHeight="1">
+          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="19.5" customHeight="1">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C179" s="3"/>
@@ -8118,109 +8234,89 @@
       <c r="E179" s="7"/>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
     <row r="180" ht="33.0" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="7"/>
-      <c r="F180" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
-        </is>
-      </c>
+      <c r="F180" s="3"/>
     </row>
     <row r="181" ht="33.0" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="7"/>
-      <c r="F181" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
-        </is>
-      </c>
+      <c r="F181" s="3"/>
     </row>
     <row r="182" ht="33.0" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="7"/>
-      <c r="F182" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
-        </is>
-      </c>
+      <c r="F182" s="3"/>
     </row>
     <row r="183" ht="33.0" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="7"/>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F183" s="3"/>
     </row>
     <row r="184" ht="33.0" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="7"/>
-      <c r="F184" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F184" s="3"/>
     </row>
     <row r="185" ht="33.0" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
@@ -8230,7 +8326,7 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C185" s="3"/>
@@ -8238,7 +8334,7 @@
       <c r="E185" s="7"/>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8346,7 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C186" s="3"/>
@@ -8258,7 +8354,7 @@
       <c r="E186" s="7"/>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8366,7 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C187" s="3"/>
@@ -8278,12 +8374,212 @@
       <c r="E187" s="7"/>
       <c r="F187" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="33.0" customHeight="1">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B188" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
+      <c r="E188" s="7"/>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="33.0" customHeight="1">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="33.0" customHeight="1">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B190" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
+      <c r="E190" s="7"/>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="33.0" customHeight="1">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B191" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+      <c r="E191" s="7"/>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="33.0" customHeight="1">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B192" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+        </is>
+      </c>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+      <c r="E192" s="7"/>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="33.0" customHeight="1">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B193" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3"/>
+      <c r="E193" s="7"/>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="33.0" customHeight="1">
+      <c r="A194" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B194" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+      <c r="E194" s="7"/>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="33.0" customHeight="1">
+      <c r="A195" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
+      <c r="E195" s="7"/>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="33.0" customHeight="1">
+      <c r="A196" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B196" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+      <c r="E196" s="7"/>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="33.0" customHeight="1">
+      <c r="A197" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B197" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3"/>
+      <c r="E197" s="7"/>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F187"/>
+  <autoFilter ref="A4:F197"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
